--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126178047</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126178127</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126182135</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126176893</v>
       </c>
       <c r="B5" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126175525</v>
+        <v>126180936</v>
       </c>
       <c r="B6" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,12 +1151,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1165,13 +1160,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533774</v>
+        <v>533738</v>
       </c>
       <c r="R6" t="n">
-        <v>6928715</v>
+        <v>6928768</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,22 +1220,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126180936</v>
+        <v>126175525</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,7 +1262,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1276,13 +1276,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533738</v>
+        <v>533774</v>
       </c>
       <c r="R7" t="n">
-        <v>6928768</v>
+        <v>6928715</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,12 +1336,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1351,7 +1351,7 @@
         <v>126182207</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126181209</v>
+        <v>126182178</v>
       </c>
       <c r="B9" t="n">
-        <v>91232</v>
+        <v>78732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533731</v>
+        <v>533652</v>
       </c>
       <c r="R9" t="n">
-        <v>6928754</v>
+        <v>6928869</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1575,7 @@
         <v>126176747</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126177259</v>
+        <v>126181693</v>
       </c>
       <c r="B11" t="n">
-        <v>80075</v>
+        <v>91234</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,42 +1699,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533735</v>
+        <v>533757</v>
       </c>
       <c r="R11" t="n">
-        <v>6928726</v>
+        <v>6928745</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1763,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126181693</v>
+        <v>126181209</v>
       </c>
       <c r="B12" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533757</v>
+        <v>533731</v>
       </c>
       <c r="R12" t="n">
-        <v>6928745</v>
+        <v>6928754</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1870,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,45 +1902,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126182188</v>
+        <v>126177259</v>
       </c>
       <c r="B13" t="n">
-        <v>92522</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533653</v>
+        <v>533735</v>
       </c>
       <c r="R13" t="n">
-        <v>6928877</v>
+        <v>6928726</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,32 +2014,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126182178</v>
+        <v>126182188</v>
       </c>
       <c r="B14" t="n">
-        <v>78731</v>
+        <v>92524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533652</v>
+        <v>533653</v>
       </c>
       <c r="R14" t="n">
-        <v>6928869</v>
+        <v>6928877</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,12 +2109,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2124,7 +2124,7 @@
         <v>126180157</v>
       </c>
       <c r="B15" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,57 +2237,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126178142</v>
+        <v>126182151</v>
       </c>
       <c r="B16" t="n">
-        <v>98373</v>
+        <v>91395</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533722</v>
+        <v>533652</v>
       </c>
       <c r="R16" t="n">
-        <v>6928754</v>
+        <v>6928869</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2316,7 +2307,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2326,7 +2317,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,60 +2332,69 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126182151</v>
+        <v>126178142</v>
       </c>
       <c r="B17" t="n">
-        <v>91393</v>
+        <v>98375</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533652</v>
+        <v>533722</v>
       </c>
       <c r="R17" t="n">
-        <v>6928869</v>
+        <v>6928754</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,12 +2448,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2463,7 +2463,7 @@
         <v>126180591</v>
       </c>
       <c r="B18" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126177332</v>
+        <v>126176599</v>
       </c>
       <c r="B19" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533734</v>
+        <v>533753</v>
       </c>
       <c r="R19" t="n">
-        <v>6928729</v>
+        <v>6928692</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,10 +2692,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126176599</v>
+        <v>126177332</v>
       </c>
       <c r="B20" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533753</v>
+        <v>533734</v>
       </c>
       <c r="R20" t="n">
-        <v>6928692</v>
+        <v>6928729</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2811,7 +2811,7 @@
         <v>126181665</v>
       </c>
       <c r="B21" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,57 +2915,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126178109</v>
+        <v>126181048</v>
       </c>
       <c r="B22" t="n">
-        <v>98373</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533718</v>
+        <v>533733</v>
       </c>
       <c r="R22" t="n">
-        <v>6928766</v>
+        <v>6928745</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2994,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,7 +2995,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer rikligt på två aspar och även en gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3019,66 +3015,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126178121</v>
+        <v>126176059</v>
       </c>
       <c r="B23" t="n">
-        <v>98373</v>
+        <v>91808</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219874</v>
+        <v>760</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533717</v>
+        <v>533746</v>
       </c>
       <c r="R23" t="n">
-        <v>6928757</v>
+        <v>6928708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3147,45 +3134,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126176059</v>
+        <v>126178109</v>
       </c>
       <c r="B24" t="n">
-        <v>91806</v>
+        <v>98375</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533746</v>
+        <v>533718</v>
       </c>
       <c r="R24" t="n">
-        <v>6928708</v>
+        <v>6928766</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,48 +3250,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126181048</v>
+        <v>126178121</v>
       </c>
       <c r="B25" t="n">
-        <v>80075</v>
+        <v>98375</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533733</v>
+        <v>533717</v>
       </c>
       <c r="R25" t="n">
-        <v>6928745</v>
+        <v>6928757</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,7 +3329,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3339,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växer rikligt på två aspar och även en gran</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,69 +3354,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126178017</v>
+        <v>126181871</v>
       </c>
       <c r="B26" t="n">
-        <v>98339</v>
+        <v>78732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533723</v>
+        <v>533757</v>
       </c>
       <c r="R26" t="n">
-        <v>6928730</v>
+        <v>6928745</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3445,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3470,57 +3461,66 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126178155</v>
+        <v>126175257</v>
       </c>
       <c r="B27" t="n">
-        <v>97223</v>
+        <v>98341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533696</v>
+        <v>533799</v>
       </c>
       <c r="R27" t="n">
-        <v>6928789</v>
+        <v>6928693</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3589,48 +3589,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126181871</v>
+        <v>126178017</v>
       </c>
       <c r="B28" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533757</v>
+        <v>533723</v>
       </c>
       <c r="R28" t="n">
-        <v>6928745</v>
+        <v>6928730</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3659,7 +3668,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3669,7 +3678,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3684,66 +3693,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126175257</v>
+        <v>126178155</v>
       </c>
       <c r="B29" t="n">
-        <v>98339</v>
+        <v>97225</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533799</v>
+        <v>533696</v>
       </c>
       <c r="R29" t="n">
-        <v>6928693</v>
+        <v>6928789</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3812,45 +3812,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126181652</v>
+        <v>126181494</v>
       </c>
       <c r="B30" t="n">
-        <v>92522</v>
+        <v>98341</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533745</v>
+        <v>533742</v>
       </c>
       <c r="R30" t="n">
-        <v>6928735</v>
+        <v>6928730</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3882,7 +3886,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3892,7 +3896,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3919,52 +3923,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126181494</v>
+        <v>126176544</v>
       </c>
       <c r="B31" t="n">
-        <v>98339</v>
+        <v>91530</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533742</v>
+        <v>533762</v>
       </c>
       <c r="R31" t="n">
-        <v>6928730</v>
+        <v>6928704</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4018,12 +4018,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4033,7 +4033,7 @@
         <v>126176144</v>
       </c>
       <c r="B32" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4137,32 +4137,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126176544</v>
+        <v>126181652</v>
       </c>
       <c r="B33" t="n">
-        <v>91528</v>
+        <v>92524</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533762</v>
+        <v>533745</v>
       </c>
       <c r="R33" t="n">
-        <v>6928704</v>
+        <v>6928735</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4232,22 +4232,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126177002</v>
+        <v>126181681</v>
       </c>
       <c r="B34" t="n">
-        <v>78731</v>
+        <v>91530</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4255,21 +4255,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4279,13 +4279,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533732</v>
+        <v>533745</v>
       </c>
       <c r="R34" t="n">
-        <v>6928727</v>
+        <v>6928735</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4339,54 +4339,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126175252</v>
+        <v>126180980</v>
       </c>
       <c r="B35" t="n">
-        <v>98339</v>
+        <v>98375</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4395,13 +4390,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533816</v>
+        <v>533724</v>
       </c>
       <c r="R35" t="n">
-        <v>6928686</v>
+        <v>6928748</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4430,7 +4425,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4440,7 +4435,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4455,44 +4450,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126178181</v>
+        <v>126177002</v>
       </c>
       <c r="B36" t="n">
-        <v>80035</v>
+        <v>78732</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4502,10 +4497,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533723</v>
+        <v>533732</v>
       </c>
       <c r="R36" t="n">
-        <v>6928739</v>
+        <v>6928727</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4574,10 +4569,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126180980</v>
+        <v>126178181</v>
       </c>
       <c r="B37" t="n">
-        <v>98373</v>
+        <v>80036</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4585,41 +4580,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533724</v>
+        <v>533723</v>
       </c>
       <c r="R37" t="n">
-        <v>6928748</v>
+        <v>6928739</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4648,7 +4639,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4658,7 +4649,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4673,60 +4664,69 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126181681</v>
+        <v>126175252</v>
       </c>
       <c r="B38" t="n">
-        <v>91528</v>
+        <v>98341</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533745</v>
+        <v>533816</v>
       </c>
       <c r="R38" t="n">
-        <v>6928735</v>
+        <v>6928686</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4780,44 +4780,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126177654</v>
+        <v>126175291</v>
       </c>
       <c r="B39" t="n">
-        <v>98373</v>
+        <v>80076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533727</v>
+        <v>533791</v>
       </c>
       <c r="R39" t="n">
-        <v>6928727</v>
+        <v>6928687</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4902,7 +4902,7 @@
         <v>126180836</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126175291</v>
+        <v>126182027</v>
       </c>
       <c r="B41" t="n">
-        <v>80075</v>
+        <v>91156</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>3242</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533791</v>
+        <v>533755</v>
       </c>
       <c r="R41" t="n">
-        <v>6928687</v>
+        <v>6928865</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5113,32 +5113,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126182027</v>
+        <v>126177654</v>
       </c>
       <c r="B42" t="n">
-        <v>91154</v>
+        <v>98375</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3242</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533755</v>
+        <v>533727</v>
       </c>
       <c r="R42" t="n">
-        <v>6928865</v>
+        <v>6928727</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5223,7 +5223,7 @@
         <v>126175980</v>
       </c>
       <c r="B43" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5336,32 +5336,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126179959</v>
+        <v>126182221</v>
       </c>
       <c r="B44" t="n">
-        <v>78731</v>
+        <v>92524</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533620</v>
+        <v>533640</v>
       </c>
       <c r="R44" t="n">
-        <v>6928771</v>
+        <v>6928856</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5443,32 +5443,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126182221</v>
+        <v>126176695</v>
       </c>
       <c r="B45" t="n">
-        <v>92522</v>
+        <v>91530</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5478,13 +5478,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533640</v>
+        <v>533734</v>
       </c>
       <c r="R45" t="n">
-        <v>6928856</v>
+        <v>6928700</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5538,12 +5538,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5553,7 +5553,7 @@
         <v>126182304</v>
       </c>
       <c r="B46" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126176695</v>
+        <v>126181218</v>
       </c>
       <c r="B47" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533734</v>
+        <v>533723</v>
       </c>
       <c r="R47" t="n">
-        <v>6928700</v>
+        <v>6928740</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5752,22 +5752,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126181218</v>
+        <v>126179959</v>
       </c>
       <c r="B48" t="n">
-        <v>91528</v>
+        <v>78732</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533723</v>
+        <v>533620</v>
       </c>
       <c r="R48" t="n">
-        <v>6928740</v>
+        <v>6928771</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5871,32 +5871,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126175432</v>
+        <v>126175215</v>
       </c>
       <c r="B49" t="n">
-        <v>80035</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533782</v>
+        <v>533811</v>
       </c>
       <c r="R49" t="n">
-        <v>6928709</v>
+        <v>6928661</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5978,10 +5978,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126175215</v>
+        <v>126182185</v>
       </c>
       <c r="B50" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5989,21 +5989,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533811</v>
+        <v>533637</v>
       </c>
       <c r="R50" t="n">
-        <v>6928661</v>
+        <v>6928864</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6085,57 +6085,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126177821</v>
+        <v>126180415</v>
       </c>
       <c r="B51" t="n">
-        <v>98339</v>
+        <v>78732</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533723</v>
+        <v>533678</v>
       </c>
       <c r="R51" t="n">
-        <v>6928726</v>
+        <v>6928776</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6164,7 +6155,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6174,7 +6165,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6189,44 +6180,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126180415</v>
+        <v>126175432</v>
       </c>
       <c r="B52" t="n">
-        <v>78731</v>
+        <v>80036</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6236,13 +6227,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533678</v>
+        <v>533782</v>
       </c>
       <c r="R52" t="n">
-        <v>6928776</v>
+        <v>6928709</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6271,7 +6262,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6281,7 +6272,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6296,57 +6287,66 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126182185</v>
+        <v>126177821</v>
       </c>
       <c r="B53" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533637</v>
+        <v>533723</v>
       </c>
       <c r="R53" t="n">
-        <v>6928864</v>
+        <v>6928726</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6418,7 +6418,7 @@
         <v>126176512</v>
       </c>
       <c r="B54" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6522,57 +6522,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126175256</v>
+        <v>126182214</v>
       </c>
       <c r="B55" t="n">
-        <v>98339</v>
+        <v>78732</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533811</v>
+        <v>533640</v>
       </c>
       <c r="R55" t="n">
-        <v>6928689</v>
+        <v>6928855</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6601,7 +6592,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6611,7 +6602,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6626,22 +6617,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126182040</v>
+        <v>126181960</v>
       </c>
       <c r="B56" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6673,10 +6664,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533719</v>
+        <v>533769</v>
       </c>
       <c r="R56" t="n">
-        <v>6928884</v>
+        <v>6928852</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6708,7 +6699,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6718,7 +6709,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6745,10 +6736,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126181960</v>
+        <v>126182040</v>
       </c>
       <c r="B57" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6780,10 +6771,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533769</v>
+        <v>533719</v>
       </c>
       <c r="R57" t="n">
-        <v>6928852</v>
+        <v>6928884</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6815,7 +6806,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6825,7 +6816,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6852,48 +6843,57 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126182214</v>
+        <v>126175256</v>
       </c>
       <c r="B58" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533640</v>
+        <v>533811</v>
       </c>
       <c r="R58" t="n">
-        <v>6928855</v>
+        <v>6928689</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6947,69 +6947,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126178221</v>
+        <v>126182236</v>
       </c>
       <c r="B59" t="n">
-        <v>98339</v>
+        <v>78732</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533693</v>
+        <v>533635</v>
       </c>
       <c r="R59" t="n">
-        <v>6928759</v>
+        <v>6928840</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7038,7 +7029,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7048,7 +7039,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7063,60 +7054,69 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126182236</v>
+        <v>126178221</v>
       </c>
       <c r="B60" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533635</v>
+        <v>533693</v>
       </c>
       <c r="R60" t="n">
-        <v>6928840</v>
+        <v>6928759</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,12 +7170,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7185,7 +7185,7 @@
         <v>126182366</v>
       </c>
       <c r="B61" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7289,52 +7289,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126180477</v>
+        <v>126175788</v>
       </c>
       <c r="B62" t="n">
-        <v>98339</v>
+        <v>91530</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533673</v>
+        <v>533763</v>
       </c>
       <c r="R62" t="n">
-        <v>6928773</v>
+        <v>6928712</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7363,7 +7359,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7373,7 +7369,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7388,12 +7384,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7403,7 +7399,7 @@
         <v>126178007</v>
       </c>
       <c r="B63" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7507,48 +7503,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126175788</v>
+        <v>126180477</v>
       </c>
       <c r="B64" t="n">
-        <v>91528</v>
+        <v>98341</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533763</v>
+        <v>533673</v>
       </c>
       <c r="R64" t="n">
-        <v>6928712</v>
+        <v>6928773</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7602,12 +7602,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7617,7 +7617,7 @@
         <v>126176239</v>
       </c>
       <c r="B65" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7721,10 +7721,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126177726</v>
+        <v>126182142</v>
       </c>
       <c r="B66" t="n">
-        <v>80075</v>
+        <v>79591</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7732,21 +7732,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7756,13 +7756,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533723</v>
+        <v>533717</v>
       </c>
       <c r="R66" t="n">
-        <v>6928726</v>
+        <v>6928888</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7816,22 +7816,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126178312</v>
+        <v>126177726</v>
       </c>
       <c r="B67" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7839,21 +7839,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533708</v>
+        <v>533723</v>
       </c>
       <c r="R67" t="n">
-        <v>6928704</v>
+        <v>6928726</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7935,10 +7935,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126182142</v>
+        <v>126178312</v>
       </c>
       <c r="B68" t="n">
-        <v>79590</v>
+        <v>91234</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7946,21 +7946,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533717</v>
+        <v>533708</v>
       </c>
       <c r="R68" t="n">
-        <v>6928888</v>
+        <v>6928704</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8030,57 +8030,66 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126176685</v>
+        <v>126176659</v>
       </c>
       <c r="B69" t="n">
-        <v>91232</v>
+        <v>98341</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533743</v>
+        <v>533742</v>
       </c>
       <c r="R69" t="n">
-        <v>6928709</v>
+        <v>6928692</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8149,54 +8158,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126176659</v>
+        <v>126176685</v>
       </c>
       <c r="B70" t="n">
-        <v>98339</v>
+        <v>91234</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533742</v>
+        <v>533743</v>
       </c>
       <c r="R70" t="n">
-        <v>6928692</v>
+        <v>6928709</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8268,7 +8268,7 @@
         <v>126182129</v>
       </c>
       <c r="B71" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1465,48 +1465,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126182178</v>
+        <v>126176747</v>
       </c>
       <c r="B9" t="n">
-        <v>78732</v>
+        <v>98341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533652</v>
+        <v>533742</v>
       </c>
       <c r="R9" t="n">
-        <v>6928869</v>
+        <v>6928718</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1535,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,69 +1569,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126176747</v>
+        <v>126181693</v>
       </c>
       <c r="B10" t="n">
-        <v>98341</v>
+        <v>91234</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533742</v>
+        <v>533757</v>
       </c>
       <c r="R10" t="n">
-        <v>6928718</v>
+        <v>6928745</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,19 +1676,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126181693</v>
+        <v>126181209</v>
       </c>
       <c r="B11" t="n">
         <v>91234</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533757</v>
+        <v>533731</v>
       </c>
       <c r="R11" t="n">
-        <v>6928745</v>
+        <v>6928754</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126181209</v>
+        <v>126177259</v>
       </c>
       <c r="B12" t="n">
-        <v>91234</v>
+        <v>80076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,37 +1806,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533731</v>
+        <v>533735</v>
       </c>
       <c r="R12" t="n">
-        <v>6928754</v>
+        <v>6928726</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,62 +1895,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126177259</v>
+        <v>126182188</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>92524</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533735</v>
+        <v>533653</v>
       </c>
       <c r="R13" t="n">
-        <v>6928726</v>
+        <v>6928877</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,32 +2014,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126182188</v>
+        <v>126182178</v>
       </c>
       <c r="B14" t="n">
-        <v>92524</v>
+        <v>78732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533653</v>
+        <v>533652</v>
       </c>
       <c r="R14" t="n">
-        <v>6928877</v>
+        <v>6928869</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,12 +2109,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -5871,45 +5871,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126175215</v>
+        <v>126177821</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>98341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533811</v>
+        <v>533723</v>
       </c>
       <c r="R49" t="n">
-        <v>6928661</v>
+        <v>6928726</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5978,10 +5987,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126182185</v>
+        <v>126175215</v>
       </c>
       <c r="B50" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5989,21 +5998,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6013,10 +6022,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533637</v>
+        <v>533811</v>
       </c>
       <c r="R50" t="n">
-        <v>6928864</v>
+        <v>6928661</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6085,7 +6094,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126180415</v>
+        <v>126182185</v>
       </c>
       <c r="B51" t="n">
         <v>78732</v>
@@ -6120,13 +6129,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533678</v>
+        <v>533637</v>
       </c>
       <c r="R51" t="n">
-        <v>6928776</v>
+        <v>6928864</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6155,7 +6164,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6165,7 +6174,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6180,44 +6189,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126175432</v>
+        <v>126180415</v>
       </c>
       <c r="B52" t="n">
-        <v>80036</v>
+        <v>78732</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6227,13 +6236,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533782</v>
+        <v>533678</v>
       </c>
       <c r="R52" t="n">
-        <v>6928709</v>
+        <v>6928776</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6262,7 +6271,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6272,7 +6281,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6287,66 +6296,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126177821</v>
+        <v>126175432</v>
       </c>
       <c r="B53" t="n">
-        <v>98341</v>
+        <v>80036</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533723</v>
+        <v>533782</v>
       </c>
       <c r="R53" t="n">
-        <v>6928726</v>
+        <v>6928709</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6959,48 +6959,57 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126182236</v>
+        <v>126178221</v>
       </c>
       <c r="B59" t="n">
-        <v>78732</v>
+        <v>98341</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533635</v>
+        <v>533693</v>
       </c>
       <c r="R59" t="n">
-        <v>6928840</v>
+        <v>6928759</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7029,7 +7038,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7039,7 +7048,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7054,19 +7063,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126178221</v>
+        <v>126182366</v>
       </c>
       <c r="B60" t="n">
         <v>98341</v>
@@ -7094,29 +7103,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533693</v>
+        <v>533589</v>
       </c>
       <c r="R60" t="n">
-        <v>6928759</v>
+        <v>6928781</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,44 +7170,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126182366</v>
+        <v>126182236</v>
       </c>
       <c r="B61" t="n">
-        <v>98341</v>
+        <v>78732</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533589</v>
+        <v>533635</v>
       </c>
       <c r="R61" t="n">
-        <v>6928781</v>
+        <v>6928840</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8370,6 +8370,1629 @@
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126231107</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91201</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>533741</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6928704</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126231086</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98343</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>533679</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6928782</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126230916</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91532</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>658</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>533875</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6928695</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126230894</v>
+      </c>
+      <c r="B75" t="n">
+        <v>92526</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>533760</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6929925</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126230947</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91532</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>658</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>533714</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6928769</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126231026</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98343</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>533728</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6928772</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126230971</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98343</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>533801</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6928708</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126231185</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98377</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Käkbenet, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>533712</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6928777</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126231069</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98343</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>533711</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6928775</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126231127</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80076</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>533716</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6928739</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126231002</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98343</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge , Mpd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>533741</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6928734</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126230937</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91532</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>658</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>533736</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6928738</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126230989</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98343</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>533766</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6928714</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126230878</v>
+      </c>
+      <c r="B85" t="n">
+        <v>78640</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>353</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>533669</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6928742</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126231142</v>
+      </c>
+      <c r="B86" t="n">
+        <v>80076</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Käkbenet, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>533702</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6928773</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126231168</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91236</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Källberget, Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>533712</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6928777</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126178047</v>
+        <v>126178127</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533733</v>
+        <v>533723</v>
       </c>
       <c r="R2" t="n">
-        <v>6928740</v>
+        <v>6928747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,54 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126178127</v>
+        <v>126178047</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533723</v>
+        <v>533733</v>
       </c>
       <c r="R3" t="n">
-        <v>6928747</v>
+        <v>6928740</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
         <v>126176893</v>
       </c>
       <c r="B5" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>126180936</v>
       </c>
       <c r="B6" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,42 +1232,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126175525</v>
+        <v>126182207</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1276,13 +1272,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533774</v>
+        <v>533644</v>
       </c>
       <c r="R7" t="n">
-        <v>6928715</v>
+        <v>6928860</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1317,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,50 +1337,54 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126182207</v>
+        <v>126175525</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1388,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533644</v>
+        <v>533774</v>
       </c>
       <c r="R8" t="n">
-        <v>6928860</v>
+        <v>6928715</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1423,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1433,12 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,54 +1453,50 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126176747</v>
+        <v>126177259</v>
       </c>
       <c r="B9" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1509,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533742</v>
+        <v>533735</v>
       </c>
       <c r="R9" t="n">
-        <v>6928718</v>
+        <v>6928726</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,32 +1577,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126181693</v>
+        <v>126182188</v>
       </c>
       <c r="B10" t="n">
-        <v>91234</v>
+        <v>92526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,13 +1612,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533757</v>
+        <v>533653</v>
       </c>
       <c r="R10" t="n">
-        <v>6928745</v>
+        <v>6928877</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,7 +1647,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1657,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,12 +1672,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1691,7 +1687,7 @@
         <v>126181209</v>
       </c>
       <c r="B11" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,38 +1791,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126177259</v>
+        <v>126176747</v>
       </c>
       <c r="B12" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533735</v>
+        <v>533742</v>
       </c>
       <c r="R12" t="n">
-        <v>6928726</v>
+        <v>6928718</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,32 +1907,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126182188</v>
+        <v>126182178</v>
       </c>
       <c r="B13" t="n">
-        <v>92524</v>
+        <v>78732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533653</v>
+        <v>533652</v>
       </c>
       <c r="R13" t="n">
-        <v>6928877</v>
+        <v>6928869</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2002,22 +2002,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126182178</v>
+        <v>126181693</v>
       </c>
       <c r="B14" t="n">
-        <v>78732</v>
+        <v>91236</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533652</v>
+        <v>533757</v>
       </c>
       <c r="R14" t="n">
-        <v>6928869</v>
+        <v>6928745</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,7 +2124,7 @@
         <v>126180157</v>
       </c>
       <c r="B15" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>126182151</v>
       </c>
       <c r="B16" t="n">
-        <v>91395</v>
+        <v>91397</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>126178142</v>
       </c>
       <c r="B17" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>126180591</v>
       </c>
       <c r="B18" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>126176599</v>
       </c>
       <c r="B19" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>126177332</v>
       </c>
       <c r="B20" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>126181665</v>
       </c>
       <c r="B21" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,48 +2915,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126181048</v>
+        <v>126178109</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>98377</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533733</v>
+        <v>533718</v>
       </c>
       <c r="R22" t="n">
-        <v>6928745</v>
+        <v>6928766</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2985,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,12 +3004,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växer rikligt på två aspar och även en gran</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3015,57 +3019,66 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126176059</v>
+        <v>126178121</v>
       </c>
       <c r="B23" t="n">
-        <v>91808</v>
+        <v>98377</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>760</v>
+        <v>219874</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533746</v>
+        <v>533717</v>
       </c>
       <c r="R23" t="n">
-        <v>6928708</v>
+        <v>6928757</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3134,57 +3147,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126178109</v>
+        <v>126181048</v>
       </c>
       <c r="B24" t="n">
-        <v>98375</v>
+        <v>80076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533718</v>
+        <v>533733</v>
       </c>
       <c r="R24" t="n">
-        <v>6928766</v>
+        <v>6928745</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3213,7 +3217,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3223,7 +3227,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer rikligt på två aspar och även en gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3238,66 +3247,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126178121</v>
+        <v>126176059</v>
       </c>
       <c r="B25" t="n">
-        <v>98375</v>
+        <v>91810</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533717</v>
+        <v>533746</v>
       </c>
       <c r="R25" t="n">
-        <v>6928757</v>
+        <v>6928708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3366,48 +3366,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126181871</v>
+        <v>126175257</v>
       </c>
       <c r="B26" t="n">
-        <v>78732</v>
+        <v>98343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533757</v>
+        <v>533799</v>
       </c>
       <c r="R26" t="n">
-        <v>6928745</v>
+        <v>6928693</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3445,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3455,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,22 +3470,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126175257</v>
+        <v>126178017</v>
       </c>
       <c r="B27" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3503,7 +3512,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3517,10 +3526,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533799</v>
+        <v>533723</v>
       </c>
       <c r="R27" t="n">
-        <v>6928693</v>
+        <v>6928730</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3589,54 +3598,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126178017</v>
+        <v>126178155</v>
       </c>
       <c r="B28" t="n">
-        <v>98341</v>
+        <v>97227</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533723</v>
+        <v>533696</v>
       </c>
       <c r="R28" t="n">
-        <v>6928730</v>
+        <v>6928789</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126178155</v>
+        <v>126181871</v>
       </c>
       <c r="B29" t="n">
-        <v>97225</v>
+        <v>78732</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533696</v>
+        <v>533757</v>
       </c>
       <c r="R29" t="n">
-        <v>6928789</v>
+        <v>6928745</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,61 +3800,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126181494</v>
+        <v>126181652</v>
       </c>
       <c r="B30" t="n">
-        <v>98341</v>
+        <v>92526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533742</v>
+        <v>533745</v>
       </c>
       <c r="R30" t="n">
-        <v>6928730</v>
+        <v>6928735</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3886,7 +3882,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3896,7 +3892,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3923,10 +3919,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126176544</v>
+        <v>126176144</v>
       </c>
       <c r="B31" t="n">
-        <v>91530</v>
+        <v>80076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,21 +3930,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3958,10 +3954,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533762</v>
+        <v>533746</v>
       </c>
       <c r="R31" t="n">
-        <v>6928704</v>
+        <v>6928708</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4030,10 +4026,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126176144</v>
+        <v>126176544</v>
       </c>
       <c r="B32" t="n">
-        <v>80076</v>
+        <v>91532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4041,21 +4037,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4065,10 +4061,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533746</v>
+        <v>533762</v>
       </c>
       <c r="R32" t="n">
-        <v>6928708</v>
+        <v>6928704</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4137,45 +4133,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126181652</v>
+        <v>126181494</v>
       </c>
       <c r="B33" t="n">
-        <v>92524</v>
+        <v>98343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533745</v>
+        <v>533742</v>
       </c>
       <c r="R33" t="n">
-        <v>6928735</v>
+        <v>6928730</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4247,7 +4247,7 @@
         <v>126181681</v>
       </c>
       <c r="B34" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>126180980</v>
       </c>
       <c r="B35" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4462,45 +4462,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126177002</v>
+        <v>126175252</v>
       </c>
       <c r="B36" t="n">
-        <v>78732</v>
+        <v>98343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533732</v>
+        <v>533816</v>
       </c>
       <c r="R36" t="n">
-        <v>6928727</v>
+        <v>6928686</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4569,32 +4578,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126178181</v>
+        <v>126177002</v>
       </c>
       <c r="B37" t="n">
-        <v>80036</v>
+        <v>78732</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4604,10 +4613,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533723</v>
+        <v>533732</v>
       </c>
       <c r="R37" t="n">
-        <v>6928739</v>
+        <v>6928727</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4676,54 +4685,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126175252</v>
+        <v>126178181</v>
       </c>
       <c r="B38" t="n">
-        <v>98341</v>
+        <v>80036</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533816</v>
+        <v>533723</v>
       </c>
       <c r="R38" t="n">
-        <v>6928686</v>
+        <v>6928739</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126175291</v>
+        <v>126180836</v>
       </c>
       <c r="B39" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4803,21 +4803,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533791</v>
+        <v>533708</v>
       </c>
       <c r="R39" t="n">
-        <v>6928687</v>
+        <v>6928798</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4887,22 +4887,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126180836</v>
+        <v>126175291</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4934,13 +4934,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533708</v>
+        <v>533791</v>
       </c>
       <c r="R40" t="n">
-        <v>6928798</v>
+        <v>6928687</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4994,12 +4994,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5009,7 +5009,7 @@
         <v>126182027</v>
       </c>
       <c r="B41" t="n">
-        <v>91156</v>
+        <v>91158</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>126177654</v>
       </c>
       <c r="B42" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5220,57 +5220,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126175980</v>
+        <v>126181218</v>
       </c>
       <c r="B43" t="n">
-        <v>98341</v>
+        <v>91532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533762</v>
+        <v>533723</v>
       </c>
       <c r="R43" t="n">
-        <v>6928707</v>
+        <v>6928740</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5299,7 +5290,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5309,7 +5300,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5324,44 +5315,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126182221</v>
+        <v>126176695</v>
       </c>
       <c r="B44" t="n">
-        <v>92524</v>
+        <v>91532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5371,13 +5362,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533640</v>
+        <v>533734</v>
       </c>
       <c r="R44" t="n">
-        <v>6928856</v>
+        <v>6928700</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5406,7 +5397,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5416,7 +5407,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5431,22 +5422,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126176695</v>
+        <v>126179959</v>
       </c>
       <c r="B45" t="n">
-        <v>91530</v>
+        <v>78732</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5454,21 +5445,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5478,13 +5469,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533734</v>
+        <v>533620</v>
       </c>
       <c r="R45" t="n">
-        <v>6928700</v>
+        <v>6928771</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5513,7 +5504,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5523,7 +5514,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5538,12 +5529,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5553,7 +5544,7 @@
         <v>126182304</v>
       </c>
       <c r="B46" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5657,32 +5648,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126181218</v>
+        <v>126182221</v>
       </c>
       <c r="B47" t="n">
-        <v>91530</v>
+        <v>92526</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5692,10 +5683,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533723</v>
+        <v>533640</v>
       </c>
       <c r="R47" t="n">
-        <v>6928740</v>
+        <v>6928856</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5727,7 +5718,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5737,7 +5728,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5764,48 +5755,57 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126179959</v>
+        <v>126175980</v>
       </c>
       <c r="B48" t="n">
-        <v>78732</v>
+        <v>98343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533620</v>
+        <v>533762</v>
       </c>
       <c r="R48" t="n">
-        <v>6928771</v>
+        <v>6928707</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5859,12 +5859,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5874,7 +5874,7 @@
         <v>126177821</v>
       </c>
       <c r="B49" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5987,10 +5987,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126175215</v>
+        <v>126182185</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5998,21 +5998,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533811</v>
+        <v>533637</v>
       </c>
       <c r="R50" t="n">
-        <v>6928661</v>
+        <v>6928864</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6094,7 +6094,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126182185</v>
+        <v>126180415</v>
       </c>
       <c r="B51" t="n">
         <v>78732</v>
@@ -6129,13 +6129,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533637</v>
+        <v>533678</v>
       </c>
       <c r="R51" t="n">
-        <v>6928864</v>
+        <v>6928776</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6189,44 +6189,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126180415</v>
+        <v>126175432</v>
       </c>
       <c r="B52" t="n">
-        <v>78732</v>
+        <v>80036</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6236,13 +6236,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533678</v>
+        <v>533782</v>
       </c>
       <c r="R52" t="n">
-        <v>6928776</v>
+        <v>6928709</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6296,44 +6296,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126175432</v>
+        <v>126175215</v>
       </c>
       <c r="B53" t="n">
-        <v>80036</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533782</v>
+        <v>533811</v>
       </c>
       <c r="R53" t="n">
-        <v>6928709</v>
+        <v>6928661</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6418,7 +6418,7 @@
         <v>126176512</v>
       </c>
       <c r="B54" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>126175256</v>
       </c>
       <c r="B58" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>126178221</v>
       </c>
       <c r="B59" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>126182366</v>
       </c>
       <c r="B60" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126175788</v>
+        <v>126178007</v>
       </c>
       <c r="B62" t="n">
-        <v>91530</v>
+        <v>91236</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7300,21 +7300,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533763</v>
+        <v>533723</v>
       </c>
       <c r="R62" t="n">
-        <v>6928712</v>
+        <v>6928730</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7396,10 +7396,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126178007</v>
+        <v>126175788</v>
       </c>
       <c r="B63" t="n">
-        <v>91234</v>
+        <v>91532</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533723</v>
+        <v>533763</v>
       </c>
       <c r="R63" t="n">
-        <v>6928730</v>
+        <v>6928712</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7506,7 +7506,7 @@
         <v>126180477</v>
       </c>
       <c r="B64" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7614,32 +7614,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126176239</v>
+        <v>126177726</v>
       </c>
       <c r="B65" t="n">
-        <v>80112</v>
+        <v>80076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533761</v>
+        <v>533723</v>
       </c>
       <c r="R65" t="n">
-        <v>6928713</v>
+        <v>6928726</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7721,32 +7721,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126182142</v>
+        <v>126176239</v>
       </c>
       <c r="B66" t="n">
-        <v>79591</v>
+        <v>80112</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7756,13 +7756,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533717</v>
+        <v>533761</v>
       </c>
       <c r="R66" t="n">
-        <v>6928888</v>
+        <v>6928713</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7816,22 +7816,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126177726</v>
+        <v>126178312</v>
       </c>
       <c r="B67" t="n">
-        <v>80076</v>
+        <v>91236</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7839,21 +7839,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533723</v>
+        <v>533708</v>
       </c>
       <c r="R67" t="n">
-        <v>6928726</v>
+        <v>6928704</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7935,10 +7935,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126178312</v>
+        <v>126182142</v>
       </c>
       <c r="B68" t="n">
-        <v>91234</v>
+        <v>79591</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7946,21 +7946,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533708</v>
+        <v>533717</v>
       </c>
       <c r="R68" t="n">
-        <v>6928704</v>
+        <v>6928888</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8030,69 +8030,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126176659</v>
+        <v>126182129</v>
       </c>
       <c r="B69" t="n">
-        <v>98341</v>
+        <v>92526</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533742</v>
+        <v>533717</v>
       </c>
       <c r="R69" t="n">
-        <v>6928692</v>
+        <v>6928888</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8121,7 +8112,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8131,7 +8122,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8146,12 +8137,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8161,7 +8152,7 @@
         <v>126176685</v>
       </c>
       <c r="B70" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8265,48 +8256,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126182129</v>
+        <v>126176659</v>
       </c>
       <c r="B71" t="n">
-        <v>92524</v>
+        <v>98343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533717</v>
+        <v>533742</v>
       </c>
       <c r="R71" t="n">
-        <v>6928888</v>
+        <v>6928692</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8360,12 +8360,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8575,32 +8575,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126230916</v>
+        <v>126230894</v>
       </c>
       <c r="B74" t="n">
-        <v>91532</v>
+        <v>92526</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8613,10 +8613,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533875</v>
+        <v>533760</v>
       </c>
       <c r="R74" t="n">
-        <v>6928695</v>
+        <v>6929925</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126230894</v>
+        <v>126230916</v>
       </c>
       <c r="B75" t="n">
-        <v>92526</v>
+        <v>91532</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533760</v>
+        <v>533875</v>
       </c>
       <c r="R75" t="n">
-        <v>6929925</v>
+        <v>6928695</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9387,49 +9387,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126231002</v>
+        <v>126230937</v>
       </c>
       <c r="B82" t="n">
-        <v>98343</v>
+        <v>91532</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Källberget, Ånge , Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533741</v>
+        <v>533736</v>
       </c>
       <c r="R82" t="n">
-        <v>6928734</v>
+        <v>6928738</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9489,48 +9488,49 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126230937</v>
+        <v>126231002</v>
       </c>
       <c r="B83" t="n">
-        <v>91532</v>
+        <v>98343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Källberget, Ånge , Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533736</v>
+        <v>533741</v>
       </c>
       <c r="R83" t="n">
-        <v>6928738</v>
+        <v>6928734</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9793,10 +9793,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126231142</v>
+        <v>126231168</v>
       </c>
       <c r="B86" t="n">
-        <v>80076</v>
+        <v>91236</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9804,21 +9804,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9827,14 +9827,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Käkbenet, Ånge, Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533702</v>
+        <v>533712</v>
       </c>
       <c r="R86" t="n">
-        <v>6928773</v>
+        <v>6928777</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126231168</v>
+        <v>126231142</v>
       </c>
       <c r="B87" t="n">
-        <v>91236</v>
+        <v>80076</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9928,14 +9928,14 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Käkbenet, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533712</v>
+        <v>533702</v>
       </c>
       <c r="R87" t="n">
-        <v>6928777</v>
+        <v>6928773</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -3812,32 +3812,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126181652</v>
+        <v>126176544</v>
       </c>
       <c r="B30" t="n">
-        <v>92526</v>
+        <v>91532</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533745</v>
+        <v>533762</v>
       </c>
       <c r="R30" t="n">
-        <v>6928735</v>
+        <v>6928704</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3907,44 +3907,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126176144</v>
+        <v>126181652</v>
       </c>
       <c r="B31" t="n">
-        <v>80076</v>
+        <v>92526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533746</v>
+        <v>533745</v>
       </c>
       <c r="R31" t="n">
-        <v>6928708</v>
+        <v>6928735</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4014,22 +4014,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126176544</v>
+        <v>126176144</v>
       </c>
       <c r="B32" t="n">
-        <v>91532</v>
+        <v>80076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533762</v>
+        <v>533746</v>
       </c>
       <c r="R32" t="n">
-        <v>6928704</v>
+        <v>6928708</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4244,45 +4244,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126181681</v>
+        <v>126180980</v>
       </c>
       <c r="B34" t="n">
-        <v>91532</v>
+        <v>98377</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533745</v>
+        <v>533724</v>
       </c>
       <c r="R34" t="n">
-        <v>6928735</v>
+        <v>6928748</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4314,7 +4318,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4324,7 +4328,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,37 +4355,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126180980</v>
+        <v>126175252</v>
       </c>
       <c r="B35" t="n">
-        <v>98377</v>
+        <v>98343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4390,13 +4399,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533724</v>
+        <v>533816</v>
       </c>
       <c r="R35" t="n">
-        <v>6928748</v>
+        <v>6928686</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4425,7 +4434,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4435,7 +4444,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4450,66 +4459,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126175252</v>
+        <v>126177002</v>
       </c>
       <c r="B36" t="n">
-        <v>98343</v>
+        <v>78732</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533816</v>
+        <v>533732</v>
       </c>
       <c r="R36" t="n">
-        <v>6928686</v>
+        <v>6928727</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4578,32 +4578,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126177002</v>
+        <v>126178181</v>
       </c>
       <c r="B37" t="n">
-        <v>78732</v>
+        <v>80036</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533732</v>
+        <v>533723</v>
       </c>
       <c r="R37" t="n">
-        <v>6928727</v>
+        <v>6928739</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4685,32 +4685,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126178181</v>
+        <v>126181681</v>
       </c>
       <c r="B38" t="n">
-        <v>80036</v>
+        <v>91532</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,13 +4720,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533723</v>
+        <v>533745</v>
       </c>
       <c r="R38" t="n">
-        <v>6928739</v>
+        <v>6928735</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4780,12 +4780,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5220,32 +5220,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126181218</v>
+        <v>126182304</v>
       </c>
       <c r="B43" t="n">
-        <v>91532</v>
+        <v>92526</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533723</v>
+        <v>533624</v>
       </c>
       <c r="R43" t="n">
-        <v>6928740</v>
+        <v>6928837</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5327,32 +5327,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126176695</v>
+        <v>126182221</v>
       </c>
       <c r="B44" t="n">
-        <v>91532</v>
+        <v>92526</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533734</v>
+        <v>533640</v>
       </c>
       <c r="R44" t="n">
-        <v>6928700</v>
+        <v>6928856</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5422,22 +5422,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126179959</v>
+        <v>126181218</v>
       </c>
       <c r="B45" t="n">
-        <v>78732</v>
+        <v>91532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5445,21 +5445,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533620</v>
+        <v>533723</v>
       </c>
       <c r="R45" t="n">
-        <v>6928771</v>
+        <v>6928740</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5541,32 +5541,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126182304</v>
+        <v>126176695</v>
       </c>
       <c r="B46" t="n">
-        <v>92526</v>
+        <v>91532</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5576,13 +5576,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533624</v>
+        <v>533734</v>
       </c>
       <c r="R46" t="n">
-        <v>6928837</v>
+        <v>6928700</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5636,60 +5636,69 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126182221</v>
+        <v>126175980</v>
       </c>
       <c r="B47" t="n">
-        <v>92526</v>
+        <v>98343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533640</v>
+        <v>533762</v>
       </c>
       <c r="R47" t="n">
-        <v>6928856</v>
+        <v>6928707</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5718,7 +5727,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5728,7 +5737,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5743,69 +5752,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126175980</v>
+        <v>126179959</v>
       </c>
       <c r="B48" t="n">
-        <v>98343</v>
+        <v>78732</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533762</v>
+        <v>533620</v>
       </c>
       <c r="R48" t="n">
-        <v>6928707</v>
+        <v>6928771</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5859,12 +5859,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6959,57 +6959,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126178221</v>
+        <v>126182236</v>
       </c>
       <c r="B59" t="n">
-        <v>98343</v>
+        <v>78732</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533693</v>
+        <v>533635</v>
       </c>
       <c r="R59" t="n">
-        <v>6928759</v>
+        <v>6928840</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7038,7 +7029,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7048,7 +7039,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7063,19 +7054,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126182366</v>
+        <v>126178221</v>
       </c>
       <c r="B60" t="n">
         <v>98343</v>
@@ -7103,20 +7094,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533589</v>
+        <v>533693</v>
       </c>
       <c r="R60" t="n">
-        <v>6928781</v>
+        <v>6928759</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,44 +7170,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126182236</v>
+        <v>126182366</v>
       </c>
       <c r="B61" t="n">
-        <v>78732</v>
+        <v>98343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533635</v>
+        <v>533589</v>
       </c>
       <c r="R61" t="n">
-        <v>6928840</v>
+        <v>6928781</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7828,10 +7828,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126178312</v>
+        <v>126182142</v>
       </c>
       <c r="B67" t="n">
-        <v>91236</v>
+        <v>79591</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7839,21 +7839,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7863,13 +7863,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533708</v>
+        <v>533717</v>
       </c>
       <c r="R67" t="n">
-        <v>6928704</v>
+        <v>6928888</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7923,22 +7923,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126182142</v>
+        <v>126178312</v>
       </c>
       <c r="B68" t="n">
-        <v>79591</v>
+        <v>91236</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7946,21 +7946,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533717</v>
+        <v>533708</v>
       </c>
       <c r="R68" t="n">
-        <v>6928888</v>
+        <v>6928704</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8030,12 +8030,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8575,32 +8575,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126230894</v>
+        <v>126230916</v>
       </c>
       <c r="B74" t="n">
-        <v>92526</v>
+        <v>91532</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8613,10 +8613,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533760</v>
+        <v>533875</v>
       </c>
       <c r="R74" t="n">
-        <v>6929925</v>
+        <v>6928695</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126230916</v>
+        <v>126230894</v>
       </c>
       <c r="B75" t="n">
-        <v>91532</v>
+        <v>92526</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533875</v>
+        <v>533760</v>
       </c>
       <c r="R75" t="n">
-        <v>6928695</v>
+        <v>6929925</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126178127</v>
+        <v>126178047</v>
       </c>
       <c r="B2" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533723</v>
+        <v>533733</v>
       </c>
       <c r="R2" t="n">
-        <v>6928747</v>
+        <v>6928740</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126178047</v>
+        <v>126178127</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533733</v>
+        <v>533723</v>
       </c>
       <c r="R3" t="n">
-        <v>6928740</v>
+        <v>6928747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
         <v>126176893</v>
       </c>
       <c r="B5" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>126180936</v>
       </c>
       <c r="B6" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,38 +1232,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126182207</v>
+        <v>126175525</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1272,13 +1276,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533644</v>
+        <v>533774</v>
       </c>
       <c r="R7" t="n">
-        <v>6928860</v>
+        <v>6928715</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,12 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,54 +1336,50 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126175525</v>
+        <v>126182207</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1393,13 +1388,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533774</v>
+        <v>533644</v>
       </c>
       <c r="R8" t="n">
-        <v>6928715</v>
+        <v>6928860</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1433,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,12 +1453,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1577,32 +1577,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126182188</v>
+        <v>126181693</v>
       </c>
       <c r="B10" t="n">
-        <v>92526</v>
+        <v>91238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1612,13 +1612,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533653</v>
+        <v>533757</v>
       </c>
       <c r="R10" t="n">
-        <v>6928877</v>
+        <v>6928745</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,12 +1672,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1687,7 +1687,7 @@
         <v>126181209</v>
       </c>
       <c r="B11" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,54 +1791,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126176747</v>
+        <v>126182188</v>
       </c>
       <c r="B12" t="n">
-        <v>98343</v>
+        <v>92528</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533742</v>
+        <v>533653</v>
       </c>
       <c r="R12" t="n">
-        <v>6928718</v>
+        <v>6928877</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,48 +1898,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126182178</v>
+        <v>126176747</v>
       </c>
       <c r="B13" t="n">
-        <v>78732</v>
+        <v>98345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533652</v>
+        <v>533742</v>
       </c>
       <c r="R13" t="n">
-        <v>6928869</v>
+        <v>6928718</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2002,22 +2002,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126181693</v>
+        <v>126182178</v>
       </c>
       <c r="B14" t="n">
-        <v>91236</v>
+        <v>78732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533757</v>
+        <v>533652</v>
       </c>
       <c r="R14" t="n">
-        <v>6928745</v>
+        <v>6928869</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,7 +2124,7 @@
         <v>126180157</v>
       </c>
       <c r="B15" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>126182151</v>
       </c>
       <c r="B16" t="n">
-        <v>91397</v>
+        <v>91399</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>126178142</v>
       </c>
       <c r="B17" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>126180591</v>
       </c>
       <c r="B18" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>126176599</v>
       </c>
       <c r="B19" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>126177332</v>
       </c>
       <c r="B20" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>126181665</v>
       </c>
       <c r="B21" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,57 +2915,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126178109</v>
+        <v>126181048</v>
       </c>
       <c r="B22" t="n">
-        <v>98377</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533718</v>
+        <v>533733</v>
       </c>
       <c r="R22" t="n">
-        <v>6928766</v>
+        <v>6928745</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2994,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,7 +2995,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer rikligt på två aspar och även en gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3019,66 +3015,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126178121</v>
+        <v>126176059</v>
       </c>
       <c r="B23" t="n">
-        <v>98377</v>
+        <v>91812</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219874</v>
+        <v>760</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533717</v>
+        <v>533746</v>
       </c>
       <c r="R23" t="n">
-        <v>6928757</v>
+        <v>6928708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3147,48 +3134,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126181048</v>
+        <v>126178109</v>
       </c>
       <c r="B24" t="n">
-        <v>80076</v>
+        <v>98379</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533733</v>
+        <v>533718</v>
       </c>
       <c r="R24" t="n">
-        <v>6928745</v>
+        <v>6928766</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3217,7 +3213,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3227,12 +3223,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växer rikligt på två aspar och även en gran</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3247,57 +3238,66 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126176059</v>
+        <v>126178121</v>
       </c>
       <c r="B25" t="n">
-        <v>91810</v>
+        <v>98379</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533746</v>
+        <v>533717</v>
       </c>
       <c r="R25" t="n">
-        <v>6928708</v>
+        <v>6928757</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3366,57 +3366,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126175257</v>
+        <v>126181871</v>
       </c>
       <c r="B26" t="n">
-        <v>98343</v>
+        <v>78732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533799</v>
+        <v>533757</v>
       </c>
       <c r="R26" t="n">
-        <v>6928693</v>
+        <v>6928745</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3445,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3470,22 +3461,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126178017</v>
+        <v>126175257</v>
       </c>
       <c r="B27" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3512,7 +3503,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3526,10 +3517,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533723</v>
+        <v>533799</v>
       </c>
       <c r="R27" t="n">
-        <v>6928730</v>
+        <v>6928693</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3598,45 +3589,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126178155</v>
+        <v>126178017</v>
       </c>
       <c r="B28" t="n">
-        <v>97227</v>
+        <v>98345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533696</v>
+        <v>533723</v>
       </c>
       <c r="R28" t="n">
-        <v>6928789</v>
+        <v>6928730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126181871</v>
+        <v>126178155</v>
       </c>
       <c r="B29" t="n">
-        <v>78732</v>
+        <v>97229</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533757</v>
+        <v>533696</v>
       </c>
       <c r="R29" t="n">
-        <v>6928745</v>
+        <v>6928789</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,22 +3800,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126176544</v>
+        <v>126176144</v>
       </c>
       <c r="B30" t="n">
-        <v>91532</v>
+        <v>80076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533762</v>
+        <v>533746</v>
       </c>
       <c r="R30" t="n">
-        <v>6928704</v>
+        <v>6928708</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3919,32 +3919,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126181652</v>
+        <v>126176544</v>
       </c>
       <c r="B31" t="n">
-        <v>92526</v>
+        <v>91534</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533745</v>
+        <v>533762</v>
       </c>
       <c r="R31" t="n">
-        <v>6928735</v>
+        <v>6928704</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4014,60 +4014,64 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126176144</v>
+        <v>126181494</v>
       </c>
       <c r="B32" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533746</v>
+        <v>533742</v>
       </c>
       <c r="R32" t="n">
-        <v>6928708</v>
+        <v>6928730</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4096,7 +4100,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4106,7 +4110,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4121,61 +4125,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126181494</v>
+        <v>126181652</v>
       </c>
       <c r="B33" t="n">
-        <v>98343</v>
+        <v>92528</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533742</v>
+        <v>533745</v>
       </c>
       <c r="R33" t="n">
-        <v>6928730</v>
+        <v>6928735</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4244,49 +4244,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126180980</v>
+        <v>126181681</v>
       </c>
       <c r="B34" t="n">
-        <v>98377</v>
+        <v>91534</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219874</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533724</v>
+        <v>533745</v>
       </c>
       <c r="R34" t="n">
-        <v>6928748</v>
+        <v>6928735</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4318,7 +4314,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4328,7 +4324,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4355,42 +4351,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126175252</v>
+        <v>126180980</v>
       </c>
       <c r="B35" t="n">
-        <v>98343</v>
+        <v>98379</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4399,13 +4390,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533816</v>
+        <v>533724</v>
       </c>
       <c r="R35" t="n">
-        <v>6928686</v>
+        <v>6928748</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4434,7 +4425,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4444,7 +4435,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4459,57 +4450,66 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126177002</v>
+        <v>126175252</v>
       </c>
       <c r="B36" t="n">
-        <v>78732</v>
+        <v>98345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533732</v>
+        <v>533816</v>
       </c>
       <c r="R36" t="n">
-        <v>6928727</v>
+        <v>6928686</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4685,10 +4685,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126181681</v>
+        <v>126177002</v>
       </c>
       <c r="B38" t="n">
-        <v>91532</v>
+        <v>78732</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4696,21 +4696,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,13 +4720,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533745</v>
+        <v>533732</v>
       </c>
       <c r="R38" t="n">
-        <v>6928735</v>
+        <v>6928727</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4780,22 +4780,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126180836</v>
+        <v>126182027</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>91160</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4803,21 +4803,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533708</v>
+        <v>533755</v>
       </c>
       <c r="R39" t="n">
-        <v>6928798</v>
+        <v>6928865</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4887,12 +4887,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126182027</v>
+        <v>126180836</v>
       </c>
       <c r="B41" t="n">
-        <v>91158</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5041,13 +5041,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533755</v>
+        <v>533708</v>
       </c>
       <c r="R41" t="n">
-        <v>6928865</v>
+        <v>6928798</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5101,12 +5101,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5116,7 +5116,7 @@
         <v>126177654</v>
       </c>
       <c r="B42" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5220,32 +5220,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126182304</v>
+        <v>126176695</v>
       </c>
       <c r="B43" t="n">
-        <v>92526</v>
+        <v>91534</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5255,13 +5255,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533624</v>
+        <v>533734</v>
       </c>
       <c r="R43" t="n">
-        <v>6928837</v>
+        <v>6928700</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5315,44 +5315,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126182221</v>
+        <v>126181218</v>
       </c>
       <c r="B44" t="n">
-        <v>92526</v>
+        <v>91534</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533640</v>
+        <v>533723</v>
       </c>
       <c r="R44" t="n">
-        <v>6928856</v>
+        <v>6928740</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5434,32 +5434,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126181218</v>
+        <v>126182304</v>
       </c>
       <c r="B45" t="n">
-        <v>91532</v>
+        <v>92528</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533723</v>
+        <v>533624</v>
       </c>
       <c r="R45" t="n">
-        <v>6928740</v>
+        <v>6928837</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5541,32 +5541,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126176695</v>
+        <v>126182221</v>
       </c>
       <c r="B46" t="n">
-        <v>91532</v>
+        <v>92528</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5576,13 +5576,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533734</v>
+        <v>533640</v>
       </c>
       <c r="R46" t="n">
-        <v>6928700</v>
+        <v>6928856</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5636,69 +5636,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126175980</v>
+        <v>126179959</v>
       </c>
       <c r="B47" t="n">
-        <v>98343</v>
+        <v>78732</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533762</v>
+        <v>533620</v>
       </c>
       <c r="R47" t="n">
-        <v>6928707</v>
+        <v>6928771</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5727,7 +5718,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5737,7 +5728,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5752,60 +5743,69 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126179959</v>
+        <v>126175980</v>
       </c>
       <c r="B48" t="n">
-        <v>78732</v>
+        <v>98345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533620</v>
+        <v>533762</v>
       </c>
       <c r="R48" t="n">
-        <v>6928771</v>
+        <v>6928707</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5859,12 +5859,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5874,7 +5874,7 @@
         <v>126177821</v>
       </c>
       <c r="B49" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>126176512</v>
       </c>
       <c r="B54" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>126175256</v>
       </c>
       <c r="B58" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6959,48 +6959,57 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126182236</v>
+        <v>126178221</v>
       </c>
       <c r="B59" t="n">
-        <v>78732</v>
+        <v>98345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533635</v>
+        <v>533693</v>
       </c>
       <c r="R59" t="n">
-        <v>6928840</v>
+        <v>6928759</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7029,7 +7038,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7039,7 +7048,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7054,22 +7063,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126178221</v>
+        <v>126182366</v>
       </c>
       <c r="B60" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7094,29 +7103,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533693</v>
+        <v>533589</v>
       </c>
       <c r="R60" t="n">
-        <v>6928759</v>
+        <v>6928781</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,44 +7170,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126182366</v>
+        <v>126182236</v>
       </c>
       <c r="B61" t="n">
-        <v>98343</v>
+        <v>78732</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533589</v>
+        <v>533635</v>
       </c>
       <c r="R61" t="n">
-        <v>6928781</v>
+        <v>6928840</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7289,10 +7289,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126178007</v>
+        <v>126175788</v>
       </c>
       <c r="B62" t="n">
-        <v>91236</v>
+        <v>91534</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7300,21 +7300,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533723</v>
+        <v>533763</v>
       </c>
       <c r="R62" t="n">
-        <v>6928730</v>
+        <v>6928712</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7396,10 +7396,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126175788</v>
+        <v>126178007</v>
       </c>
       <c r="B63" t="n">
-        <v>91532</v>
+        <v>91238</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533763</v>
+        <v>533723</v>
       </c>
       <c r="R63" t="n">
-        <v>6928712</v>
+        <v>6928730</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7506,7 +7506,7 @@
         <v>126180477</v>
       </c>
       <c r="B64" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7614,32 +7614,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126177726</v>
+        <v>126176239</v>
       </c>
       <c r="B65" t="n">
-        <v>80076</v>
+        <v>80112</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533723</v>
+        <v>533761</v>
       </c>
       <c r="R65" t="n">
-        <v>6928726</v>
+        <v>6928713</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7721,32 +7721,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126176239</v>
+        <v>126182142</v>
       </c>
       <c r="B66" t="n">
-        <v>80112</v>
+        <v>79591</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7756,13 +7756,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533761</v>
+        <v>533717</v>
       </c>
       <c r="R66" t="n">
-        <v>6928713</v>
+        <v>6928888</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7816,22 +7816,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126182142</v>
+        <v>126177726</v>
       </c>
       <c r="B67" t="n">
-        <v>79591</v>
+        <v>80076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7839,21 +7839,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7863,13 +7863,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533717</v>
+        <v>533723</v>
       </c>
       <c r="R67" t="n">
-        <v>6928888</v>
+        <v>6928726</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7923,12 +7923,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7938,7 +7938,7 @@
         <v>126178312</v>
       </c>
       <c r="B68" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>126182129</v>
       </c>
       <c r="B69" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>126176685</v>
       </c>
       <c r="B70" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>126176659</v>
       </c>
       <c r="B71" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8372,37 +8372,38 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126231107</v>
+        <v>126231086</v>
       </c>
       <c r="B72" t="n">
-        <v>91201</v>
+        <v>98345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8410,10 +8411,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533741</v>
+        <v>533679</v>
       </c>
       <c r="R72" t="n">
-        <v>6928704</v>
+        <v>6928782</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8473,38 +8474,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126231086</v>
+        <v>126231107</v>
       </c>
       <c r="B73" t="n">
-        <v>98343</v>
+        <v>91203</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8512,10 +8512,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533679</v>
+        <v>533741</v>
       </c>
       <c r="R73" t="n">
-        <v>6928782</v>
+        <v>6928704</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8578,7 +8578,7 @@
         <v>126230916</v>
       </c>
       <c r="B74" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>126230894</v>
       </c>
       <c r="B75" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>126230947</v>
       </c>
       <c r="B76" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>126231026</v>
       </c>
       <c r="B77" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>126230971</v>
       </c>
       <c r="B78" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>126231185</v>
       </c>
       <c r="B79" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>126231069</v>
       </c>
       <c r="B80" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>126230937</v>
       </c>
       <c r="B82" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>126231002</v>
       </c>
       <c r="B83" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>126230989</v>
       </c>
       <c r="B84" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9793,10 +9793,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126231168</v>
+        <v>126231142</v>
       </c>
       <c r="B86" t="n">
-        <v>91236</v>
+        <v>80076</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9804,21 +9804,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9827,14 +9827,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Käkbenet, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533712</v>
+        <v>533702</v>
       </c>
       <c r="R86" t="n">
-        <v>6928777</v>
+        <v>6928773</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126231142</v>
+        <v>126231168</v>
       </c>
       <c r="B87" t="n">
-        <v>80076</v>
+        <v>91238</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9928,14 +9928,14 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Käkbenet, Ånge, Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533702</v>
+        <v>533712</v>
       </c>
       <c r="R87" t="n">
-        <v>6928773</v>
+        <v>6928777</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -4244,45 +4244,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126181681</v>
+        <v>126180980</v>
       </c>
       <c r="B34" t="n">
-        <v>91534</v>
+        <v>98379</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533745</v>
+        <v>533724</v>
       </c>
       <c r="R34" t="n">
-        <v>6928735</v>
+        <v>6928748</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4314,7 +4318,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4324,7 +4328,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,37 +4355,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126180980</v>
+        <v>126175252</v>
       </c>
       <c r="B35" t="n">
-        <v>98379</v>
+        <v>98345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4390,13 +4399,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533724</v>
+        <v>533816</v>
       </c>
       <c r="R35" t="n">
-        <v>6928748</v>
+        <v>6928686</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4425,7 +4434,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4435,7 +4444,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4450,66 +4459,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126175252</v>
+        <v>126178181</v>
       </c>
       <c r="B36" t="n">
-        <v>98345</v>
+        <v>80036</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533816</v>
+        <v>533723</v>
       </c>
       <c r="R36" t="n">
-        <v>6928686</v>
+        <v>6928739</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4578,32 +4578,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126178181</v>
+        <v>126177002</v>
       </c>
       <c r="B37" t="n">
-        <v>80036</v>
+        <v>78732</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533723</v>
+        <v>533732</v>
       </c>
       <c r="R37" t="n">
-        <v>6928739</v>
+        <v>6928727</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4685,10 +4685,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126177002</v>
+        <v>126181681</v>
       </c>
       <c r="B38" t="n">
-        <v>78732</v>
+        <v>91534</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4696,21 +4696,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,13 +4720,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533732</v>
+        <v>533745</v>
       </c>
       <c r="R38" t="n">
-        <v>6928727</v>
+        <v>6928735</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4780,22 +4780,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126182027</v>
+        <v>126175291</v>
       </c>
       <c r="B39" t="n">
-        <v>91160</v>
+        <v>80076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4803,21 +4803,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3242</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533755</v>
+        <v>533791</v>
       </c>
       <c r="R39" t="n">
-        <v>6928865</v>
+        <v>6928687</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126175291</v>
+        <v>126180836</v>
       </c>
       <c r="B40" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4934,13 +4934,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533791</v>
+        <v>533708</v>
       </c>
       <c r="R40" t="n">
-        <v>6928687</v>
+        <v>6928798</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4994,22 +4994,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126180836</v>
+        <v>126182027</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>91160</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5041,13 +5041,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533708</v>
+        <v>533755</v>
       </c>
       <c r="R41" t="n">
-        <v>6928798</v>
+        <v>6928865</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5101,12 +5101,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5220,45 +5220,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126176695</v>
+        <v>126175980</v>
       </c>
       <c r="B43" t="n">
-        <v>91534</v>
+        <v>98345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533734</v>
+        <v>533762</v>
       </c>
       <c r="R43" t="n">
-        <v>6928700</v>
+        <v>6928707</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5327,10 +5336,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126181218</v>
+        <v>126179959</v>
       </c>
       <c r="B44" t="n">
-        <v>91534</v>
+        <v>78732</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5338,21 +5347,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5362,10 +5371,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533723</v>
+        <v>533620</v>
       </c>
       <c r="R44" t="n">
-        <v>6928740</v>
+        <v>6928771</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5397,7 +5406,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5407,7 +5416,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5434,32 +5443,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126182304</v>
+        <v>126176695</v>
       </c>
       <c r="B45" t="n">
-        <v>92528</v>
+        <v>91534</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5469,13 +5478,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533624</v>
+        <v>533734</v>
       </c>
       <c r="R45" t="n">
-        <v>6928837</v>
+        <v>6928700</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5504,7 +5513,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5514,7 +5523,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5529,44 +5538,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126182221</v>
+        <v>126181218</v>
       </c>
       <c r="B46" t="n">
-        <v>92528</v>
+        <v>91534</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5576,10 +5585,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533640</v>
+        <v>533723</v>
       </c>
       <c r="R46" t="n">
-        <v>6928856</v>
+        <v>6928740</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5611,7 +5620,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5621,7 +5630,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5648,32 +5657,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126179959</v>
+        <v>126182304</v>
       </c>
       <c r="B47" t="n">
-        <v>78732</v>
+        <v>92528</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5683,10 +5692,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533620</v>
+        <v>533624</v>
       </c>
       <c r="R47" t="n">
-        <v>6928771</v>
+        <v>6928837</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5718,7 +5727,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5728,7 +5737,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5755,57 +5764,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126175980</v>
+        <v>126182221</v>
       </c>
       <c r="B48" t="n">
-        <v>98345</v>
+        <v>92528</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533762</v>
+        <v>533640</v>
       </c>
       <c r="R48" t="n">
-        <v>6928707</v>
+        <v>6928856</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5859,12 +5859,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6522,48 +6522,57 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126182214</v>
+        <v>126175256</v>
       </c>
       <c r="B55" t="n">
-        <v>78732</v>
+        <v>98345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533640</v>
+        <v>533811</v>
       </c>
       <c r="R55" t="n">
-        <v>6928855</v>
+        <v>6928689</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6592,7 +6601,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6602,7 +6611,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6617,19 +6626,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126181960</v>
+        <v>126182214</v>
       </c>
       <c r="B56" t="n">
         <v>78732</v>
@@ -6664,10 +6673,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533769</v>
+        <v>533640</v>
       </c>
       <c r="R56" t="n">
-        <v>6928852</v>
+        <v>6928855</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6699,7 +6708,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6709,7 +6718,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6736,7 +6745,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126182040</v>
+        <v>126181960</v>
       </c>
       <c r="B57" t="n">
         <v>78732</v>
@@ -6771,10 +6780,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533719</v>
+        <v>533769</v>
       </c>
       <c r="R57" t="n">
-        <v>6928884</v>
+        <v>6928852</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6806,7 +6815,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6816,7 +6825,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6843,57 +6852,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126175256</v>
+        <v>126182040</v>
       </c>
       <c r="B58" t="n">
-        <v>98345</v>
+        <v>78732</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533811</v>
+        <v>533719</v>
       </c>
       <c r="R58" t="n">
-        <v>6928689</v>
+        <v>6928884</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6947,12 +6947,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -8575,32 +8575,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126230916</v>
+        <v>126230894</v>
       </c>
       <c r="B74" t="n">
-        <v>91534</v>
+        <v>92528</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8613,10 +8613,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533875</v>
+        <v>533760</v>
       </c>
       <c r="R74" t="n">
-        <v>6928695</v>
+        <v>6929925</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126230894</v>
+        <v>126230916</v>
       </c>
       <c r="B75" t="n">
-        <v>92528</v>
+        <v>91534</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533760</v>
+        <v>533875</v>
       </c>
       <c r="R75" t="n">
-        <v>6929925</v>
+        <v>6928695</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9387,48 +9387,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126230937</v>
+        <v>126231002</v>
       </c>
       <c r="B82" t="n">
-        <v>91534</v>
+        <v>98345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Källberget, Ånge , Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533736</v>
+        <v>533741</v>
       </c>
       <c r="R82" t="n">
-        <v>6928738</v>
+        <v>6928734</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9488,49 +9489,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126231002</v>
+        <v>126230937</v>
       </c>
       <c r="B83" t="n">
-        <v>98345</v>
+        <v>91534</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Källberget, Ånge , Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533741</v>
+        <v>533736</v>
       </c>
       <c r="R83" t="n">
-        <v>6928734</v>
+        <v>6928738</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126178047</v>
+        <v>126178127</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533733</v>
+        <v>533723</v>
       </c>
       <c r="R2" t="n">
-        <v>6928740</v>
+        <v>6928747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,54 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126178127</v>
+        <v>126178047</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533723</v>
+        <v>533733</v>
       </c>
       <c r="R3" t="n">
-        <v>6928747</v>
+        <v>6928740</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +901,7 @@
         <v>126182135</v>
       </c>
       <c r="B4" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126176893</v>
       </c>
       <c r="B5" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,37 +1121,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126180936</v>
+        <v>126182207</v>
       </c>
       <c r="B6" t="n">
-        <v>98345</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>55</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1160,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533738</v>
+        <v>533644</v>
       </c>
       <c r="R6" t="n">
-        <v>6928768</v>
+        <v>6928860</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1195,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1206,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126175525</v>
+        <v>126180936</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,12 +1268,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1276,13 +1277,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533774</v>
+        <v>533738</v>
       </c>
       <c r="R7" t="n">
-        <v>6928715</v>
+        <v>6928768</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,50 +1337,54 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126182207</v>
+        <v>126175525</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1388,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533644</v>
+        <v>533774</v>
       </c>
       <c r="R8" t="n">
-        <v>6928860</v>
+        <v>6928715</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1423,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1433,12 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,62 +1453,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126177259</v>
+        <v>126182188</v>
       </c>
       <c r="B9" t="n">
-        <v>80076</v>
+        <v>92532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533735</v>
+        <v>533653</v>
       </c>
       <c r="R9" t="n">
-        <v>6928726</v>
+        <v>6928877</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1575,7 @@
         <v>126181693</v>
       </c>
       <c r="B10" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1682,7 @@
         <v>126181209</v>
       </c>
       <c r="B11" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,45 +1786,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126182188</v>
+        <v>126177259</v>
       </c>
       <c r="B12" t="n">
-        <v>92528</v>
+        <v>80080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533653</v>
+        <v>533735</v>
       </c>
       <c r="R12" t="n">
-        <v>6928877</v>
+        <v>6928726</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,57 +1898,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126176747</v>
+        <v>126182178</v>
       </c>
       <c r="B13" t="n">
-        <v>98345</v>
+        <v>78736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533742</v>
+        <v>533652</v>
       </c>
       <c r="R13" t="n">
-        <v>6928718</v>
+        <v>6928869</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2002,60 +1993,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126182178</v>
+        <v>126176747</v>
       </c>
       <c r="B14" t="n">
-        <v>78732</v>
+        <v>98349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533652</v>
+        <v>533742</v>
       </c>
       <c r="R14" t="n">
-        <v>6928869</v>
+        <v>6928718</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,12 +2109,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2124,7 +2124,7 @@
         <v>126180157</v>
       </c>
       <c r="B15" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,48 +2237,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126182151</v>
+        <v>126178142</v>
       </c>
       <c r="B16" t="n">
-        <v>91399</v>
+        <v>98383</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533652</v>
+        <v>533722</v>
       </c>
       <c r="R16" t="n">
-        <v>6928869</v>
+        <v>6928754</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2307,7 +2316,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2317,7 +2326,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,69 +2341,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126178142</v>
+        <v>126182151</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>91403</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533722</v>
+        <v>533652</v>
       </c>
       <c r="R17" t="n">
-        <v>6928754</v>
+        <v>6928869</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,12 +2448,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2463,7 +2463,7 @@
         <v>126180591</v>
       </c>
       <c r="B18" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>126176599</v>
       </c>
       <c r="B19" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>126177332</v>
       </c>
       <c r="B20" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>126181665</v>
       </c>
       <c r="B21" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,48 +2915,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126181048</v>
+        <v>126178109</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>98383</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533733</v>
+        <v>533718</v>
       </c>
       <c r="R22" t="n">
-        <v>6928745</v>
+        <v>6928766</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2985,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,12 +3004,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växer rikligt på två aspar och även en gran</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3015,57 +3019,66 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126176059</v>
+        <v>126178121</v>
       </c>
       <c r="B23" t="n">
-        <v>91812</v>
+        <v>98383</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>760</v>
+        <v>219874</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533746</v>
+        <v>533717</v>
       </c>
       <c r="R23" t="n">
-        <v>6928708</v>
+        <v>6928757</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3134,54 +3147,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126178109</v>
+        <v>126176059</v>
       </c>
       <c r="B24" t="n">
-        <v>98379</v>
+        <v>91816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533718</v>
+        <v>533746</v>
       </c>
       <c r="R24" t="n">
-        <v>6928766</v>
+        <v>6928708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,57 +3254,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126178121</v>
+        <v>126181048</v>
       </c>
       <c r="B25" t="n">
-        <v>98379</v>
+        <v>80080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533717</v>
+        <v>533733</v>
       </c>
       <c r="R25" t="n">
-        <v>6928757</v>
+        <v>6928745</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,7 +3324,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3339,7 +3334,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växer rikligt på två aspar och även en gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,60 +3354,69 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126181871</v>
+        <v>126175257</v>
       </c>
       <c r="B26" t="n">
-        <v>78732</v>
+        <v>98349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533757</v>
+        <v>533799</v>
       </c>
       <c r="R26" t="n">
-        <v>6928745</v>
+        <v>6928693</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3445,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3455,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,22 +3470,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126175257</v>
+        <v>126178017</v>
       </c>
       <c r="B27" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3503,7 +3512,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3517,10 +3526,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533799</v>
+        <v>533723</v>
       </c>
       <c r="R27" t="n">
-        <v>6928693</v>
+        <v>6928730</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3589,54 +3598,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126178017</v>
+        <v>126178155</v>
       </c>
       <c r="B28" t="n">
-        <v>98345</v>
+        <v>97233</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533723</v>
+        <v>533696</v>
       </c>
       <c r="R28" t="n">
-        <v>6928730</v>
+        <v>6928789</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126178155</v>
+        <v>126181871</v>
       </c>
       <c r="B29" t="n">
-        <v>97229</v>
+        <v>78736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533696</v>
+        <v>533757</v>
       </c>
       <c r="R29" t="n">
-        <v>6928789</v>
+        <v>6928745</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,22 +3800,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126176144</v>
+        <v>126176544</v>
       </c>
       <c r="B30" t="n">
-        <v>80076</v>
+        <v>91538</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533746</v>
+        <v>533762</v>
       </c>
       <c r="R30" t="n">
-        <v>6928708</v>
+        <v>6928704</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3919,32 +3919,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126176544</v>
+        <v>126181652</v>
       </c>
       <c r="B31" t="n">
-        <v>91534</v>
+        <v>92532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533762</v>
+        <v>533745</v>
       </c>
       <c r="R31" t="n">
-        <v>6928704</v>
+        <v>6928735</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4014,12 +4014,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4029,7 +4029,7 @@
         <v>126181494</v>
       </c>
       <c r="B32" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4137,32 +4137,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126181652</v>
+        <v>126176144</v>
       </c>
       <c r="B33" t="n">
-        <v>92528</v>
+        <v>80080</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533745</v>
+        <v>533746</v>
       </c>
       <c r="R33" t="n">
-        <v>6928735</v>
+        <v>6928708</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4232,12 +4232,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4247,7 +4247,7 @@
         <v>126180980</v>
       </c>
       <c r="B34" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4355,57 +4355,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126175252</v>
+        <v>126181681</v>
       </c>
       <c r="B35" t="n">
-        <v>98345</v>
+        <v>91538</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533816</v>
+        <v>533745</v>
       </c>
       <c r="R35" t="n">
-        <v>6928686</v>
+        <v>6928735</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4434,7 +4425,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4444,7 +4435,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4459,57 +4450,66 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126178181</v>
+        <v>126175252</v>
       </c>
       <c r="B36" t="n">
-        <v>80036</v>
+        <v>98349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533723</v>
+        <v>533816</v>
       </c>
       <c r="R36" t="n">
-        <v>6928739</v>
+        <v>6928686</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4581,7 +4581,7 @@
         <v>126177002</v>
       </c>
       <c r="B37" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4685,32 +4685,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126181681</v>
+        <v>126178181</v>
       </c>
       <c r="B38" t="n">
-        <v>91534</v>
+        <v>80040</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,13 +4720,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533745</v>
+        <v>533723</v>
       </c>
       <c r="R38" t="n">
-        <v>6928735</v>
+        <v>6928739</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4780,22 +4780,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126175291</v>
+        <v>126180836</v>
       </c>
       <c r="B39" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4803,21 +4803,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533791</v>
+        <v>533708</v>
       </c>
       <c r="R39" t="n">
-        <v>6928687</v>
+        <v>6928798</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4887,22 +4887,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126180836</v>
+        <v>126182027</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>91164</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4934,13 +4934,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533708</v>
+        <v>533755</v>
       </c>
       <c r="R40" t="n">
-        <v>6928798</v>
+        <v>6928865</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4994,22 +4994,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126182027</v>
+        <v>126175291</v>
       </c>
       <c r="B41" t="n">
-        <v>91160</v>
+        <v>80080</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3242</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533755</v>
+        <v>533791</v>
       </c>
       <c r="R41" t="n">
-        <v>6928865</v>
+        <v>6928687</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5116,7 +5116,7 @@
         <v>126177654</v>
       </c>
       <c r="B42" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5220,57 +5220,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126175980</v>
+        <v>126179959</v>
       </c>
       <c r="B43" t="n">
-        <v>98345</v>
+        <v>78736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533762</v>
+        <v>533620</v>
       </c>
       <c r="R43" t="n">
-        <v>6928707</v>
+        <v>6928771</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5299,7 +5290,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5309,7 +5300,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5324,60 +5315,69 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126179959</v>
+        <v>126175980</v>
       </c>
       <c r="B44" t="n">
-        <v>78732</v>
+        <v>98349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533620</v>
+        <v>533762</v>
       </c>
       <c r="R44" t="n">
-        <v>6928771</v>
+        <v>6928707</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5431,12 +5431,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5446,7 +5446,7 @@
         <v>126176695</v>
       </c>
       <c r="B45" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>126181218</v>
       </c>
       <c r="B46" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126182304</v>
+        <v>126182221</v>
       </c>
       <c r="B47" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533624</v>
+        <v>533640</v>
       </c>
       <c r="R47" t="n">
-        <v>6928837</v>
+        <v>6928856</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5764,10 +5764,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126182221</v>
+        <v>126182304</v>
       </c>
       <c r="B48" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533640</v>
+        <v>533624</v>
       </c>
       <c r="R48" t="n">
-        <v>6928856</v>
+        <v>6928837</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5871,54 +5871,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126177821</v>
+        <v>126175215</v>
       </c>
       <c r="B49" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533723</v>
+        <v>533811</v>
       </c>
       <c r="R49" t="n">
-        <v>6928726</v>
+        <v>6928661</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5990,7 +5981,7 @@
         <v>126182185</v>
       </c>
       <c r="B50" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6097,7 +6088,7 @@
         <v>126180415</v>
       </c>
       <c r="B51" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6201,45 +6192,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126175432</v>
+        <v>126177821</v>
       </c>
       <c r="B52" t="n">
-        <v>80036</v>
+        <v>98349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533782</v>
+        <v>533723</v>
       </c>
       <c r="R52" t="n">
-        <v>6928709</v>
+        <v>6928726</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126175215</v>
+        <v>126175432</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>80040</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533811</v>
+        <v>533782</v>
       </c>
       <c r="R53" t="n">
-        <v>6928661</v>
+        <v>6928709</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6415,45 +6415,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126176512</v>
+        <v>126175256</v>
       </c>
       <c r="B54" t="n">
-        <v>91238</v>
+        <v>98349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533767</v>
+        <v>533811</v>
       </c>
       <c r="R54" t="n">
-        <v>6928695</v>
+        <v>6928689</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6522,57 +6531,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126175256</v>
+        <v>126182214</v>
       </c>
       <c r="B55" t="n">
-        <v>98345</v>
+        <v>78736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533811</v>
+        <v>533640</v>
       </c>
       <c r="R55" t="n">
-        <v>6928689</v>
+        <v>6928855</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6626,22 +6626,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126182214</v>
+        <v>126181960</v>
       </c>
       <c r="B56" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533640</v>
+        <v>533769</v>
       </c>
       <c r="R56" t="n">
-        <v>6928855</v>
+        <v>6928852</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6745,10 +6745,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126181960</v>
+        <v>126182040</v>
       </c>
       <c r="B57" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533769</v>
+        <v>533719</v>
       </c>
       <c r="R57" t="n">
-        <v>6928852</v>
+        <v>6928884</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6852,10 +6852,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126182040</v>
+        <v>126176512</v>
       </c>
       <c r="B58" t="n">
-        <v>78732</v>
+        <v>91242</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6863,21 +6863,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6887,13 +6887,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533719</v>
+        <v>533767</v>
       </c>
       <c r="R58" t="n">
-        <v>6928884</v>
+        <v>6928695</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6947,69 +6947,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126178221</v>
+        <v>126182236</v>
       </c>
       <c r="B59" t="n">
-        <v>98345</v>
+        <v>78736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533693</v>
+        <v>533635</v>
       </c>
       <c r="R59" t="n">
-        <v>6928759</v>
+        <v>6928840</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7038,7 +7029,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7048,7 +7039,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7063,22 +7054,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126182366</v>
+        <v>126178221</v>
       </c>
       <c r="B60" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7103,20 +7094,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533589</v>
+        <v>533693</v>
       </c>
       <c r="R60" t="n">
-        <v>6928781</v>
+        <v>6928759</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,44 +7170,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126182236</v>
+        <v>126182366</v>
       </c>
       <c r="B61" t="n">
-        <v>78732</v>
+        <v>98349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533635</v>
+        <v>533589</v>
       </c>
       <c r="R61" t="n">
-        <v>6928840</v>
+        <v>6928781</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7289,48 +7289,52 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126175788</v>
+        <v>126180477</v>
       </c>
       <c r="B62" t="n">
-        <v>91534</v>
+        <v>98349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533763</v>
+        <v>533673</v>
       </c>
       <c r="R62" t="n">
-        <v>6928712</v>
+        <v>6928773</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7359,7 +7363,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7369,7 +7373,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,22 +7388,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126178007</v>
+        <v>126175788</v>
       </c>
       <c r="B63" t="n">
-        <v>91238</v>
+        <v>91538</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7407,21 +7411,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7431,10 +7435,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533723</v>
+        <v>533763</v>
       </c>
       <c r="R63" t="n">
-        <v>6928730</v>
+        <v>6928712</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7503,52 +7507,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126180477</v>
+        <v>126178007</v>
       </c>
       <c r="B64" t="n">
-        <v>98345</v>
+        <v>91242</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533673</v>
+        <v>533723</v>
       </c>
       <c r="R64" t="n">
-        <v>6928773</v>
+        <v>6928730</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7602,44 +7602,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126176239</v>
+        <v>126178312</v>
       </c>
       <c r="B65" t="n">
-        <v>80112</v>
+        <v>91242</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533761</v>
+        <v>533708</v>
       </c>
       <c r="R65" t="n">
-        <v>6928713</v>
+        <v>6928704</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7721,32 +7721,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126182142</v>
+        <v>126176239</v>
       </c>
       <c r="B66" t="n">
-        <v>79591</v>
+        <v>80116</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7756,13 +7756,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533717</v>
+        <v>533761</v>
       </c>
       <c r="R66" t="n">
-        <v>6928888</v>
+        <v>6928713</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7816,22 +7816,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126177726</v>
+        <v>126182142</v>
       </c>
       <c r="B67" t="n">
-        <v>80076</v>
+        <v>79595</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7839,21 +7839,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7863,13 +7863,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533723</v>
+        <v>533717</v>
       </c>
       <c r="R67" t="n">
-        <v>6928726</v>
+        <v>6928888</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7923,22 +7923,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126178312</v>
+        <v>126177726</v>
       </c>
       <c r="B68" t="n">
-        <v>91238</v>
+        <v>80080</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7946,21 +7946,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533708</v>
+        <v>533723</v>
       </c>
       <c r="R68" t="n">
-        <v>6928704</v>
+        <v>6928726</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8042,32 +8042,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126182129</v>
+        <v>126176685</v>
       </c>
       <c r="B69" t="n">
-        <v>92528</v>
+        <v>91242</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533717</v>
+        <v>533743</v>
       </c>
       <c r="R69" t="n">
-        <v>6928888</v>
+        <v>6928709</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8137,44 +8137,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126176685</v>
+        <v>126182129</v>
       </c>
       <c r="B70" t="n">
-        <v>91238</v>
+        <v>92532</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8184,13 +8184,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533743</v>
+        <v>533717</v>
       </c>
       <c r="R70" t="n">
-        <v>6928709</v>
+        <v>6928888</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8244,12 +8244,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8259,7 +8259,7 @@
         <v>126176659</v>
       </c>
       <c r="B71" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8372,38 +8372,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126231086</v>
+        <v>126231107</v>
       </c>
       <c r="B72" t="n">
-        <v>98345</v>
+        <v>91207</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8411,10 +8410,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533679</v>
+        <v>533741</v>
       </c>
       <c r="R72" t="n">
-        <v>6928782</v>
+        <v>6928704</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8474,37 +8473,38 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126231107</v>
+        <v>126231086</v>
       </c>
       <c r="B73" t="n">
-        <v>91203</v>
+        <v>98349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8512,10 +8512,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533741</v>
+        <v>533679</v>
       </c>
       <c r="R73" t="n">
-        <v>6928704</v>
+        <v>6928782</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8578,7 +8578,7 @@
         <v>126230894</v>
       </c>
       <c r="B74" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>126230916</v>
       </c>
       <c r="B75" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>126230947</v>
       </c>
       <c r="B76" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>126231026</v>
       </c>
       <c r="B77" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>126230971</v>
       </c>
       <c r="B78" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>126231185</v>
       </c>
       <c r="B79" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>126231069</v>
       </c>
       <c r="B80" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>126231127</v>
       </c>
       <c r="B81" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9387,49 +9387,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126231002</v>
+        <v>126230937</v>
       </c>
       <c r="B82" t="n">
-        <v>98345</v>
+        <v>91538</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Källberget, Ånge , Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533741</v>
+        <v>533736</v>
       </c>
       <c r="R82" t="n">
-        <v>6928734</v>
+        <v>6928738</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9489,48 +9488,49 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126230937</v>
+        <v>126231002</v>
       </c>
       <c r="B83" t="n">
-        <v>91534</v>
+        <v>98349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Källberget, Ånge , Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533736</v>
+        <v>533741</v>
       </c>
       <c r="R83" t="n">
-        <v>6928738</v>
+        <v>6928734</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9593,7 +9593,7 @@
         <v>126230989</v>
       </c>
       <c r="B84" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>126230878</v>
       </c>
       <c r="B85" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>126231142</v>
       </c>
       <c r="B86" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>126231168</v>
       </c>
       <c r="B87" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -1465,45 +1465,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126182188</v>
+        <v>126176747</v>
       </c>
       <c r="B9" t="n">
-        <v>92532</v>
+        <v>98349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533653</v>
+        <v>533742</v>
       </c>
       <c r="R9" t="n">
-        <v>6928877</v>
+        <v>6928718</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126181693</v>
+        <v>126182178</v>
       </c>
       <c r="B10" t="n">
-        <v>91242</v>
+        <v>78736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1607,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533757</v>
+        <v>533652</v>
       </c>
       <c r="R10" t="n">
-        <v>6928745</v>
+        <v>6928869</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1642,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,32 +1688,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126181209</v>
+        <v>126182188</v>
       </c>
       <c r="B11" t="n">
-        <v>91242</v>
+        <v>92532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,13 +1723,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533731</v>
+        <v>533653</v>
       </c>
       <c r="R11" t="n">
-        <v>6928754</v>
+        <v>6928877</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126177259</v>
+        <v>126181693</v>
       </c>
       <c r="B12" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,42 +1806,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533735</v>
+        <v>533757</v>
       </c>
       <c r="R12" t="n">
-        <v>6928726</v>
+        <v>6928745</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,22 +1890,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126182178</v>
+        <v>126181209</v>
       </c>
       <c r="B13" t="n">
-        <v>78736</v>
+        <v>91242</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,21 +1913,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1933,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533652</v>
+        <v>533731</v>
       </c>
       <c r="R13" t="n">
-        <v>6928869</v>
+        <v>6928754</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1978,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,42 +2009,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126176747</v>
+        <v>126177259</v>
       </c>
       <c r="B14" t="n">
-        <v>98349</v>
+        <v>80080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533742</v>
+        <v>533735</v>
       </c>
       <c r="R14" t="n">
-        <v>6928718</v>
+        <v>6928726</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2237,57 +2237,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126178142</v>
+        <v>126182151</v>
       </c>
       <c r="B16" t="n">
-        <v>98383</v>
+        <v>91403</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533722</v>
+        <v>533652</v>
       </c>
       <c r="R16" t="n">
-        <v>6928754</v>
+        <v>6928869</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2316,7 +2307,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2326,7 +2317,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,60 +2332,69 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126182151</v>
+        <v>126178142</v>
       </c>
       <c r="B17" t="n">
-        <v>91403</v>
+        <v>98383</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533652</v>
+        <v>533722</v>
       </c>
       <c r="R17" t="n">
-        <v>6928869</v>
+        <v>6928754</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,12 +2448,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2915,54 +2915,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126178109</v>
+        <v>126176059</v>
       </c>
       <c r="B22" t="n">
-        <v>98383</v>
+        <v>91816</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533718</v>
+        <v>533746</v>
       </c>
       <c r="R22" t="n">
-        <v>6928766</v>
+        <v>6928708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3031,57 +3022,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126178121</v>
+        <v>126181048</v>
       </c>
       <c r="B23" t="n">
-        <v>98383</v>
+        <v>80080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533717</v>
+        <v>533733</v>
       </c>
       <c r="R23" t="n">
-        <v>6928757</v>
+        <v>6928745</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3110,7 +3092,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3120,7 +3102,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Växer rikligt på två aspar och även en gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3135,57 +3122,66 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126176059</v>
+        <v>126178109</v>
       </c>
       <c r="B24" t="n">
-        <v>91816</v>
+        <v>98383</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533746</v>
+        <v>533718</v>
       </c>
       <c r="R24" t="n">
-        <v>6928708</v>
+        <v>6928766</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,48 +3250,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126181048</v>
+        <v>126178121</v>
       </c>
       <c r="B25" t="n">
-        <v>80080</v>
+        <v>98383</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533733</v>
+        <v>533717</v>
       </c>
       <c r="R25" t="n">
-        <v>6928745</v>
+        <v>6928757</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,7 +3329,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3339,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växer rikligt på två aspar och även en gran</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,12 +3354,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -5978,45 +5978,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126182185</v>
+        <v>126177821</v>
       </c>
       <c r="B50" t="n">
-        <v>78736</v>
+        <v>98349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533637</v>
+        <v>533723</v>
       </c>
       <c r="R50" t="n">
-        <v>6928864</v>
+        <v>6928726</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6085,7 +6094,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126180415</v>
+        <v>126182185</v>
       </c>
       <c r="B51" t="n">
         <v>78736</v>
@@ -6120,13 +6129,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533678</v>
+        <v>533637</v>
       </c>
       <c r="R51" t="n">
-        <v>6928776</v>
+        <v>6928864</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6155,7 +6164,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6165,7 +6174,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6180,69 +6189,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126177821</v>
+        <v>126180415</v>
       </c>
       <c r="B52" t="n">
-        <v>98349</v>
+        <v>78736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533723</v>
+        <v>533678</v>
       </c>
       <c r="R52" t="n">
-        <v>6928726</v>
+        <v>6928776</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6296,12 +6296,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -8575,32 +8575,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126230894</v>
+        <v>126230916</v>
       </c>
       <c r="B74" t="n">
-        <v>92532</v>
+        <v>91538</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8613,10 +8613,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533760</v>
+        <v>533875</v>
       </c>
       <c r="R74" t="n">
-        <v>6929925</v>
+        <v>6928695</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126230916</v>
+        <v>126230894</v>
       </c>
       <c r="B75" t="n">
-        <v>91538</v>
+        <v>92532</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533875</v>
+        <v>533760</v>
       </c>
       <c r="R75" t="n">
-        <v>6928695</v>
+        <v>6929925</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126178127</v>
+        <v>126178047</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533723</v>
+        <v>533733</v>
       </c>
       <c r="R2" t="n">
-        <v>6928747</v>
+        <v>6928740</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126178047</v>
+        <v>126178127</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533733</v>
+        <v>533723</v>
       </c>
       <c r="R3" t="n">
-        <v>6928740</v>
+        <v>6928747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
         <v>126176893</v>
       </c>
       <c r="B5" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126180936</v>
+        <v>126175525</v>
       </c>
       <c r="B7" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1277,13 +1282,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533738</v>
+        <v>533774</v>
       </c>
       <c r="R7" t="n">
-        <v>6928768</v>
+        <v>6928715</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,22 +1342,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126175525</v>
+        <v>126180936</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,12 +1384,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533774</v>
+        <v>533738</v>
       </c>
       <c r="R8" t="n">
-        <v>6928715</v>
+        <v>6928768</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,69 +1453,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126176747</v>
+        <v>126182178</v>
       </c>
       <c r="B9" t="n">
-        <v>98349</v>
+        <v>78736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533742</v>
+        <v>533652</v>
       </c>
       <c r="R9" t="n">
-        <v>6928718</v>
+        <v>6928869</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,60 +1560,69 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126182178</v>
+        <v>126176747</v>
       </c>
       <c r="B10" t="n">
-        <v>78736</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533652</v>
+        <v>533742</v>
       </c>
       <c r="R10" t="n">
-        <v>6928869</v>
+        <v>6928718</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,57 +1676,62 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126182188</v>
+        <v>126177259</v>
       </c>
       <c r="B11" t="n">
-        <v>92532</v>
+        <v>80080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533653</v>
+        <v>533735</v>
       </c>
       <c r="R11" t="n">
-        <v>6928877</v>
+        <v>6928726</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2009,50 +2014,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126177259</v>
+        <v>126182188</v>
       </c>
       <c r="B14" t="n">
-        <v>80080</v>
+        <v>92532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533735</v>
+        <v>533653</v>
       </c>
       <c r="R14" t="n">
-        <v>6928726</v>
+        <v>6928877</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
         <v>126180157</v>
       </c>
       <c r="B15" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>126178142</v>
       </c>
       <c r="B17" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>126180591</v>
       </c>
       <c r="B18" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126176599</v>
+        <v>126181665</v>
       </c>
       <c r="B19" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,29 +2604,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533753</v>
+        <v>533745</v>
       </c>
       <c r="R19" t="n">
-        <v>6928692</v>
+        <v>6928735</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2655,7 +2646,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2665,7 +2656,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,12 +2671,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2695,7 +2686,7 @@
         <v>126177332</v>
       </c>
       <c r="B20" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2808,10 +2799,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126181665</v>
+        <v>126176599</v>
       </c>
       <c r="B21" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,20 +2827,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533745</v>
+        <v>533753</v>
       </c>
       <c r="R21" t="n">
-        <v>6928735</v>
+        <v>6928692</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,57 +2903,66 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126176059</v>
+        <v>126178121</v>
       </c>
       <c r="B22" t="n">
-        <v>91816</v>
+        <v>98386</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>219874</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533746</v>
+        <v>533717</v>
       </c>
       <c r="R22" t="n">
-        <v>6928708</v>
+        <v>6928757</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3134,54 +3143,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126178109</v>
+        <v>126176059</v>
       </c>
       <c r="B24" t="n">
-        <v>98383</v>
+        <v>91816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533718</v>
+        <v>533746</v>
       </c>
       <c r="R24" t="n">
-        <v>6928766</v>
+        <v>6928708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126178121</v>
+        <v>126178109</v>
       </c>
       <c r="B25" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533717</v>
+        <v>533718</v>
       </c>
       <c r="R25" t="n">
-        <v>6928757</v>
+        <v>6928766</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3366,57 +3366,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126175257</v>
+        <v>126181871</v>
       </c>
       <c r="B26" t="n">
-        <v>98349</v>
+        <v>78736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533799</v>
+        <v>533757</v>
       </c>
       <c r="R26" t="n">
-        <v>6928693</v>
+        <v>6928745</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3445,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3470,12 +3461,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3485,7 +3476,7 @@
         <v>126178017</v>
       </c>
       <c r="B27" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3598,45 +3589,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126178155</v>
+        <v>126175257</v>
       </c>
       <c r="B28" t="n">
-        <v>97233</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533696</v>
+        <v>533799</v>
       </c>
       <c r="R28" t="n">
-        <v>6928789</v>
+        <v>6928693</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126181871</v>
+        <v>126178155</v>
       </c>
       <c r="B29" t="n">
-        <v>78736</v>
+        <v>97236</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533757</v>
+        <v>533696</v>
       </c>
       <c r="R29" t="n">
-        <v>6928745</v>
+        <v>6928789</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,12 +3800,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4029,7 +4029,7 @@
         <v>126181494</v>
       </c>
       <c r="B32" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>126180980</v>
       </c>
       <c r="B34" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4355,32 +4355,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126181681</v>
+        <v>126178181</v>
       </c>
       <c r="B35" t="n">
-        <v>91538</v>
+        <v>80040</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4390,13 +4390,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533745</v>
+        <v>533723</v>
       </c>
       <c r="R35" t="n">
-        <v>6928735</v>
+        <v>6928739</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4450,12 +4450,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4465,7 +4465,7 @@
         <v>126175252</v>
       </c>
       <c r="B36" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126177002</v>
+        <v>126181681</v>
       </c>
       <c r="B37" t="n">
-        <v>78736</v>
+        <v>91538</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4589,21 +4589,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533732</v>
+        <v>533745</v>
       </c>
       <c r="R37" t="n">
-        <v>6928727</v>
+        <v>6928735</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4673,44 +4673,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126178181</v>
+        <v>126177002</v>
       </c>
       <c r="B38" t="n">
-        <v>80040</v>
+        <v>78736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533723</v>
+        <v>533732</v>
       </c>
       <c r="R38" t="n">
-        <v>6928739</v>
+        <v>6928727</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126180836</v>
+        <v>126175291</v>
       </c>
       <c r="B39" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4803,21 +4803,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533708</v>
+        <v>533791</v>
       </c>
       <c r="R39" t="n">
-        <v>6928798</v>
+        <v>6928687</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4887,22 +4887,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126182027</v>
+        <v>126180836</v>
       </c>
       <c r="B40" t="n">
-        <v>91164</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4934,13 +4934,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533755</v>
+        <v>533708</v>
       </c>
       <c r="R40" t="n">
-        <v>6928865</v>
+        <v>6928798</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4994,22 +4994,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126175291</v>
+        <v>126182027</v>
       </c>
       <c r="B41" t="n">
-        <v>80080</v>
+        <v>91164</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>3242</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533791</v>
+        <v>533755</v>
       </c>
       <c r="R41" t="n">
-        <v>6928687</v>
+        <v>6928865</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5116,7 +5116,7 @@
         <v>126177654</v>
       </c>
       <c r="B42" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126179959</v>
+        <v>126181218</v>
       </c>
       <c r="B43" t="n">
-        <v>78736</v>
+        <v>91538</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5231,21 +5231,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533620</v>
+        <v>533723</v>
       </c>
       <c r="R43" t="n">
-        <v>6928771</v>
+        <v>6928740</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5327,57 +5327,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126175980</v>
+        <v>126182304</v>
       </c>
       <c r="B44" t="n">
-        <v>98349</v>
+        <v>92532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533762</v>
+        <v>533624</v>
       </c>
       <c r="R44" t="n">
-        <v>6928707</v>
+        <v>6928837</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5406,7 +5397,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5416,7 +5407,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5431,44 +5422,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126176695</v>
+        <v>126182221</v>
       </c>
       <c r="B45" t="n">
-        <v>91538</v>
+        <v>92532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5478,13 +5469,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533734</v>
+        <v>533640</v>
       </c>
       <c r="R45" t="n">
-        <v>6928700</v>
+        <v>6928856</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5513,7 +5504,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5523,7 +5514,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5538,19 +5529,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126181218</v>
+        <v>126176695</v>
       </c>
       <c r="B46" t="n">
         <v>91538</v>
@@ -5585,13 +5576,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533723</v>
+        <v>533734</v>
       </c>
       <c r="R46" t="n">
-        <v>6928740</v>
+        <v>6928700</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5620,7 +5611,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5630,7 +5621,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5645,44 +5636,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126182221</v>
+        <v>126179959</v>
       </c>
       <c r="B47" t="n">
-        <v>92532</v>
+        <v>78736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5692,10 +5683,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533640</v>
+        <v>533620</v>
       </c>
       <c r="R47" t="n">
-        <v>6928856</v>
+        <v>6928771</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5727,7 +5718,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5737,7 +5728,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5764,48 +5755,57 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126182304</v>
+        <v>126175980</v>
       </c>
       <c r="B48" t="n">
-        <v>92532</v>
+        <v>98352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533624</v>
+        <v>533762</v>
       </c>
       <c r="R48" t="n">
-        <v>6928837</v>
+        <v>6928707</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5859,44 +5859,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126175215</v>
+        <v>126175432</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>80040</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533811</v>
+        <v>533782</v>
       </c>
       <c r="R49" t="n">
-        <v>6928661</v>
+        <v>6928709</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5981,7 +5981,7 @@
         <v>126177821</v>
       </c>
       <c r="B50" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126175432</v>
+        <v>126175215</v>
       </c>
       <c r="B53" t="n">
-        <v>80040</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533782</v>
+        <v>533811</v>
       </c>
       <c r="R53" t="n">
-        <v>6928709</v>
+        <v>6928661</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6415,54 +6415,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126175256</v>
+        <v>126176512</v>
       </c>
       <c r="B54" t="n">
-        <v>98349</v>
+        <v>91242</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533811</v>
+        <v>533767</v>
       </c>
       <c r="R54" t="n">
-        <v>6928689</v>
+        <v>6928695</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6638,7 +6629,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126181960</v>
+        <v>126182040</v>
       </c>
       <c r="B56" t="n">
         <v>78736</v>
@@ -6673,10 +6664,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533769</v>
+        <v>533719</v>
       </c>
       <c r="R56" t="n">
-        <v>6928852</v>
+        <v>6928884</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6708,7 +6699,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6718,7 +6709,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6745,7 +6736,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126182040</v>
+        <v>126181960</v>
       </c>
       <c r="B57" t="n">
         <v>78736</v>
@@ -6780,10 +6771,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533719</v>
+        <v>533769</v>
       </c>
       <c r="R57" t="n">
-        <v>6928884</v>
+        <v>6928852</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6815,7 +6806,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6825,7 +6816,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6852,45 +6843,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126176512</v>
+        <v>126175256</v>
       </c>
       <c r="B58" t="n">
-        <v>91242</v>
+        <v>98352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533767</v>
+        <v>533811</v>
       </c>
       <c r="R58" t="n">
-        <v>6928695</v>
+        <v>6928689</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7066,10 +7066,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126178221</v>
+        <v>126182366</v>
       </c>
       <c r="B60" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7094,29 +7094,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533693</v>
+        <v>533589</v>
       </c>
       <c r="R60" t="n">
-        <v>6928759</v>
+        <v>6928781</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7145,7 +7136,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7155,7 +7146,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,22 +7161,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126182366</v>
+        <v>126178221</v>
       </c>
       <c r="B61" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7210,20 +7201,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533589</v>
+        <v>533693</v>
       </c>
       <c r="R61" t="n">
-        <v>6928781</v>
+        <v>6928759</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7277,64 +7277,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126180477</v>
+        <v>126175788</v>
       </c>
       <c r="B62" t="n">
-        <v>98349</v>
+        <v>91538</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533673</v>
+        <v>533763</v>
       </c>
       <c r="R62" t="n">
-        <v>6928773</v>
+        <v>6928712</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7363,7 +7359,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7373,7 +7369,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7388,22 +7384,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126175788</v>
+        <v>126178007</v>
       </c>
       <c r="B63" t="n">
-        <v>91538</v>
+        <v>91242</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7411,21 +7407,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7435,10 +7431,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533763</v>
+        <v>533723</v>
       </c>
       <c r="R63" t="n">
-        <v>6928712</v>
+        <v>6928730</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7507,48 +7503,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126178007</v>
+        <v>126180477</v>
       </c>
       <c r="B64" t="n">
-        <v>91242</v>
+        <v>98352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533723</v>
+        <v>533673</v>
       </c>
       <c r="R64" t="n">
-        <v>6928730</v>
+        <v>6928773</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7602,22 +7602,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126178312</v>
+        <v>126177726</v>
       </c>
       <c r="B65" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7625,21 +7625,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533708</v>
+        <v>533723</v>
       </c>
       <c r="R65" t="n">
-        <v>6928704</v>
+        <v>6928726</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7935,10 +7935,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126177726</v>
+        <v>126178312</v>
       </c>
       <c r="B68" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7946,21 +7946,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533723</v>
+        <v>533708</v>
       </c>
       <c r="R68" t="n">
-        <v>6928726</v>
+        <v>6928704</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8149,48 +8149,57 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126182129</v>
+        <v>126176659</v>
       </c>
       <c r="B70" t="n">
-        <v>92532</v>
+        <v>98352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533717</v>
+        <v>533742</v>
       </c>
       <c r="R70" t="n">
-        <v>6928888</v>
+        <v>6928692</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8219,7 +8228,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8229,7 +8238,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8244,69 +8253,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126176659</v>
+        <v>126182129</v>
       </c>
       <c r="B71" t="n">
-        <v>98349</v>
+        <v>92532</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533742</v>
+        <v>533717</v>
       </c>
       <c r="R71" t="n">
-        <v>6928692</v>
+        <v>6928888</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8360,49 +8360,50 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126231107</v>
+        <v>126231086</v>
       </c>
       <c r="B72" t="n">
-        <v>91207</v>
+        <v>98352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8410,10 +8411,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533741</v>
+        <v>533679</v>
       </c>
       <c r="R72" t="n">
-        <v>6928704</v>
+        <v>6928782</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8473,38 +8474,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126231086</v>
+        <v>126231107</v>
       </c>
       <c r="B73" t="n">
-        <v>98349</v>
+        <v>91207</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8512,10 +8512,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533679</v>
+        <v>533741</v>
       </c>
       <c r="R73" t="n">
-        <v>6928782</v>
+        <v>6928704</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8881,7 +8881,7 @@
         <v>126231026</v>
       </c>
       <c r="B77" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>126230971</v>
       </c>
       <c r="B78" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>126231185</v>
       </c>
       <c r="B79" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>126231069</v>
       </c>
       <c r="B80" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9387,48 +9387,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126230937</v>
+        <v>126231002</v>
       </c>
       <c r="B82" t="n">
-        <v>91538</v>
+        <v>98352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Källberget, Ånge , Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533736</v>
+        <v>533741</v>
       </c>
       <c r="R82" t="n">
-        <v>6928738</v>
+        <v>6928734</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9488,49 +9489,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126231002</v>
+        <v>126230937</v>
       </c>
       <c r="B83" t="n">
-        <v>98349</v>
+        <v>91538</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Källberget, Ånge , Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533741</v>
+        <v>533736</v>
       </c>
       <c r="R83" t="n">
-        <v>6928734</v>
+        <v>6928738</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9593,7 +9593,7 @@
         <v>126230989</v>
       </c>
       <c r="B84" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9793,10 +9793,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126231142</v>
+        <v>126231168</v>
       </c>
       <c r="B86" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9804,21 +9804,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9827,14 +9827,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Käkbenet, Ånge, Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533702</v>
+        <v>533712</v>
       </c>
       <c r="R86" t="n">
-        <v>6928773</v>
+        <v>6928777</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126231168</v>
+        <v>126231142</v>
       </c>
       <c r="B87" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9928,14 +9928,14 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Käkbenet, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533712</v>
+        <v>533702</v>
       </c>
       <c r="R87" t="n">
-        <v>6928777</v>
+        <v>6928773</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126178047</v>
+        <v>126178127</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533733</v>
+        <v>533723</v>
       </c>
       <c r="R2" t="n">
-        <v>6928740</v>
+        <v>6928747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,54 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126178127</v>
+        <v>126178047</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533723</v>
+        <v>533733</v>
       </c>
       <c r="R3" t="n">
-        <v>6928747</v>
+        <v>6928740</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2344,37 +2344,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126178142</v>
+        <v>126180591</v>
       </c>
       <c r="B17" t="n">
-        <v>98386</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533722</v>
+        <v>533682</v>
       </c>
       <c r="R17" t="n">
-        <v>6928754</v>
+        <v>6928792</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2460,37 +2460,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126180591</v>
+        <v>126178142</v>
       </c>
       <c r="B18" t="n">
-        <v>98352</v>
+        <v>98386</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533682</v>
+        <v>533722</v>
       </c>
       <c r="R18" t="n">
-        <v>6928792</v>
+        <v>6928754</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2915,54 +2915,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126178121</v>
+        <v>126176059</v>
       </c>
       <c r="B22" t="n">
-        <v>98386</v>
+        <v>91816</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533717</v>
+        <v>533746</v>
       </c>
       <c r="R22" t="n">
-        <v>6928757</v>
+        <v>6928708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3031,48 +3022,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126181048</v>
+        <v>126178109</v>
       </c>
       <c r="B23" t="n">
-        <v>80080</v>
+        <v>98386</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533733</v>
+        <v>533718</v>
       </c>
       <c r="R23" t="n">
-        <v>6928745</v>
+        <v>6928766</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3111,12 +3111,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Växer rikligt på två aspar och även en gran</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3131,57 +3126,66 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126176059</v>
+        <v>126178121</v>
       </c>
       <c r="B24" t="n">
-        <v>91816</v>
+        <v>98386</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533746</v>
+        <v>533717</v>
       </c>
       <c r="R24" t="n">
-        <v>6928708</v>
+        <v>6928757</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,57 +3254,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126178109</v>
+        <v>126181048</v>
       </c>
       <c r="B25" t="n">
-        <v>98386</v>
+        <v>80080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533718</v>
+        <v>533733</v>
       </c>
       <c r="R25" t="n">
-        <v>6928766</v>
+        <v>6928745</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,7 +3324,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3339,7 +3334,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växer rikligt på två aspar och även en gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,12 +3354,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126176544</v>
+        <v>126176144</v>
       </c>
       <c r="B30" t="n">
-        <v>91538</v>
+        <v>80080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533762</v>
+        <v>533746</v>
       </c>
       <c r="R30" t="n">
-        <v>6928704</v>
+        <v>6928708</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4026,52 +4026,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126181494</v>
+        <v>126176544</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>91538</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533742</v>
+        <v>533762</v>
       </c>
       <c r="R32" t="n">
-        <v>6928730</v>
+        <v>6928704</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4100,7 +4096,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4110,7 +4106,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4125,60 +4121,64 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126176144</v>
+        <v>126181494</v>
       </c>
       <c r="B33" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533746</v>
+        <v>533742</v>
       </c>
       <c r="R33" t="n">
-        <v>6928708</v>
+        <v>6928730</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4232,12 +4232,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126181681</v>
+        <v>126177002</v>
       </c>
       <c r="B37" t="n">
-        <v>91538</v>
+        <v>78736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4589,21 +4589,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533745</v>
+        <v>533732</v>
       </c>
       <c r="R37" t="n">
-        <v>6928735</v>
+        <v>6928727</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4673,22 +4673,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126177002</v>
+        <v>126181681</v>
       </c>
       <c r="B38" t="n">
-        <v>78736</v>
+        <v>91538</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4696,21 +4696,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,13 +4720,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533732</v>
+        <v>533745</v>
       </c>
       <c r="R38" t="n">
-        <v>6928727</v>
+        <v>6928735</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4780,12 +4780,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126181218</v>
+        <v>126179959</v>
       </c>
       <c r="B43" t="n">
-        <v>91538</v>
+        <v>78736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5231,21 +5231,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533723</v>
+        <v>533620</v>
       </c>
       <c r="R43" t="n">
-        <v>6928740</v>
+        <v>6928771</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5327,48 +5327,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126182304</v>
+        <v>126175980</v>
       </c>
       <c r="B44" t="n">
-        <v>92532</v>
+        <v>98352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533624</v>
+        <v>533762</v>
       </c>
       <c r="R44" t="n">
-        <v>6928837</v>
+        <v>6928707</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,7 +5406,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5407,7 +5416,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5422,44 +5431,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126182221</v>
+        <v>126181218</v>
       </c>
       <c r="B45" t="n">
-        <v>92532</v>
+        <v>91538</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5469,10 +5478,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533640</v>
+        <v>533723</v>
       </c>
       <c r="R45" t="n">
-        <v>6928856</v>
+        <v>6928740</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5504,7 +5513,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5514,7 +5523,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5648,32 +5657,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126179959</v>
+        <v>126182304</v>
       </c>
       <c r="B47" t="n">
-        <v>78736</v>
+        <v>92532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5683,10 +5692,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533620</v>
+        <v>533624</v>
       </c>
       <c r="R47" t="n">
-        <v>6928771</v>
+        <v>6928837</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5718,7 +5727,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5728,7 +5737,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5755,57 +5764,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126175980</v>
+        <v>126182221</v>
       </c>
       <c r="B48" t="n">
-        <v>98352</v>
+        <v>92532</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533762</v>
+        <v>533640</v>
       </c>
       <c r="R48" t="n">
-        <v>6928707</v>
+        <v>6928856</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5859,44 +5859,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126175432</v>
+        <v>126175215</v>
       </c>
       <c r="B49" t="n">
-        <v>80040</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533782</v>
+        <v>533811</v>
       </c>
       <c r="R49" t="n">
-        <v>6928709</v>
+        <v>6928661</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5978,54 +5978,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126177821</v>
+        <v>126182185</v>
       </c>
       <c r="B50" t="n">
-        <v>98352</v>
+        <v>78736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533723</v>
+        <v>533637</v>
       </c>
       <c r="R50" t="n">
-        <v>6928726</v>
+        <v>6928864</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6094,7 +6085,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126182185</v>
+        <v>126180415</v>
       </c>
       <c r="B51" t="n">
         <v>78736</v>
@@ -6129,13 +6120,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533637</v>
+        <v>533678</v>
       </c>
       <c r="R51" t="n">
-        <v>6928864</v>
+        <v>6928776</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6164,7 +6155,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6174,7 +6165,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6189,44 +6180,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126180415</v>
+        <v>126175432</v>
       </c>
       <c r="B52" t="n">
-        <v>78736</v>
+        <v>80040</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6236,13 +6227,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533678</v>
+        <v>533782</v>
       </c>
       <c r="R52" t="n">
-        <v>6928776</v>
+        <v>6928709</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6271,7 +6262,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6281,7 +6272,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6296,57 +6287,66 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126175215</v>
+        <v>126177821</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533811</v>
+        <v>533723</v>
       </c>
       <c r="R53" t="n">
-        <v>6928661</v>
+        <v>6928726</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -8042,32 +8042,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126176685</v>
+        <v>126182129</v>
       </c>
       <c r="B69" t="n">
-        <v>91242</v>
+        <v>92532</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533743</v>
+        <v>533717</v>
       </c>
       <c r="R69" t="n">
-        <v>6928709</v>
+        <v>6928888</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8137,12 +8137,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8265,32 +8265,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126182129</v>
+        <v>126176685</v>
       </c>
       <c r="B71" t="n">
-        <v>92532</v>
+        <v>91242</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8300,13 +8300,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533717</v>
+        <v>533743</v>
       </c>
       <c r="R71" t="n">
-        <v>6928888</v>
+        <v>6928709</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8360,12 +8360,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9082,32 +9082,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126231185</v>
+        <v>126231069</v>
       </c>
       <c r="B79" t="n">
-        <v>98386</v>
+        <v>98352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9117,14 +9117,14 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Käkbenet, Ånge, Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533712</v>
+        <v>533711</v>
       </c>
       <c r="R79" t="n">
-        <v>6928777</v>
+        <v>6928775</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9184,32 +9184,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126231069</v>
+        <v>126231185</v>
       </c>
       <c r="B80" t="n">
-        <v>98352</v>
+        <v>98386</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9219,14 +9219,14 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Käkbenet, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533711</v>
+        <v>533712</v>
       </c>
       <c r="R80" t="n">
-        <v>6928775</v>
+        <v>6928777</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9793,10 +9793,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126231168</v>
+        <v>126231142</v>
       </c>
       <c r="B86" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9804,21 +9804,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9827,14 +9827,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Käkbenet, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533712</v>
+        <v>533702</v>
       </c>
       <c r="R86" t="n">
-        <v>6928777</v>
+        <v>6928773</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126231142</v>
+        <v>126231168</v>
       </c>
       <c r="B87" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9928,14 +9928,14 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Käkbenet, Ånge, Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533702</v>
+        <v>533712</v>
       </c>
       <c r="R87" t="n">
-        <v>6928773</v>
+        <v>6928777</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126178127</v>
+        <v>126178047</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533723</v>
+        <v>533733</v>
       </c>
       <c r="R2" t="n">
-        <v>6928747</v>
+        <v>6928740</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126178047</v>
+        <v>126178127</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533733</v>
+        <v>533723</v>
       </c>
       <c r="R3" t="n">
-        <v>6928740</v>
+        <v>6928747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126175525</v>
+        <v>126180936</v>
       </c>
       <c r="B7" t="n">
         <v>98352</v>
@@ -1268,12 +1268,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1282,13 +1277,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533774</v>
+        <v>533738</v>
       </c>
       <c r="R7" t="n">
-        <v>6928715</v>
+        <v>6928768</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,19 +1337,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126180936</v>
+        <v>126175525</v>
       </c>
       <c r="B8" t="n">
         <v>98352</v>
@@ -1384,7 +1379,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533738</v>
+        <v>533774</v>
       </c>
       <c r="R8" t="n">
-        <v>6928768</v>
+        <v>6928715</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,22 +1453,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126182178</v>
+        <v>126181209</v>
       </c>
       <c r="B9" t="n">
-        <v>78736</v>
+        <v>91242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533652</v>
+        <v>533731</v>
       </c>
       <c r="R9" t="n">
-        <v>6928869</v>
+        <v>6928754</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,57 +1572,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126176747</v>
+        <v>126181693</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>91242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533742</v>
+        <v>533757</v>
       </c>
       <c r="R10" t="n">
-        <v>6928718</v>
+        <v>6928745</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,50 +1667,54 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126177259</v>
+        <v>126176747</v>
       </c>
       <c r="B11" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1728,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533735</v>
+        <v>533742</v>
       </c>
       <c r="R11" t="n">
-        <v>6928726</v>
+        <v>6928718</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126181693</v>
+        <v>126177259</v>
       </c>
       <c r="B12" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,37 +1806,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533757</v>
+        <v>533735</v>
       </c>
       <c r="R12" t="n">
-        <v>6928745</v>
+        <v>6928726</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,44 +1895,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126181209</v>
+        <v>126182188</v>
       </c>
       <c r="B13" t="n">
-        <v>91242</v>
+        <v>92532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533731</v>
+        <v>533653</v>
       </c>
       <c r="R13" t="n">
-        <v>6928754</v>
+        <v>6928877</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2002,44 +2002,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126182188</v>
+        <v>126182178</v>
       </c>
       <c r="B14" t="n">
-        <v>92532</v>
+        <v>78736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533653</v>
+        <v>533652</v>
       </c>
       <c r="R14" t="n">
-        <v>6928877</v>
+        <v>6928869</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,12 +2109,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2344,37 +2344,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126180591</v>
+        <v>126178142</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>98386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533682</v>
+        <v>533722</v>
       </c>
       <c r="R17" t="n">
-        <v>6928792</v>
+        <v>6928754</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2460,37 +2460,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126178142</v>
+        <v>126180591</v>
       </c>
       <c r="B18" t="n">
-        <v>98386</v>
+        <v>98352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533722</v>
+        <v>533682</v>
       </c>
       <c r="R18" t="n">
-        <v>6928754</v>
+        <v>6928792</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126181665</v>
+        <v>126176599</v>
       </c>
       <c r="B19" t="n">
         <v>98352</v>
@@ -2604,20 +2604,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533745</v>
+        <v>533753</v>
       </c>
       <c r="R19" t="n">
-        <v>6928735</v>
+        <v>6928692</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2646,7 +2655,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2656,7 +2665,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,12 +2680,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2799,7 +2808,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126176599</v>
+        <v>126181665</v>
       </c>
       <c r="B21" t="n">
         <v>98352</v>
@@ -2827,29 +2836,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533753</v>
+        <v>533745</v>
       </c>
       <c r="R21" t="n">
-        <v>6928692</v>
+        <v>6928735</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,44 +2903,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126176059</v>
+        <v>126181048</v>
       </c>
       <c r="B22" t="n">
-        <v>91816</v>
+        <v>80080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,13 +2950,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533746</v>
+        <v>533733</v>
       </c>
       <c r="R22" t="n">
-        <v>6928708</v>
+        <v>6928745</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,7 +2995,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer rikligt på två aspar och även en gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,66 +3015,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126178109</v>
+        <v>126176059</v>
       </c>
       <c r="B23" t="n">
-        <v>98386</v>
+        <v>91816</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219874</v>
+        <v>760</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533718</v>
+        <v>533746</v>
       </c>
       <c r="R23" t="n">
-        <v>6928766</v>
+        <v>6928708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3138,7 +3134,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126178121</v>
+        <v>126178109</v>
       </c>
       <c r="B24" t="n">
         <v>98386</v>
@@ -3168,7 +3164,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3182,10 +3178,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533717</v>
+        <v>533718</v>
       </c>
       <c r="R24" t="n">
-        <v>6928757</v>
+        <v>6928766</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,48 +3250,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126181048</v>
+        <v>126178121</v>
       </c>
       <c r="B25" t="n">
-        <v>80080</v>
+        <v>98386</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533733</v>
+        <v>533717</v>
       </c>
       <c r="R25" t="n">
-        <v>6928745</v>
+        <v>6928757</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,7 +3329,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3339,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växer rikligt på två aspar och även en gran</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,44 +3354,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126181871</v>
+        <v>126178155</v>
       </c>
       <c r="B26" t="n">
-        <v>78736</v>
+        <v>97236</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3401,13 +3401,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533757</v>
+        <v>533696</v>
       </c>
       <c r="R26" t="n">
-        <v>6928745</v>
+        <v>6928789</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,19 +3461,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126178017</v>
+        <v>126175257</v>
       </c>
       <c r="B27" t="n">
         <v>98352</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533723</v>
+        <v>533799</v>
       </c>
       <c r="R27" t="n">
-        <v>6928730</v>
+        <v>6928693</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3589,7 +3589,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126175257</v>
+        <v>126178017</v>
       </c>
       <c r="B28" t="n">
         <v>98352</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533799</v>
+        <v>533723</v>
       </c>
       <c r="R28" t="n">
-        <v>6928693</v>
+        <v>6928730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126178155</v>
+        <v>126181871</v>
       </c>
       <c r="B29" t="n">
-        <v>97236</v>
+        <v>78736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533696</v>
+        <v>533757</v>
       </c>
       <c r="R29" t="n">
-        <v>6928789</v>
+        <v>6928745</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,60 +3800,64 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126176144</v>
+        <v>126181494</v>
       </c>
       <c r="B30" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533746</v>
+        <v>533742</v>
       </c>
       <c r="R30" t="n">
-        <v>6928708</v>
+        <v>6928730</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3882,7 +3886,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3892,7 +3896,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3907,44 +3911,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126181652</v>
+        <v>126176544</v>
       </c>
       <c r="B31" t="n">
-        <v>92532</v>
+        <v>91538</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3954,13 +3958,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533745</v>
+        <v>533762</v>
       </c>
       <c r="R31" t="n">
-        <v>6928735</v>
+        <v>6928704</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3989,7 +3993,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3999,7 +4003,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4014,44 +4018,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126176544</v>
+        <v>126181652</v>
       </c>
       <c r="B32" t="n">
-        <v>91538</v>
+        <v>92532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4061,13 +4065,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533762</v>
+        <v>533745</v>
       </c>
       <c r="R32" t="n">
-        <v>6928704</v>
+        <v>6928735</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4096,7 +4100,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4106,7 +4110,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4121,64 +4125,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126181494</v>
+        <v>126176144</v>
       </c>
       <c r="B33" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533742</v>
+        <v>533746</v>
       </c>
       <c r="R33" t="n">
-        <v>6928730</v>
+        <v>6928708</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4232,49 +4232,54 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126180980</v>
+        <v>126175252</v>
       </c>
       <c r="B34" t="n">
-        <v>98386</v>
+        <v>98352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4283,13 +4288,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533724</v>
+        <v>533816</v>
       </c>
       <c r="R34" t="n">
-        <v>6928748</v>
+        <v>6928686</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4318,7 +4323,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4328,7 +4333,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4343,44 +4348,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126178181</v>
+        <v>126177002</v>
       </c>
       <c r="B35" t="n">
-        <v>80040</v>
+        <v>78736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4390,10 +4395,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533723</v>
+        <v>533732</v>
       </c>
       <c r="R35" t="n">
-        <v>6928739</v>
+        <v>6928727</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4462,54 +4467,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126175252</v>
+        <v>126178181</v>
       </c>
       <c r="B36" t="n">
-        <v>98352</v>
+        <v>80040</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533816</v>
+        <v>533723</v>
       </c>
       <c r="R36" t="n">
-        <v>6928686</v>
+        <v>6928739</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4578,10 +4574,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126177002</v>
+        <v>126181681</v>
       </c>
       <c r="B37" t="n">
-        <v>78736</v>
+        <v>91538</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4589,21 +4585,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4613,13 +4609,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533732</v>
+        <v>533745</v>
       </c>
       <c r="R37" t="n">
-        <v>6928727</v>
+        <v>6928735</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4648,7 +4644,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4658,7 +4654,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4673,57 +4669,61 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126181681</v>
+        <v>126180980</v>
       </c>
       <c r="B38" t="n">
-        <v>91538</v>
+        <v>98386</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533745</v>
+        <v>533724</v>
       </c>
       <c r="R38" t="n">
-        <v>6928735</v>
+        <v>6928748</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4792,32 +4792,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126175291</v>
+        <v>126177654</v>
       </c>
       <c r="B39" t="n">
-        <v>80080</v>
+        <v>98386</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533791</v>
+        <v>533727</v>
       </c>
       <c r="R39" t="n">
-        <v>6928687</v>
+        <v>6928727</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126182027</v>
+        <v>126175291</v>
       </c>
       <c r="B41" t="n">
-        <v>91164</v>
+        <v>80080</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3242</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533755</v>
+        <v>533791</v>
       </c>
       <c r="R41" t="n">
-        <v>6928865</v>
+        <v>6928687</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5113,32 +5113,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126177654</v>
+        <v>126182027</v>
       </c>
       <c r="B42" t="n">
-        <v>98386</v>
+        <v>91164</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>3242</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533727</v>
+        <v>533755</v>
       </c>
       <c r="R42" t="n">
-        <v>6928727</v>
+        <v>6928865</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126179959</v>
+        <v>126181218</v>
       </c>
       <c r="B43" t="n">
-        <v>78736</v>
+        <v>91538</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5231,21 +5231,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533620</v>
+        <v>533723</v>
       </c>
       <c r="R43" t="n">
-        <v>6928771</v>
+        <v>6928740</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5327,54 +5327,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126175980</v>
+        <v>126176695</v>
       </c>
       <c r="B44" t="n">
-        <v>98352</v>
+        <v>91538</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533762</v>
+        <v>533734</v>
       </c>
       <c r="R44" t="n">
-        <v>6928707</v>
+        <v>6928700</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5443,48 +5434,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126181218</v>
+        <v>126175980</v>
       </c>
       <c r="B45" t="n">
-        <v>91538</v>
+        <v>98352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533723</v>
+        <v>533762</v>
       </c>
       <c r="R45" t="n">
-        <v>6928740</v>
+        <v>6928707</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5538,22 +5538,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126176695</v>
+        <v>126179959</v>
       </c>
       <c r="B46" t="n">
-        <v>91538</v>
+        <v>78736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533734</v>
+        <v>533620</v>
       </c>
       <c r="R46" t="n">
-        <v>6928700</v>
+        <v>6928771</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5645,12 +5645,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5978,45 +5978,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126182185</v>
+        <v>126177821</v>
       </c>
       <c r="B50" t="n">
-        <v>78736</v>
+        <v>98352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533637</v>
+        <v>533723</v>
       </c>
       <c r="R50" t="n">
-        <v>6928864</v>
+        <v>6928726</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6085,7 +6094,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126180415</v>
+        <v>126182185</v>
       </c>
       <c r="B51" t="n">
         <v>78736</v>
@@ -6120,13 +6129,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533678</v>
+        <v>533637</v>
       </c>
       <c r="R51" t="n">
-        <v>6928776</v>
+        <v>6928864</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6155,7 +6164,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6165,7 +6174,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6180,44 +6189,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126175432</v>
+        <v>126180415</v>
       </c>
       <c r="B52" t="n">
-        <v>80040</v>
+        <v>78736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6227,13 +6236,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533782</v>
+        <v>533678</v>
       </c>
       <c r="R52" t="n">
-        <v>6928709</v>
+        <v>6928776</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6262,7 +6271,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6272,7 +6281,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6287,66 +6296,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126177821</v>
+        <v>126175432</v>
       </c>
       <c r="B53" t="n">
-        <v>98352</v>
+        <v>80040</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533723</v>
+        <v>533782</v>
       </c>
       <c r="R53" t="n">
-        <v>6928726</v>
+        <v>6928709</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6522,48 +6522,57 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126182214</v>
+        <v>126175256</v>
       </c>
       <c r="B55" t="n">
-        <v>78736</v>
+        <v>98352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533640</v>
+        <v>533811</v>
       </c>
       <c r="R55" t="n">
-        <v>6928855</v>
+        <v>6928689</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6592,7 +6601,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6602,7 +6611,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6617,19 +6626,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126182040</v>
+        <v>126182214</v>
       </c>
       <c r="B56" t="n">
         <v>78736</v>
@@ -6664,10 +6673,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533719</v>
+        <v>533640</v>
       </c>
       <c r="R56" t="n">
-        <v>6928884</v>
+        <v>6928855</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6699,7 +6708,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6709,7 +6718,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6843,57 +6852,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126175256</v>
+        <v>126182040</v>
       </c>
       <c r="B58" t="n">
-        <v>98352</v>
+        <v>78736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533811</v>
+        <v>533719</v>
       </c>
       <c r="R58" t="n">
-        <v>6928689</v>
+        <v>6928884</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6947,12 +6947,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7066,7 +7066,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126182366</v>
+        <v>126178221</v>
       </c>
       <c r="B60" t="n">
         <v>98352</v>
@@ -7094,20 +7094,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533589</v>
+        <v>533693</v>
       </c>
       <c r="R60" t="n">
-        <v>6928781</v>
+        <v>6928759</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7136,7 +7145,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7146,7 +7155,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7161,19 +7170,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126178221</v>
+        <v>126182366</v>
       </c>
       <c r="B61" t="n">
         <v>98352</v>
@@ -7201,29 +7210,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533693</v>
+        <v>533589</v>
       </c>
       <c r="R61" t="n">
-        <v>6928759</v>
+        <v>6928781</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7277,60 +7277,64 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126175788</v>
+        <v>126180477</v>
       </c>
       <c r="B62" t="n">
-        <v>91538</v>
+        <v>98352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533763</v>
+        <v>533673</v>
       </c>
       <c r="R62" t="n">
-        <v>6928712</v>
+        <v>6928773</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7359,7 +7363,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7369,7 +7373,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,12 +7388,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7503,52 +7507,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126180477</v>
+        <v>126175788</v>
       </c>
       <c r="B64" t="n">
-        <v>98352</v>
+        <v>91538</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533673</v>
+        <v>533763</v>
       </c>
       <c r="R64" t="n">
-        <v>6928773</v>
+        <v>6928712</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7602,22 +7602,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126177726</v>
+        <v>126178312</v>
       </c>
       <c r="B65" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7625,21 +7625,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533723</v>
+        <v>533708</v>
       </c>
       <c r="R65" t="n">
-        <v>6928726</v>
+        <v>6928704</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7721,32 +7721,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126176239</v>
+        <v>126177726</v>
       </c>
       <c r="B66" t="n">
-        <v>80116</v>
+        <v>80080</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7756,10 +7756,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533761</v>
+        <v>533723</v>
       </c>
       <c r="R66" t="n">
-        <v>6928713</v>
+        <v>6928726</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7828,32 +7828,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126182142</v>
+        <v>126176239</v>
       </c>
       <c r="B67" t="n">
-        <v>79595</v>
+        <v>80116</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7863,13 +7863,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533717</v>
+        <v>533761</v>
       </c>
       <c r="R67" t="n">
-        <v>6928888</v>
+        <v>6928713</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7923,22 +7923,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126178312</v>
+        <v>126182142</v>
       </c>
       <c r="B68" t="n">
-        <v>91242</v>
+        <v>79595</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7946,21 +7946,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533708</v>
+        <v>533717</v>
       </c>
       <c r="R68" t="n">
-        <v>6928704</v>
+        <v>6928888</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8030,44 +8030,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126182129</v>
+        <v>126176685</v>
       </c>
       <c r="B69" t="n">
-        <v>92532</v>
+        <v>91242</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533717</v>
+        <v>533743</v>
       </c>
       <c r="R69" t="n">
-        <v>6928888</v>
+        <v>6928709</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8137,69 +8137,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126176659</v>
+        <v>126182129</v>
       </c>
       <c r="B70" t="n">
-        <v>98352</v>
+        <v>92532</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533742</v>
+        <v>533717</v>
       </c>
       <c r="R70" t="n">
-        <v>6928692</v>
+        <v>6928888</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8228,7 +8219,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8238,7 +8229,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8253,57 +8244,66 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126176685</v>
+        <v>126176659</v>
       </c>
       <c r="B71" t="n">
-        <v>91242</v>
+        <v>98352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533743</v>
+        <v>533742</v>
       </c>
       <c r="R71" t="n">
-        <v>6928709</v>
+        <v>6928692</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8575,32 +8575,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126230916</v>
+        <v>126230894</v>
       </c>
       <c r="B74" t="n">
-        <v>91538</v>
+        <v>92532</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8613,10 +8613,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533875</v>
+        <v>533760</v>
       </c>
       <c r="R74" t="n">
-        <v>6928695</v>
+        <v>6929925</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126230894</v>
+        <v>126230916</v>
       </c>
       <c r="B75" t="n">
-        <v>92532</v>
+        <v>91538</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533760</v>
+        <v>533875</v>
       </c>
       <c r="R75" t="n">
-        <v>6929925</v>
+        <v>6928695</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9387,49 +9387,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126231002</v>
+        <v>126230937</v>
       </c>
       <c r="B82" t="n">
-        <v>98352</v>
+        <v>91538</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Källberget, Ånge , Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533741</v>
+        <v>533736</v>
       </c>
       <c r="R82" t="n">
-        <v>6928734</v>
+        <v>6928738</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9489,48 +9488,49 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126230937</v>
+        <v>126231002</v>
       </c>
       <c r="B83" t="n">
-        <v>91538</v>
+        <v>98352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Källberget, Ånge , Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533736</v>
+        <v>533741</v>
       </c>
       <c r="R83" t="n">
-        <v>6928738</v>
+        <v>6928734</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126181209</v>
+        <v>126177259</v>
       </c>
       <c r="B9" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,37 +1476,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533731</v>
+        <v>533735</v>
       </c>
       <c r="R9" t="n">
-        <v>6928754</v>
+        <v>6928726</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1535,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,44 +1565,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126181693</v>
+        <v>126182188</v>
       </c>
       <c r="B10" t="n">
-        <v>91242</v>
+        <v>92532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1607,13 +1612,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533757</v>
+        <v>533653</v>
       </c>
       <c r="R10" t="n">
-        <v>6928745</v>
+        <v>6928877</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,7 +1647,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1657,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,69 +1672,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126176747</v>
+        <v>126181209</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>91242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533742</v>
+        <v>533731</v>
       </c>
       <c r="R11" t="n">
-        <v>6928718</v>
+        <v>6928754</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1754,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1764,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,22 +1779,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126177259</v>
+        <v>126181693</v>
       </c>
       <c r="B12" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,42 +1802,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533735</v>
+        <v>533757</v>
       </c>
       <c r="R12" t="n">
-        <v>6928726</v>
+        <v>6928745</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,57 +1886,66 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126182188</v>
+        <v>126176747</v>
       </c>
       <c r="B13" t="n">
-        <v>92532</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533653</v>
+        <v>533742</v>
       </c>
       <c r="R13" t="n">
-        <v>6928877</v>
+        <v>6928718</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2915,32 +2915,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126181048</v>
+        <v>126176059</v>
       </c>
       <c r="B22" t="n">
-        <v>80080</v>
+        <v>91816</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,13 +2950,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533733</v>
+        <v>533746</v>
       </c>
       <c r="R22" t="n">
-        <v>6928745</v>
+        <v>6928708</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,12 +2995,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växer rikligt på två aspar och även en gran</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3015,57 +3010,66 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126176059</v>
+        <v>126178109</v>
       </c>
       <c r="B23" t="n">
-        <v>91816</v>
+        <v>98386</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>760</v>
+        <v>219874</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533746</v>
+        <v>533718</v>
       </c>
       <c r="R23" t="n">
-        <v>6928708</v>
+        <v>6928766</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3134,7 +3138,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126178109</v>
+        <v>126178121</v>
       </c>
       <c r="B24" t="n">
         <v>98386</v>
@@ -3164,7 +3168,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3178,10 +3182,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533718</v>
+        <v>533717</v>
       </c>
       <c r="R24" t="n">
-        <v>6928766</v>
+        <v>6928757</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,57 +3254,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126178121</v>
+        <v>126181048</v>
       </c>
       <c r="B25" t="n">
-        <v>98386</v>
+        <v>80080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533717</v>
+        <v>533733</v>
       </c>
       <c r="R25" t="n">
-        <v>6928757</v>
+        <v>6928745</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,7 +3324,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3339,7 +3334,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växer rikligt på två aspar och även en gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,57 +3354,66 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126178155</v>
+        <v>126175257</v>
       </c>
       <c r="B26" t="n">
-        <v>97236</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533696</v>
+        <v>533799</v>
       </c>
       <c r="R26" t="n">
-        <v>6928789</v>
+        <v>6928693</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3473,7 +3482,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126175257</v>
+        <v>126178017</v>
       </c>
       <c r="B27" t="n">
         <v>98352</v>
@@ -3503,7 +3512,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3517,10 +3526,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533799</v>
+        <v>533723</v>
       </c>
       <c r="R27" t="n">
-        <v>6928693</v>
+        <v>6928730</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3589,57 +3598,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126178017</v>
+        <v>126181871</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>78736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533723</v>
+        <v>533757</v>
       </c>
       <c r="R28" t="n">
-        <v>6928730</v>
+        <v>6928745</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3693,44 +3693,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126181871</v>
+        <v>126178155</v>
       </c>
       <c r="B29" t="n">
-        <v>78736</v>
+        <v>97236</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533757</v>
+        <v>533696</v>
       </c>
       <c r="R29" t="n">
-        <v>6928745</v>
+        <v>6928789</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,12 +3800,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4244,57 +4244,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126175252</v>
+        <v>126181681</v>
       </c>
       <c r="B34" t="n">
-        <v>98352</v>
+        <v>91538</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533816</v>
+        <v>533745</v>
       </c>
       <c r="R34" t="n">
-        <v>6928686</v>
+        <v>6928735</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4323,7 +4314,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4333,7 +4324,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4348,60 +4339,64 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126177002</v>
+        <v>126180980</v>
       </c>
       <c r="B35" t="n">
-        <v>78736</v>
+        <v>98386</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>219874</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533732</v>
+        <v>533724</v>
       </c>
       <c r="R35" t="n">
-        <v>6928727</v>
+        <v>6928748</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4430,7 +4425,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4440,7 +4435,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4455,57 +4450,66 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126178181</v>
+        <v>126175252</v>
       </c>
       <c r="B36" t="n">
-        <v>80040</v>
+        <v>98352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533723</v>
+        <v>533816</v>
       </c>
       <c r="R36" t="n">
-        <v>6928739</v>
+        <v>6928686</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4574,10 +4578,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126181681</v>
+        <v>126177002</v>
       </c>
       <c r="B37" t="n">
-        <v>91538</v>
+        <v>78736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4585,21 +4589,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4609,13 +4613,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533745</v>
+        <v>533732</v>
       </c>
       <c r="R37" t="n">
-        <v>6928735</v>
+        <v>6928727</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4644,7 +4648,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4654,7 +4658,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4669,22 +4673,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126180980</v>
+        <v>126178181</v>
       </c>
       <c r="B38" t="n">
-        <v>98386</v>
+        <v>80040</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4692,41 +4696,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219874</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533724</v>
+        <v>533723</v>
       </c>
       <c r="R38" t="n">
-        <v>6928748</v>
+        <v>6928739</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4780,12 +4780,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5220,32 +5220,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126181218</v>
+        <v>126182304</v>
       </c>
       <c r="B43" t="n">
-        <v>91538</v>
+        <v>92532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533723</v>
+        <v>533624</v>
       </c>
       <c r="R43" t="n">
-        <v>6928740</v>
+        <v>6928837</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5327,32 +5327,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126176695</v>
+        <v>126182221</v>
       </c>
       <c r="B44" t="n">
-        <v>91538</v>
+        <v>92532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533734</v>
+        <v>533640</v>
       </c>
       <c r="R44" t="n">
-        <v>6928700</v>
+        <v>6928856</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5422,69 +5422,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126175980</v>
+        <v>126181218</v>
       </c>
       <c r="B45" t="n">
-        <v>98352</v>
+        <v>91538</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533762</v>
+        <v>533723</v>
       </c>
       <c r="R45" t="n">
-        <v>6928707</v>
+        <v>6928740</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5513,7 +5504,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5523,7 +5514,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5538,22 +5529,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126179959</v>
+        <v>126176695</v>
       </c>
       <c r="B46" t="n">
-        <v>78736</v>
+        <v>91538</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5561,21 +5552,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5585,13 +5576,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533620</v>
+        <v>533734</v>
       </c>
       <c r="R46" t="n">
-        <v>6928771</v>
+        <v>6928700</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5620,7 +5611,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5630,7 +5621,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5645,60 +5636,69 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126182304</v>
+        <v>126175980</v>
       </c>
       <c r="B47" t="n">
-        <v>92532</v>
+        <v>98352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533624</v>
+        <v>533762</v>
       </c>
       <c r="R47" t="n">
-        <v>6928837</v>
+        <v>6928707</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5752,44 +5752,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126182221</v>
+        <v>126179959</v>
       </c>
       <c r="B48" t="n">
-        <v>92532</v>
+        <v>78736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533640</v>
+        <v>533620</v>
       </c>
       <c r="R48" t="n">
-        <v>6928856</v>
+        <v>6928771</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6959,48 +6959,57 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126182236</v>
+        <v>126178221</v>
       </c>
       <c r="B59" t="n">
-        <v>78736</v>
+        <v>98352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533635</v>
+        <v>533693</v>
       </c>
       <c r="R59" t="n">
-        <v>6928840</v>
+        <v>6928759</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7029,7 +7038,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7039,7 +7048,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7054,19 +7063,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126178221</v>
+        <v>126182366</v>
       </c>
       <c r="B60" t="n">
         <v>98352</v>
@@ -7094,29 +7103,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533693</v>
+        <v>533589</v>
       </c>
       <c r="R60" t="n">
-        <v>6928759</v>
+        <v>6928781</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,44 +7170,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126182366</v>
+        <v>126182236</v>
       </c>
       <c r="B61" t="n">
-        <v>98352</v>
+        <v>78736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533589</v>
+        <v>533635</v>
       </c>
       <c r="R61" t="n">
-        <v>6928781</v>
+        <v>6928840</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7614,10 +7614,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126178312</v>
+        <v>126177726</v>
       </c>
       <c r="B65" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7625,21 +7625,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533708</v>
+        <v>533723</v>
       </c>
       <c r="R65" t="n">
-        <v>6928704</v>
+        <v>6928726</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7721,32 +7721,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126177726</v>
+        <v>126176239</v>
       </c>
       <c r="B66" t="n">
-        <v>80080</v>
+        <v>80116</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7756,10 +7756,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533723</v>
+        <v>533761</v>
       </c>
       <c r="R66" t="n">
-        <v>6928726</v>
+        <v>6928713</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7828,32 +7828,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126176239</v>
+        <v>126182142</v>
       </c>
       <c r="B67" t="n">
-        <v>80116</v>
+        <v>79595</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7863,13 +7863,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533761</v>
+        <v>533717</v>
       </c>
       <c r="R67" t="n">
-        <v>6928713</v>
+        <v>6928888</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7923,22 +7923,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126182142</v>
+        <v>126178312</v>
       </c>
       <c r="B68" t="n">
-        <v>79595</v>
+        <v>91242</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7946,21 +7946,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533717</v>
+        <v>533708</v>
       </c>
       <c r="R68" t="n">
-        <v>6928888</v>
+        <v>6928704</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8030,12 +8030,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8372,38 +8372,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126231086</v>
+        <v>126231107</v>
       </c>
       <c r="B72" t="n">
-        <v>98352</v>
+        <v>91207</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8411,10 +8410,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533679</v>
+        <v>533741</v>
       </c>
       <c r="R72" t="n">
-        <v>6928782</v>
+        <v>6928704</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8474,37 +8473,38 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126231107</v>
+        <v>126231086</v>
       </c>
       <c r="B73" t="n">
-        <v>91207</v>
+        <v>98352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8512,10 +8512,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533741</v>
+        <v>533679</v>
       </c>
       <c r="R73" t="n">
-        <v>6928704</v>
+        <v>6928782</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8575,32 +8575,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126230894</v>
+        <v>126230916</v>
       </c>
       <c r="B74" t="n">
-        <v>92532</v>
+        <v>91538</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8613,10 +8613,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533760</v>
+        <v>533875</v>
       </c>
       <c r="R74" t="n">
-        <v>6929925</v>
+        <v>6928695</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126230916</v>
+        <v>126230894</v>
       </c>
       <c r="B75" t="n">
-        <v>91538</v>
+        <v>92532</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533875</v>
+        <v>533760</v>
       </c>
       <c r="R75" t="n">
-        <v>6928695</v>
+        <v>6929925</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126178047</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126178127</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126182135</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126176893</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>126182207</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>126180936</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>126175525</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126177259</v>
+        <v>126182178</v>
       </c>
       <c r="B9" t="n">
-        <v>80080</v>
+        <v>78739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,42 +1476,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533735</v>
+        <v>533652</v>
       </c>
       <c r="R9" t="n">
-        <v>6928726</v>
+        <v>6928869</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,12 +1560,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1580,7 +1575,7 @@
         <v>126182188</v>
       </c>
       <c r="B10" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1682,7 @@
         <v>126181209</v>
       </c>
       <c r="B11" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1789,7 @@
         <v>126181693</v>
       </c>
       <c r="B12" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,42 +1893,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126176747</v>
+        <v>126177259</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>80083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1942,10 +1933,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533742</v>
+        <v>533735</v>
       </c>
       <c r="R13" t="n">
-        <v>6928718</v>
+        <v>6928726</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,48 +2005,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126182178</v>
+        <v>126176747</v>
       </c>
       <c r="B14" t="n">
-        <v>78736</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533652</v>
+        <v>533742</v>
       </c>
       <c r="R14" t="n">
-        <v>6928869</v>
+        <v>6928718</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,12 +2109,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2124,7 +2124,7 @@
         <v>126180157</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>126182151</v>
       </c>
       <c r="B16" t="n">
-        <v>91403</v>
+        <v>91406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>126178142</v>
       </c>
       <c r="B17" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>126180591</v>
       </c>
       <c r="B18" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>126176599</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>126177332</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>126181665</v>
       </c>
       <c r="B21" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>126176059</v>
       </c>
       <c r="B22" t="n">
-        <v>91816</v>
+        <v>91819</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3022,57 +3022,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126178109</v>
+        <v>126181048</v>
       </c>
       <c r="B23" t="n">
-        <v>98386</v>
+        <v>80083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533718</v>
+        <v>533733</v>
       </c>
       <c r="R23" t="n">
-        <v>6928766</v>
+        <v>6928745</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,7 +3092,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3111,7 +3102,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Växer rikligt på två aspar och även en gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3126,22 +3122,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126178121</v>
+        <v>126178109</v>
       </c>
       <c r="B24" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3168,7 +3164,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3182,10 +3178,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533717</v>
+        <v>533718</v>
       </c>
       <c r="R24" t="n">
-        <v>6928757</v>
+        <v>6928766</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,48 +3250,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126181048</v>
+        <v>126178121</v>
       </c>
       <c r="B25" t="n">
-        <v>80080</v>
+        <v>98395</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533733</v>
+        <v>533717</v>
       </c>
       <c r="R25" t="n">
-        <v>6928745</v>
+        <v>6928757</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,7 +3329,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3339,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växer rikligt på två aspar och även en gran</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,12 +3354,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3369,7 +3369,7 @@
         <v>126175257</v>
       </c>
       <c r="B26" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>126178017</v>
       </c>
       <c r="B27" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3598,32 +3598,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126181871</v>
+        <v>126178155</v>
       </c>
       <c r="B28" t="n">
-        <v>78736</v>
+        <v>97245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3633,13 +3633,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533757</v>
+        <v>533696</v>
       </c>
       <c r="R28" t="n">
-        <v>6928745</v>
+        <v>6928789</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3693,44 +3693,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126178155</v>
+        <v>126181871</v>
       </c>
       <c r="B29" t="n">
-        <v>97236</v>
+        <v>78739</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533696</v>
+        <v>533757</v>
       </c>
       <c r="R29" t="n">
-        <v>6928789</v>
+        <v>6928745</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,64 +3800,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126181494</v>
+        <v>126176544</v>
       </c>
       <c r="B30" t="n">
-        <v>98352</v>
+        <v>91541</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533742</v>
+        <v>533762</v>
       </c>
       <c r="R30" t="n">
-        <v>6928730</v>
+        <v>6928704</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3886,7 +3882,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3896,7 +3892,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3911,44 +3907,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126176544</v>
+        <v>126181652</v>
       </c>
       <c r="B31" t="n">
-        <v>91538</v>
+        <v>92535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3958,13 +3954,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533762</v>
+        <v>533745</v>
       </c>
       <c r="R31" t="n">
-        <v>6928704</v>
+        <v>6928735</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3993,7 +3989,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4003,7 +3999,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4018,44 +4014,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126181652</v>
+        <v>126176144</v>
       </c>
       <c r="B32" t="n">
-        <v>92532</v>
+        <v>80083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4065,13 +4061,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533745</v>
+        <v>533746</v>
       </c>
       <c r="R32" t="n">
-        <v>6928735</v>
+        <v>6928708</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4100,7 +4096,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4110,7 +4106,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4125,60 +4121,64 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126176144</v>
+        <v>126181494</v>
       </c>
       <c r="B33" t="n">
-        <v>80080</v>
+        <v>98361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533746</v>
+        <v>533742</v>
       </c>
       <c r="R33" t="n">
-        <v>6928708</v>
+        <v>6928730</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4232,12 +4232,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4247,7 +4247,7 @@
         <v>126181681</v>
       </c>
       <c r="B34" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>126180980</v>
       </c>
       <c r="B35" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>126175252</v>
       </c>
       <c r="B36" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>126177002</v>
       </c>
       <c r="B37" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>126178181</v>
       </c>
       <c r="B38" t="n">
-        <v>80040</v>
+        <v>80043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4792,32 +4792,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126177654</v>
+        <v>126182027</v>
       </c>
       <c r="B39" t="n">
-        <v>98386</v>
+        <v>91167</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219874</v>
+        <v>3242</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533727</v>
+        <v>533755</v>
       </c>
       <c r="R39" t="n">
-        <v>6928727</v>
+        <v>6928865</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126180836</v>
+        <v>126175291</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>80083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4934,13 +4934,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533708</v>
+        <v>533791</v>
       </c>
       <c r="R40" t="n">
-        <v>6928798</v>
+        <v>6928687</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4994,22 +4994,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126175291</v>
+        <v>126180836</v>
       </c>
       <c r="B41" t="n">
-        <v>80080</v>
+        <v>78980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5041,13 +5041,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533791</v>
+        <v>533708</v>
       </c>
       <c r="R41" t="n">
-        <v>6928687</v>
+        <v>6928798</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5101,44 +5101,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126182027</v>
+        <v>126177654</v>
       </c>
       <c r="B42" t="n">
-        <v>91164</v>
+        <v>98395</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3242</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533755</v>
+        <v>533727</v>
       </c>
       <c r="R42" t="n">
-        <v>6928865</v>
+        <v>6928727</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5223,7 +5223,7 @@
         <v>126182304</v>
       </c>
       <c r="B43" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5327,32 +5327,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126182221</v>
+        <v>126181218</v>
       </c>
       <c r="B44" t="n">
-        <v>92532</v>
+        <v>91541</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533640</v>
+        <v>533723</v>
       </c>
       <c r="R44" t="n">
-        <v>6928856</v>
+        <v>6928740</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5434,10 +5434,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126181218</v>
+        <v>126176695</v>
       </c>
       <c r="B45" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5469,13 +5469,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533723</v>
+        <v>533734</v>
       </c>
       <c r="R45" t="n">
-        <v>6928740</v>
+        <v>6928700</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5529,57 +5529,66 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126176695</v>
+        <v>126175980</v>
       </c>
       <c r="B46" t="n">
-        <v>91538</v>
+        <v>98361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533734</v>
+        <v>533762</v>
       </c>
       <c r="R46" t="n">
-        <v>6928700</v>
+        <v>6928707</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5648,57 +5657,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126175980</v>
+        <v>126179959</v>
       </c>
       <c r="B47" t="n">
-        <v>98352</v>
+        <v>78739</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533762</v>
+        <v>533620</v>
       </c>
       <c r="R47" t="n">
-        <v>6928707</v>
+        <v>6928771</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5752,44 +5752,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126179959</v>
+        <v>126182221</v>
       </c>
       <c r="B48" t="n">
-        <v>78736</v>
+        <v>92535</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533620</v>
+        <v>533640</v>
       </c>
       <c r="R48" t="n">
-        <v>6928771</v>
+        <v>6928856</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5874,7 +5874,7 @@
         <v>126175215</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>126177821</v>
       </c>
       <c r="B50" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>126182185</v>
       </c>
       <c r="B51" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>126180415</v>
       </c>
       <c r="B52" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>126175432</v>
       </c>
       <c r="B53" t="n">
-        <v>80040</v>
+        <v>80043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6415,45 +6415,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126176512</v>
+        <v>126175256</v>
       </c>
       <c r="B54" t="n">
-        <v>91242</v>
+        <v>98361</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533767</v>
+        <v>533811</v>
       </c>
       <c r="R54" t="n">
-        <v>6928695</v>
+        <v>6928689</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6522,57 +6531,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126175256</v>
+        <v>126182214</v>
       </c>
       <c r="B55" t="n">
-        <v>98352</v>
+        <v>78739</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533811</v>
+        <v>533640</v>
       </c>
       <c r="R55" t="n">
-        <v>6928689</v>
+        <v>6928855</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6626,22 +6626,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126182214</v>
+        <v>126181960</v>
       </c>
       <c r="B56" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533640</v>
+        <v>533769</v>
       </c>
       <c r="R56" t="n">
-        <v>6928855</v>
+        <v>6928852</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6745,10 +6745,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126181960</v>
+        <v>126182040</v>
       </c>
       <c r="B57" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533769</v>
+        <v>533719</v>
       </c>
       <c r="R57" t="n">
-        <v>6928852</v>
+        <v>6928884</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6852,10 +6852,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126182040</v>
+        <v>126176512</v>
       </c>
       <c r="B58" t="n">
-        <v>78736</v>
+        <v>91245</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6863,21 +6863,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6887,13 +6887,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533719</v>
+        <v>533767</v>
       </c>
       <c r="R58" t="n">
-        <v>6928884</v>
+        <v>6928695</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6947,12 +6947,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6962,7 +6962,7 @@
         <v>126178221</v>
       </c>
       <c r="B59" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>126182366</v>
       </c>
       <c r="B60" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>126182236</v>
       </c>
       <c r="B61" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7289,52 +7289,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126180477</v>
+        <v>126178007</v>
       </c>
       <c r="B62" t="n">
-        <v>98352</v>
+        <v>91245</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533673</v>
+        <v>533723</v>
       </c>
       <c r="R62" t="n">
-        <v>6928773</v>
+        <v>6928730</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7363,7 +7359,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7373,7 +7369,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7388,22 +7384,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126178007</v>
+        <v>126175788</v>
       </c>
       <c r="B63" t="n">
-        <v>91242</v>
+        <v>91541</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7411,21 +7407,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7435,10 +7431,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533723</v>
+        <v>533763</v>
       </c>
       <c r="R63" t="n">
-        <v>6928730</v>
+        <v>6928712</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7507,48 +7503,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126175788</v>
+        <v>126180477</v>
       </c>
       <c r="B64" t="n">
-        <v>91538</v>
+        <v>98361</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533763</v>
+        <v>533673</v>
       </c>
       <c r="R64" t="n">
-        <v>6928712</v>
+        <v>6928773</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7602,22 +7602,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126177726</v>
+        <v>126178312</v>
       </c>
       <c r="B65" t="n">
-        <v>80080</v>
+        <v>91245</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7625,21 +7625,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533723</v>
+        <v>533708</v>
       </c>
       <c r="R65" t="n">
-        <v>6928726</v>
+        <v>6928704</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7724,7 +7724,7 @@
         <v>126176239</v>
       </c>
       <c r="B66" t="n">
-        <v>80116</v>
+        <v>80119</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>126182142</v>
       </c>
       <c r="B67" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7935,10 +7935,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126178312</v>
+        <v>126177726</v>
       </c>
       <c r="B68" t="n">
-        <v>91242</v>
+        <v>80083</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7946,21 +7946,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533708</v>
+        <v>533723</v>
       </c>
       <c r="R68" t="n">
-        <v>6928704</v>
+        <v>6928726</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8042,32 +8042,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126176685</v>
+        <v>126182129</v>
       </c>
       <c r="B69" t="n">
-        <v>91242</v>
+        <v>92535</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533743</v>
+        <v>533717</v>
       </c>
       <c r="R69" t="n">
-        <v>6928709</v>
+        <v>6928888</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8137,44 +8137,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126182129</v>
+        <v>126176685</v>
       </c>
       <c r="B70" t="n">
-        <v>92532</v>
+        <v>91245</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8184,13 +8184,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533717</v>
+        <v>533743</v>
       </c>
       <c r="R70" t="n">
-        <v>6928888</v>
+        <v>6928709</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8244,12 +8244,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8259,7 +8259,7 @@
         <v>126176659</v>
       </c>
       <c r="B71" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>126231107</v>
       </c>
       <c r="B72" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>126231086</v>
       </c>
       <c r="B73" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>126230916</v>
       </c>
       <c r="B74" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>126230894</v>
       </c>
       <c r="B75" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>126230947</v>
       </c>
       <c r="B76" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>126231026</v>
       </c>
       <c r="B77" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>126230971</v>
       </c>
       <c r="B78" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9082,32 +9082,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126231069</v>
+        <v>126231185</v>
       </c>
       <c r="B79" t="n">
-        <v>98352</v>
+        <v>98395</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9117,14 +9117,14 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Käkbenet, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533711</v>
+        <v>533712</v>
       </c>
       <c r="R79" t="n">
-        <v>6928775</v>
+        <v>6928777</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9184,32 +9184,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126231185</v>
+        <v>126231069</v>
       </c>
       <c r="B80" t="n">
-        <v>98386</v>
+        <v>98361</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9219,14 +9219,14 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Käkbenet, Ånge, Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533712</v>
+        <v>533711</v>
       </c>
       <c r="R80" t="n">
-        <v>6928777</v>
+        <v>6928775</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9289,7 +9289,7 @@
         <v>126231127</v>
       </c>
       <c r="B81" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>126230937</v>
       </c>
       <c r="B82" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>126231002</v>
       </c>
       <c r="B83" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>126230989</v>
       </c>
       <c r="B84" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>126230878</v>
       </c>
       <c r="B85" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>126231142</v>
       </c>
       <c r="B86" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>126231168</v>
       </c>
       <c r="B87" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -2237,48 +2237,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126182151</v>
+        <v>126178142</v>
       </c>
       <c r="B16" t="n">
-        <v>91406</v>
+        <v>98395</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533652</v>
+        <v>533722</v>
       </c>
       <c r="R16" t="n">
-        <v>6928869</v>
+        <v>6928754</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2307,7 +2316,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2317,7 +2326,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,49 +2341,49 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126178142</v>
+        <v>126180591</v>
       </c>
       <c r="B17" t="n">
-        <v>98395</v>
+        <v>98361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2388,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533722</v>
+        <v>533682</v>
       </c>
       <c r="R17" t="n">
-        <v>6928754</v>
+        <v>6928792</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2460,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126180591</v>
+        <v>126182151</v>
       </c>
       <c r="B18" t="n">
-        <v>98361</v>
+        <v>91406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,46 +2480,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533682</v>
+        <v>533652</v>
       </c>
       <c r="R18" t="n">
-        <v>6928792</v>
+        <v>6928869</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,12 +2564,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2915,45 +2915,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126176059</v>
+        <v>126178109</v>
       </c>
       <c r="B22" t="n">
-        <v>91819</v>
+        <v>98395</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>219874</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533746</v>
+        <v>533718</v>
       </c>
       <c r="R22" t="n">
-        <v>6928708</v>
+        <v>6928766</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3022,48 +3031,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126181048</v>
+        <v>126178121</v>
       </c>
       <c r="B23" t="n">
-        <v>80083</v>
+        <v>98395</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533733</v>
+        <v>533717</v>
       </c>
       <c r="R23" t="n">
-        <v>6928745</v>
+        <v>6928757</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3092,7 +3110,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3102,12 +3120,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Växer rikligt på två aspar och även en gran</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3122,66 +3135,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126178109</v>
+        <v>126176059</v>
       </c>
       <c r="B24" t="n">
-        <v>98395</v>
+        <v>91819</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533718</v>
+        <v>533746</v>
       </c>
       <c r="R24" t="n">
-        <v>6928766</v>
+        <v>6928708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,57 +3254,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126178121</v>
+        <v>126181048</v>
       </c>
       <c r="B25" t="n">
-        <v>98395</v>
+        <v>80083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533717</v>
+        <v>533733</v>
       </c>
       <c r="R25" t="n">
-        <v>6928757</v>
+        <v>6928745</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,7 +3324,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3339,7 +3334,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växer rikligt på två aspar och även en gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,69 +3354,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126175257</v>
+        <v>126181871</v>
       </c>
       <c r="B26" t="n">
-        <v>98361</v>
+        <v>78739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533799</v>
+        <v>533757</v>
       </c>
       <c r="R26" t="n">
-        <v>6928693</v>
+        <v>6928745</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3445,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3470,19 +3461,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126178017</v>
+        <v>126175257</v>
       </c>
       <c r="B27" t="n">
         <v>98361</v>
@@ -3512,7 +3503,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3526,10 +3517,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533723</v>
+        <v>533799</v>
       </c>
       <c r="R27" t="n">
-        <v>6928730</v>
+        <v>6928693</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3598,45 +3589,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126178155</v>
+        <v>126178017</v>
       </c>
       <c r="B28" t="n">
-        <v>97245</v>
+        <v>98361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533696</v>
+        <v>533723</v>
       </c>
       <c r="R28" t="n">
-        <v>6928789</v>
+        <v>6928730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126181871</v>
+        <v>126178155</v>
       </c>
       <c r="B29" t="n">
-        <v>78739</v>
+        <v>97245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533757</v>
+        <v>533696</v>
       </c>
       <c r="R29" t="n">
-        <v>6928745</v>
+        <v>6928789</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,60 +3800,64 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126176544</v>
+        <v>126181494</v>
       </c>
       <c r="B30" t="n">
-        <v>91541</v>
+        <v>98361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533762</v>
+        <v>533742</v>
       </c>
       <c r="R30" t="n">
-        <v>6928704</v>
+        <v>6928730</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3882,7 +3886,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3892,7 +3896,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3907,44 +3911,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126181652</v>
+        <v>126176544</v>
       </c>
       <c r="B31" t="n">
-        <v>92535</v>
+        <v>91541</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3954,13 +3958,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533745</v>
+        <v>533762</v>
       </c>
       <c r="R31" t="n">
-        <v>6928735</v>
+        <v>6928704</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3989,7 +3993,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3999,7 +4003,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4014,44 +4018,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126176144</v>
+        <v>126181652</v>
       </c>
       <c r="B32" t="n">
-        <v>80083</v>
+        <v>92535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4061,13 +4065,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533746</v>
+        <v>533745</v>
       </c>
       <c r="R32" t="n">
-        <v>6928708</v>
+        <v>6928735</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4096,7 +4100,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4106,7 +4110,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4121,64 +4125,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126181494</v>
+        <v>126176144</v>
       </c>
       <c r="B33" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533742</v>
+        <v>533746</v>
       </c>
       <c r="R33" t="n">
-        <v>6928730</v>
+        <v>6928708</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4232,12 +4232,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4792,32 +4792,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126182027</v>
+        <v>126177654</v>
       </c>
       <c r="B39" t="n">
-        <v>91167</v>
+        <v>98395</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3242</v>
+        <v>219874</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533755</v>
+        <v>533727</v>
       </c>
       <c r="R39" t="n">
-        <v>6928865</v>
+        <v>6928727</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126175291</v>
+        <v>126182027</v>
       </c>
       <c r="B40" t="n">
-        <v>80083</v>
+        <v>91167</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>3242</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533791</v>
+        <v>533755</v>
       </c>
       <c r="R40" t="n">
-        <v>6928687</v>
+        <v>6928865</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126180836</v>
+        <v>126175291</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5041,13 +5041,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533708</v>
+        <v>533791</v>
       </c>
       <c r="R41" t="n">
-        <v>6928798</v>
+        <v>6928687</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5101,44 +5101,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126177654</v>
+        <v>126180836</v>
       </c>
       <c r="B42" t="n">
-        <v>98395</v>
+        <v>78980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533727</v>
+        <v>533708</v>
       </c>
       <c r="R42" t="n">
-        <v>6928727</v>
+        <v>6928798</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,12 +5208,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -1238,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126180936</v>
+        <v>126175525</v>
       </c>
       <c r="B7" t="n">
         <v>98361</v>
@@ -1268,7 +1268,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1277,13 +1282,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533738</v>
+        <v>533774</v>
       </c>
       <c r="R7" t="n">
-        <v>6928768</v>
+        <v>6928715</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,19 +1342,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126175525</v>
+        <v>126180936</v>
       </c>
       <c r="B8" t="n">
         <v>98361</v>
@@ -1379,12 +1384,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533774</v>
+        <v>533738</v>
       </c>
       <c r="R8" t="n">
-        <v>6928715</v>
+        <v>6928768</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,12 +1453,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1572,45 +1572,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126182188</v>
+        <v>126176747</v>
       </c>
       <c r="B10" t="n">
-        <v>92535</v>
+        <v>98361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533653</v>
+        <v>533742</v>
       </c>
       <c r="R10" t="n">
-        <v>6928877</v>
+        <v>6928718</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,32 +1688,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126181209</v>
+        <v>126182188</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>92535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,13 +1723,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533731</v>
+        <v>533653</v>
       </c>
       <c r="R11" t="n">
-        <v>6928754</v>
+        <v>6928877</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126181693</v>
+        <v>126177259</v>
       </c>
       <c r="B12" t="n">
-        <v>91245</v>
+        <v>80083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,37 +1806,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533757</v>
+        <v>533735</v>
       </c>
       <c r="R12" t="n">
-        <v>6928745</v>
+        <v>6928726</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1866,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,22 +1895,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126177259</v>
+        <v>126181209</v>
       </c>
       <c r="B13" t="n">
-        <v>80083</v>
+        <v>91245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,42 +1918,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533735</v>
+        <v>533731</v>
       </c>
       <c r="R13" t="n">
-        <v>6928726</v>
+        <v>6928754</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1978,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,69 +2002,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126176747</v>
+        <v>126181693</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>91245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533742</v>
+        <v>533757</v>
       </c>
       <c r="R14" t="n">
-        <v>6928718</v>
+        <v>6928745</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,12 +2109,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3366,32 +3366,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126181871</v>
+        <v>126178155</v>
       </c>
       <c r="B26" t="n">
-        <v>78739</v>
+        <v>97245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3401,13 +3401,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533757</v>
+        <v>533696</v>
       </c>
       <c r="R26" t="n">
-        <v>6928745</v>
+        <v>6928789</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,12 +3461,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126178155</v>
+        <v>126181871</v>
       </c>
       <c r="B29" t="n">
-        <v>97245</v>
+        <v>78739</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533696</v>
+        <v>533757</v>
       </c>
       <c r="R29" t="n">
-        <v>6928789</v>
+        <v>6928745</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,12 +3800,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4030,32 +4030,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126181652</v>
+        <v>126176144</v>
       </c>
       <c r="B32" t="n">
-        <v>92535</v>
+        <v>80083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4065,13 +4065,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533745</v>
+        <v>533746</v>
       </c>
       <c r="R32" t="n">
-        <v>6928735</v>
+        <v>6928708</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4125,44 +4125,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126176144</v>
+        <v>126181652</v>
       </c>
       <c r="B33" t="n">
-        <v>80083</v>
+        <v>92535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533746</v>
+        <v>533745</v>
       </c>
       <c r="R33" t="n">
-        <v>6928708</v>
+        <v>6928735</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4232,57 +4232,61 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126181681</v>
+        <v>126180980</v>
       </c>
       <c r="B34" t="n">
-        <v>91541</v>
+        <v>98395</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533745</v>
+        <v>533724</v>
       </c>
       <c r="R34" t="n">
-        <v>6928735</v>
+        <v>6928748</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4314,7 +4318,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4324,7 +4328,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,37 +4355,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126180980</v>
+        <v>126175252</v>
       </c>
       <c r="B35" t="n">
-        <v>98395</v>
+        <v>98361</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4390,13 +4399,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533724</v>
+        <v>533816</v>
       </c>
       <c r="R35" t="n">
-        <v>6928748</v>
+        <v>6928686</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4425,7 +4434,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4435,7 +4444,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4450,66 +4459,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126175252</v>
+        <v>126177002</v>
       </c>
       <c r="B36" t="n">
-        <v>98361</v>
+        <v>78739</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533816</v>
+        <v>533732</v>
       </c>
       <c r="R36" t="n">
-        <v>6928686</v>
+        <v>6928727</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4578,32 +4578,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126177002</v>
+        <v>126178181</v>
       </c>
       <c r="B37" t="n">
-        <v>78739</v>
+        <v>80043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533732</v>
+        <v>533723</v>
       </c>
       <c r="R37" t="n">
-        <v>6928727</v>
+        <v>6928739</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4685,32 +4685,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126178181</v>
+        <v>126181681</v>
       </c>
       <c r="B38" t="n">
-        <v>80043</v>
+        <v>91541</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,13 +4720,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533723</v>
+        <v>533745</v>
       </c>
       <c r="R38" t="n">
-        <v>6928739</v>
+        <v>6928735</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4780,12 +4780,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126182027</v>
+        <v>126180836</v>
       </c>
       <c r="B40" t="n">
-        <v>91167</v>
+        <v>78980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4910,21 +4910,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4934,13 +4934,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533755</v>
+        <v>533708</v>
       </c>
       <c r="R40" t="n">
-        <v>6928865</v>
+        <v>6928798</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4994,12 +4994,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126180836</v>
+        <v>126182027</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>91167</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5124,21 +5124,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533708</v>
+        <v>533755</v>
       </c>
       <c r="R42" t="n">
-        <v>6928798</v>
+        <v>6928865</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,44 +5208,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126182304</v>
+        <v>126181218</v>
       </c>
       <c r="B43" t="n">
-        <v>92535</v>
+        <v>91541</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533624</v>
+        <v>533723</v>
       </c>
       <c r="R43" t="n">
-        <v>6928837</v>
+        <v>6928740</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5327,7 +5327,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126181218</v>
+        <v>126176695</v>
       </c>
       <c r="B44" t="n">
         <v>91541</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533723</v>
+        <v>533734</v>
       </c>
       <c r="R44" t="n">
-        <v>6928740</v>
+        <v>6928700</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5422,44 +5422,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126176695</v>
+        <v>126182304</v>
       </c>
       <c r="B45" t="n">
-        <v>91541</v>
+        <v>92535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5469,13 +5469,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533734</v>
+        <v>533624</v>
       </c>
       <c r="R45" t="n">
-        <v>6928700</v>
+        <v>6928837</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5529,69 +5529,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126175980</v>
+        <v>126182221</v>
       </c>
       <c r="B46" t="n">
-        <v>98361</v>
+        <v>92535</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533762</v>
+        <v>533640</v>
       </c>
       <c r="R46" t="n">
-        <v>6928707</v>
+        <v>6928856</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5620,7 +5611,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5630,7 +5621,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5645,12 +5636,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5764,48 +5755,57 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126182221</v>
+        <v>126175980</v>
       </c>
       <c r="B48" t="n">
-        <v>92535</v>
+        <v>98361</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533640</v>
+        <v>533762</v>
       </c>
       <c r="R48" t="n">
-        <v>6928856</v>
+        <v>6928707</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5859,12 +5859,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5978,54 +5978,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126177821</v>
+        <v>126182185</v>
       </c>
       <c r="B50" t="n">
-        <v>98361</v>
+        <v>78739</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533723</v>
+        <v>533637</v>
       </c>
       <c r="R50" t="n">
-        <v>6928726</v>
+        <v>6928864</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6094,7 +6085,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126182185</v>
+        <v>126180415</v>
       </c>
       <c r="B51" t="n">
         <v>78739</v>
@@ -6129,13 +6120,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533637</v>
+        <v>533678</v>
       </c>
       <c r="R51" t="n">
-        <v>6928864</v>
+        <v>6928776</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6164,7 +6155,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6174,7 +6165,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6189,44 +6180,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126180415</v>
+        <v>126175432</v>
       </c>
       <c r="B52" t="n">
-        <v>78739</v>
+        <v>80043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6236,13 +6227,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533678</v>
+        <v>533782</v>
       </c>
       <c r="R52" t="n">
-        <v>6928776</v>
+        <v>6928709</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6271,7 +6262,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6281,7 +6272,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6296,57 +6287,66 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126175432</v>
+        <v>126177821</v>
       </c>
       <c r="B53" t="n">
-        <v>80043</v>
+        <v>98361</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533782</v>
+        <v>533723</v>
       </c>
       <c r="R53" t="n">
-        <v>6928709</v>
+        <v>6928726</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6415,54 +6415,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126175256</v>
+        <v>126176512</v>
       </c>
       <c r="B54" t="n">
-        <v>98361</v>
+        <v>91245</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533811</v>
+        <v>533767</v>
       </c>
       <c r="R54" t="n">
-        <v>6928689</v>
+        <v>6928695</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6852,45 +6843,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126176512</v>
+        <v>126175256</v>
       </c>
       <c r="B58" t="n">
-        <v>91245</v>
+        <v>98361</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533767</v>
+        <v>533811</v>
       </c>
       <c r="R58" t="n">
-        <v>6928695</v>
+        <v>6928689</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6959,57 +6959,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126178221</v>
+        <v>126182236</v>
       </c>
       <c r="B59" t="n">
-        <v>98361</v>
+        <v>78739</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533693</v>
+        <v>533635</v>
       </c>
       <c r="R59" t="n">
-        <v>6928759</v>
+        <v>6928840</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7038,7 +7029,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7048,7 +7039,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7063,19 +7054,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126182366</v>
+        <v>126178221</v>
       </c>
       <c r="B60" t="n">
         <v>98361</v>
@@ -7103,20 +7094,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533589</v>
+        <v>533693</v>
       </c>
       <c r="R60" t="n">
-        <v>6928781</v>
+        <v>6928759</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,44 +7170,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126182236</v>
+        <v>126182366</v>
       </c>
       <c r="B61" t="n">
-        <v>78739</v>
+        <v>98361</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533635</v>
+        <v>533589</v>
       </c>
       <c r="R61" t="n">
-        <v>6928840</v>
+        <v>6928781</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7289,10 +7289,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126178007</v>
+        <v>126175788</v>
       </c>
       <c r="B62" t="n">
-        <v>91245</v>
+        <v>91541</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7300,21 +7300,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533723</v>
+        <v>533763</v>
       </c>
       <c r="R62" t="n">
-        <v>6928730</v>
+        <v>6928712</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7396,10 +7396,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126175788</v>
+        <v>126178007</v>
       </c>
       <c r="B63" t="n">
-        <v>91541</v>
+        <v>91245</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533763</v>
+        <v>533723</v>
       </c>
       <c r="R63" t="n">
-        <v>6928712</v>
+        <v>6928730</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7614,32 +7614,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126178312</v>
+        <v>126176239</v>
       </c>
       <c r="B65" t="n">
-        <v>91245</v>
+        <v>80119</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533708</v>
+        <v>533761</v>
       </c>
       <c r="R65" t="n">
-        <v>6928704</v>
+        <v>6928713</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7721,32 +7721,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126176239</v>
+        <v>126177726</v>
       </c>
       <c r="B66" t="n">
-        <v>80119</v>
+        <v>80083</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7756,10 +7756,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533761</v>
+        <v>533723</v>
       </c>
       <c r="R66" t="n">
-        <v>6928713</v>
+        <v>6928726</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7935,10 +7935,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126177726</v>
+        <v>126178312</v>
       </c>
       <c r="B68" t="n">
-        <v>80083</v>
+        <v>91245</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7946,21 +7946,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533723</v>
+        <v>533708</v>
       </c>
       <c r="R68" t="n">
-        <v>6928726</v>
+        <v>6928704</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8042,48 +8042,57 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126182129</v>
+        <v>126176659</v>
       </c>
       <c r="B69" t="n">
-        <v>92535</v>
+        <v>98361</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533717</v>
+        <v>533742</v>
       </c>
       <c r="R69" t="n">
-        <v>6928888</v>
+        <v>6928692</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8112,7 +8121,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8122,7 +8131,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8137,44 +8146,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126176685</v>
+        <v>126182129</v>
       </c>
       <c r="B70" t="n">
-        <v>91245</v>
+        <v>92535</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8184,13 +8193,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533743</v>
+        <v>533717</v>
       </c>
       <c r="R70" t="n">
-        <v>6928709</v>
+        <v>6928888</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8219,7 +8228,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8229,7 +8238,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8244,66 +8253,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126176659</v>
+        <v>126176685</v>
       </c>
       <c r="B71" t="n">
-        <v>98361</v>
+        <v>91245</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533742</v>
+        <v>533743</v>
       </c>
       <c r="R71" t="n">
-        <v>6928692</v>
+        <v>6928709</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9793,10 +9793,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126231142</v>
+        <v>126231168</v>
       </c>
       <c r="B86" t="n">
-        <v>80083</v>
+        <v>91245</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9804,21 +9804,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9827,14 +9827,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Käkbenet, Ånge, Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533702</v>
+        <v>533712</v>
       </c>
       <c r="R86" t="n">
-        <v>6928773</v>
+        <v>6928777</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126231168</v>
+        <v>126231142</v>
       </c>
       <c r="B87" t="n">
-        <v>91245</v>
+        <v>80083</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9928,14 +9928,14 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Käkbenet, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533712</v>
+        <v>533702</v>
       </c>
       <c r="R87" t="n">
-        <v>6928777</v>
+        <v>6928773</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -1465,32 +1465,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126182178</v>
+        <v>126182188</v>
       </c>
       <c r="B9" t="n">
-        <v>78739</v>
+        <v>92535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533652</v>
+        <v>533653</v>
       </c>
       <c r="R9" t="n">
-        <v>6928869</v>
+        <v>6928877</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,54 +1560,50 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126176747</v>
+        <v>126177259</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1616,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533742</v>
+        <v>533735</v>
       </c>
       <c r="R10" t="n">
-        <v>6928718</v>
+        <v>6928726</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,32 +1684,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126182188</v>
+        <v>126181209</v>
       </c>
       <c r="B11" t="n">
-        <v>92535</v>
+        <v>91245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,13 +1719,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533653</v>
+        <v>533731</v>
       </c>
       <c r="R11" t="n">
-        <v>6928877</v>
+        <v>6928754</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1754,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1764,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,22 +1779,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126177259</v>
+        <v>126181693</v>
       </c>
       <c r="B12" t="n">
-        <v>80083</v>
+        <v>91245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,42 +1802,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533735</v>
+        <v>533757</v>
       </c>
       <c r="R12" t="n">
-        <v>6928726</v>
+        <v>6928745</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1861,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1871,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,22 +1886,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126181209</v>
+        <v>126182178</v>
       </c>
       <c r="B13" t="n">
-        <v>91245</v>
+        <v>78739</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1909,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1933,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533731</v>
+        <v>533652</v>
       </c>
       <c r="R13" t="n">
-        <v>6928754</v>
+        <v>6928869</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1977,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,48 +2005,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126181693</v>
+        <v>126176747</v>
       </c>
       <c r="B14" t="n">
-        <v>91245</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533757</v>
+        <v>533742</v>
       </c>
       <c r="R14" t="n">
-        <v>6928745</v>
+        <v>6928718</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,12 +2109,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2237,57 +2237,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126178142</v>
+        <v>126182151</v>
       </c>
       <c r="B16" t="n">
-        <v>98395</v>
+        <v>91406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533722</v>
+        <v>533652</v>
       </c>
       <c r="R16" t="n">
-        <v>6928754</v>
+        <v>6928869</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2316,7 +2307,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2326,7 +2317,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,49 +2332,49 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126180591</v>
+        <v>126178142</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>98395</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2397,10 +2388,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533682</v>
+        <v>533722</v>
       </c>
       <c r="R17" t="n">
-        <v>6928792</v>
+        <v>6928754</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126182151</v>
+        <v>126180591</v>
       </c>
       <c r="B18" t="n">
-        <v>91406</v>
+        <v>98361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2480,37 +2471,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533652</v>
+        <v>533682</v>
       </c>
       <c r="R18" t="n">
-        <v>6928869</v>
+        <v>6928792</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,12 +2564,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3366,32 +3366,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126178155</v>
+        <v>126181871</v>
       </c>
       <c r="B26" t="n">
-        <v>97245</v>
+        <v>78739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3401,13 +3401,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533696</v>
+        <v>533757</v>
       </c>
       <c r="R26" t="n">
-        <v>6928789</v>
+        <v>6928745</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,66 +3461,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126175257</v>
+        <v>126178155</v>
       </c>
       <c r="B27" t="n">
-        <v>98361</v>
+        <v>97245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533799</v>
+        <v>533696</v>
       </c>
       <c r="R27" t="n">
-        <v>6928693</v>
+        <v>6928789</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3589,7 +3580,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126178017</v>
+        <v>126175257</v>
       </c>
       <c r="B28" t="n">
         <v>98361</v>
@@ -3619,7 +3610,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3633,10 +3624,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533723</v>
+        <v>533799</v>
       </c>
       <c r="R28" t="n">
-        <v>6928730</v>
+        <v>6928693</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3705,48 +3696,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126181871</v>
+        <v>126178017</v>
       </c>
       <c r="B29" t="n">
-        <v>78739</v>
+        <v>98361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533757</v>
+        <v>533723</v>
       </c>
       <c r="R29" t="n">
-        <v>6928745</v>
+        <v>6928730</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,12 +3800,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -5220,32 +5220,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126181218</v>
+        <v>126182304</v>
       </c>
       <c r="B43" t="n">
-        <v>91541</v>
+        <v>92535</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533723</v>
+        <v>533624</v>
       </c>
       <c r="R43" t="n">
-        <v>6928740</v>
+        <v>6928837</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5327,32 +5327,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126176695</v>
+        <v>126182221</v>
       </c>
       <c r="B44" t="n">
-        <v>91541</v>
+        <v>92535</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533734</v>
+        <v>533640</v>
       </c>
       <c r="R44" t="n">
-        <v>6928700</v>
+        <v>6928856</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5422,44 +5422,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126182304</v>
+        <v>126181218</v>
       </c>
       <c r="B45" t="n">
-        <v>92535</v>
+        <v>91541</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533624</v>
+        <v>533723</v>
       </c>
       <c r="R45" t="n">
-        <v>6928837</v>
+        <v>6928740</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5541,32 +5541,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126182221</v>
+        <v>126176695</v>
       </c>
       <c r="B46" t="n">
-        <v>92535</v>
+        <v>91541</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5576,13 +5576,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533640</v>
+        <v>533734</v>
       </c>
       <c r="R46" t="n">
-        <v>6928856</v>
+        <v>6928700</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5636,12 +5636,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -8042,57 +8042,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126176659</v>
+        <v>126182129</v>
       </c>
       <c r="B69" t="n">
-        <v>98361</v>
+        <v>92535</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533742</v>
+        <v>533717</v>
       </c>
       <c r="R69" t="n">
-        <v>6928692</v>
+        <v>6928888</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8121,7 +8112,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8131,7 +8122,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8146,44 +8137,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126182129</v>
+        <v>126176685</v>
       </c>
       <c r="B70" t="n">
-        <v>92535</v>
+        <v>91245</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8193,13 +8184,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533717</v>
+        <v>533743</v>
       </c>
       <c r="R70" t="n">
-        <v>6928888</v>
+        <v>6928709</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8228,7 +8219,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8238,7 +8229,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8253,57 +8244,66 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126176685</v>
+        <v>126176659</v>
       </c>
       <c r="B71" t="n">
-        <v>91245</v>
+        <v>98361</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533743</v>
+        <v>533742</v>
       </c>
       <c r="R71" t="n">
-        <v>6928709</v>
+        <v>6928692</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9387,48 +9387,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126230937</v>
+        <v>126231002</v>
       </c>
       <c r="B82" t="n">
-        <v>91541</v>
+        <v>98361</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Källberget, Ånge , Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533736</v>
+        <v>533741</v>
       </c>
       <c r="R82" t="n">
-        <v>6928738</v>
+        <v>6928734</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9488,49 +9489,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126231002</v>
+        <v>126230937</v>
       </c>
       <c r="B83" t="n">
-        <v>98361</v>
+        <v>91541</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Källberget, Ånge , Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533741</v>
+        <v>533736</v>
       </c>
       <c r="R83" t="n">
-        <v>6928734</v>
+        <v>6928738</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -2237,48 +2237,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126182151</v>
+        <v>126178142</v>
       </c>
       <c r="B16" t="n">
-        <v>91406</v>
+        <v>98395</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533652</v>
+        <v>533722</v>
       </c>
       <c r="R16" t="n">
-        <v>6928869</v>
+        <v>6928754</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2307,7 +2316,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2317,7 +2326,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,49 +2341,49 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126178142</v>
+        <v>126180591</v>
       </c>
       <c r="B17" t="n">
-        <v>98395</v>
+        <v>98361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2388,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533722</v>
+        <v>533682</v>
       </c>
       <c r="R17" t="n">
-        <v>6928754</v>
+        <v>6928792</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2460,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126180591</v>
+        <v>126182151</v>
       </c>
       <c r="B18" t="n">
-        <v>98361</v>
+        <v>91406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,46 +2480,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533682</v>
+        <v>533652</v>
       </c>
       <c r="R18" t="n">
-        <v>6928792</v>
+        <v>6928869</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,12 +2564,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -5220,32 +5220,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126182304</v>
+        <v>126181218</v>
       </c>
       <c r="B43" t="n">
-        <v>92535</v>
+        <v>91541</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533624</v>
+        <v>533723</v>
       </c>
       <c r="R43" t="n">
-        <v>6928837</v>
+        <v>6928740</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5327,32 +5327,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126182221</v>
+        <v>126176695</v>
       </c>
       <c r="B44" t="n">
-        <v>92535</v>
+        <v>91541</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533640</v>
+        <v>533734</v>
       </c>
       <c r="R44" t="n">
-        <v>6928856</v>
+        <v>6928700</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5422,44 +5422,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126181218</v>
+        <v>126182304</v>
       </c>
       <c r="B45" t="n">
-        <v>91541</v>
+        <v>92535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533723</v>
+        <v>533624</v>
       </c>
       <c r="R45" t="n">
-        <v>6928740</v>
+        <v>6928837</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5541,32 +5541,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126176695</v>
+        <v>126182221</v>
       </c>
       <c r="B46" t="n">
-        <v>91541</v>
+        <v>92535</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5576,13 +5576,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533734</v>
+        <v>533640</v>
       </c>
       <c r="R46" t="n">
-        <v>6928700</v>
+        <v>6928856</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5636,12 +5636,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5871,45 +5871,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126175215</v>
+        <v>126177821</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533811</v>
+        <v>533723</v>
       </c>
       <c r="R49" t="n">
-        <v>6928661</v>
+        <v>6928726</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5978,10 +5987,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126182185</v>
+        <v>126175215</v>
       </c>
       <c r="B50" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5989,21 +5998,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6013,10 +6022,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533637</v>
+        <v>533811</v>
       </c>
       <c r="R50" t="n">
-        <v>6928864</v>
+        <v>6928661</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6085,7 +6094,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126180415</v>
+        <v>126182185</v>
       </c>
       <c r="B51" t="n">
         <v>78739</v>
@@ -6120,13 +6129,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533678</v>
+        <v>533637</v>
       </c>
       <c r="R51" t="n">
-        <v>6928776</v>
+        <v>6928864</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6155,7 +6164,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6165,7 +6174,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6180,44 +6189,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126175432</v>
+        <v>126180415</v>
       </c>
       <c r="B52" t="n">
-        <v>80043</v>
+        <v>78739</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6227,13 +6236,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533782</v>
+        <v>533678</v>
       </c>
       <c r="R52" t="n">
-        <v>6928709</v>
+        <v>6928776</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6262,7 +6271,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6272,7 +6281,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6287,66 +6296,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126177821</v>
+        <v>126175432</v>
       </c>
       <c r="B53" t="n">
-        <v>98361</v>
+        <v>80043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533723</v>
+        <v>533782</v>
       </c>
       <c r="R53" t="n">
-        <v>6928726</v>
+        <v>6928709</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6415,10 +6415,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126176512</v>
+        <v>126182214</v>
       </c>
       <c r="B54" t="n">
-        <v>91245</v>
+        <v>78739</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6426,21 +6426,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6450,13 +6450,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533767</v>
+        <v>533640</v>
       </c>
       <c r="R54" t="n">
-        <v>6928695</v>
+        <v>6928855</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6510,19 +6510,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126182214</v>
+        <v>126181960</v>
       </c>
       <c r="B55" t="n">
         <v>78739</v>
@@ -6557,10 +6557,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533640</v>
+        <v>533769</v>
       </c>
       <c r="R55" t="n">
-        <v>6928855</v>
+        <v>6928852</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6629,7 +6629,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126181960</v>
+        <v>126182040</v>
       </c>
       <c r="B56" t="n">
         <v>78739</v>
@@ -6664,10 +6664,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533769</v>
+        <v>533719</v>
       </c>
       <c r="R56" t="n">
-        <v>6928852</v>
+        <v>6928884</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6736,48 +6736,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126182040</v>
+        <v>126175256</v>
       </c>
       <c r="B57" t="n">
-        <v>78739</v>
+        <v>98361</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533719</v>
+        <v>533811</v>
       </c>
       <c r="R57" t="n">
-        <v>6928884</v>
+        <v>6928689</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6806,7 +6815,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6816,7 +6825,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6831,66 +6840,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126175256</v>
+        <v>126176512</v>
       </c>
       <c r="B58" t="n">
-        <v>98361</v>
+        <v>91245</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533811</v>
+        <v>533767</v>
       </c>
       <c r="R58" t="n">
-        <v>6928689</v>
+        <v>6928695</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6959,48 +6959,57 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126182236</v>
+        <v>126178221</v>
       </c>
       <c r="B59" t="n">
-        <v>78739</v>
+        <v>98361</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533635</v>
+        <v>533693</v>
       </c>
       <c r="R59" t="n">
-        <v>6928840</v>
+        <v>6928759</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7029,7 +7038,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7039,7 +7048,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7054,69 +7063,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126178221</v>
+        <v>126182236</v>
       </c>
       <c r="B60" t="n">
-        <v>98361</v>
+        <v>78739</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533693</v>
+        <v>533635</v>
       </c>
       <c r="R60" t="n">
-        <v>6928759</v>
+        <v>6928840</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,12 +7170,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -1121,38 +1121,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126182207</v>
+        <v>126180936</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>55</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1161,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533644</v>
+        <v>533738</v>
       </c>
       <c r="R6" t="n">
-        <v>6928860</v>
+        <v>6928768</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,12 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1354,37 +1348,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126180936</v>
+        <v>126182207</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>55</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1393,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533738</v>
+        <v>533644</v>
       </c>
       <c r="R8" t="n">
-        <v>6928768</v>
+        <v>6928860</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1433,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3147,32 +3147,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126176059</v>
+        <v>126181048</v>
       </c>
       <c r="B24" t="n">
-        <v>91819</v>
+        <v>80083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533746</v>
+        <v>533733</v>
       </c>
       <c r="R24" t="n">
-        <v>6928708</v>
+        <v>6928745</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3227,7 +3227,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer rikligt på två aspar och även en gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3242,44 +3247,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126181048</v>
+        <v>126176059</v>
       </c>
       <c r="B25" t="n">
-        <v>80083</v>
+        <v>91819</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3289,13 +3294,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533733</v>
+        <v>533746</v>
       </c>
       <c r="R25" t="n">
-        <v>6928745</v>
+        <v>6928708</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,7 +3329,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3339,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växer rikligt på två aspar och även en gran</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,44 +3354,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126181871</v>
+        <v>126178155</v>
       </c>
       <c r="B26" t="n">
-        <v>78739</v>
+        <v>97245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3401,13 +3401,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533757</v>
+        <v>533696</v>
       </c>
       <c r="R26" t="n">
-        <v>6928745</v>
+        <v>6928789</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,57 +3461,66 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126178155</v>
+        <v>126175257</v>
       </c>
       <c r="B27" t="n">
-        <v>97245</v>
+        <v>98361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533696</v>
+        <v>533799</v>
       </c>
       <c r="R27" t="n">
-        <v>6928789</v>
+        <v>6928693</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3580,7 +3589,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126175257</v>
+        <v>126178017</v>
       </c>
       <c r="B28" t="n">
         <v>98361</v>
@@ -3610,7 +3619,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3624,10 +3633,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533799</v>
+        <v>533723</v>
       </c>
       <c r="R28" t="n">
-        <v>6928693</v>
+        <v>6928730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3696,57 +3705,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126178017</v>
+        <v>126181871</v>
       </c>
       <c r="B29" t="n">
-        <v>98361</v>
+        <v>78739</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533723</v>
+        <v>533757</v>
       </c>
       <c r="R29" t="n">
-        <v>6928730</v>
+        <v>6928745</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,12 +3800,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4244,37 +4244,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126180980</v>
+        <v>126175252</v>
       </c>
       <c r="B34" t="n">
-        <v>98395</v>
+        <v>98361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4283,13 +4288,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533724</v>
+        <v>533816</v>
       </c>
       <c r="R34" t="n">
-        <v>6928748</v>
+        <v>6928686</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4318,7 +4323,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4328,7 +4333,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4343,69 +4348,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126175252</v>
+        <v>126181681</v>
       </c>
       <c r="B35" t="n">
-        <v>98361</v>
+        <v>91541</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533816</v>
+        <v>533745</v>
       </c>
       <c r="R35" t="n">
-        <v>6928686</v>
+        <v>6928735</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4434,7 +4430,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4444,7 +4440,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4459,60 +4455,64 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126177002</v>
+        <v>126180980</v>
       </c>
       <c r="B36" t="n">
-        <v>78739</v>
+        <v>98395</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>219874</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533732</v>
+        <v>533724</v>
       </c>
       <c r="R36" t="n">
-        <v>6928727</v>
+        <v>6928748</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4566,44 +4566,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126178181</v>
+        <v>126177002</v>
       </c>
       <c r="B37" t="n">
-        <v>80043</v>
+        <v>78739</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533723</v>
+        <v>533732</v>
       </c>
       <c r="R37" t="n">
-        <v>6928739</v>
+        <v>6928727</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4685,32 +4685,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126181681</v>
+        <v>126178181</v>
       </c>
       <c r="B38" t="n">
-        <v>91541</v>
+        <v>80043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,13 +4720,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533745</v>
+        <v>533723</v>
       </c>
       <c r="R38" t="n">
-        <v>6928735</v>
+        <v>6928739</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4780,12 +4780,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5871,54 +5871,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126177821</v>
+        <v>126175215</v>
       </c>
       <c r="B49" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533723</v>
+        <v>533811</v>
       </c>
       <c r="R49" t="n">
-        <v>6928726</v>
+        <v>6928661</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5987,10 +5978,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126175215</v>
+        <v>126182185</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5998,21 +5989,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6022,10 +6013,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533811</v>
+        <v>533637</v>
       </c>
       <c r="R50" t="n">
-        <v>6928661</v>
+        <v>6928864</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6094,7 +6085,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126182185</v>
+        <v>126180415</v>
       </c>
       <c r="B51" t="n">
         <v>78739</v>
@@ -6129,13 +6120,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533637</v>
+        <v>533678</v>
       </c>
       <c r="R51" t="n">
-        <v>6928864</v>
+        <v>6928776</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6164,7 +6155,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6174,7 +6165,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6189,44 +6180,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126180415</v>
+        <v>126175432</v>
       </c>
       <c r="B52" t="n">
-        <v>78739</v>
+        <v>80043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6236,13 +6227,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533678</v>
+        <v>533782</v>
       </c>
       <c r="R52" t="n">
-        <v>6928776</v>
+        <v>6928709</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6271,7 +6262,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6281,7 +6272,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6296,57 +6287,66 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126175432</v>
+        <v>126177821</v>
       </c>
       <c r="B53" t="n">
-        <v>80043</v>
+        <v>98361</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533782</v>
+        <v>533723</v>
       </c>
       <c r="R53" t="n">
-        <v>6928709</v>
+        <v>6928726</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -8042,48 +8042,57 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126182129</v>
+        <v>126176659</v>
       </c>
       <c r="B69" t="n">
-        <v>92535</v>
+        <v>98361</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533717</v>
+        <v>533742</v>
       </c>
       <c r="R69" t="n">
-        <v>6928888</v>
+        <v>6928692</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8112,7 +8121,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8122,7 +8131,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8137,44 +8146,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emma Sundvisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126176685</v>
+        <v>126182129</v>
       </c>
       <c r="B70" t="n">
-        <v>91245</v>
+        <v>92535</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8184,13 +8193,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533743</v>
+        <v>533717</v>
       </c>
       <c r="R70" t="n">
-        <v>6928709</v>
+        <v>6928888</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8219,7 +8228,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8229,7 +8238,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8244,66 +8253,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Emma Sundvisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126176659</v>
+        <v>126176685</v>
       </c>
       <c r="B71" t="n">
-        <v>98361</v>
+        <v>91245</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Källberget, Källberget, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533742</v>
+        <v>533743</v>
       </c>
       <c r="R71" t="n">
-        <v>6928692</v>
+        <v>6928709</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9387,49 +9387,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126231002</v>
+        <v>126230937</v>
       </c>
       <c r="B82" t="n">
-        <v>98361</v>
+        <v>91541</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Källberget, Ånge , Mpd</t>
+          <t>Källberget, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533741</v>
+        <v>533736</v>
       </c>
       <c r="R82" t="n">
-        <v>6928734</v>
+        <v>6928738</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9489,48 +9488,49 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126230937</v>
+        <v>126231002</v>
       </c>
       <c r="B83" t="n">
-        <v>91541</v>
+        <v>98361</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Källberget, Ånge, Mpd</t>
+          <t>Källberget, Ånge , Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533736</v>
+        <v>533741</v>
       </c>
       <c r="R83" t="n">
-        <v>6928738</v>
+        <v>6928734</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -9998,7 +9998,7 @@
         <v>127048363</v>
       </c>
       <c r="B88" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>127046229</v>
       </c>
       <c r="B89" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>127045743</v>
       </c>
       <c r="B90" t="n">
-        <v>91819</v>
+        <v>91893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>127046237</v>
       </c>
       <c r="B91" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>127045952</v>
       </c>
       <c r="B92" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>127049793</v>
       </c>
       <c r="B93" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10587,10 +10587,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127049534</v>
+        <v>127051986</v>
       </c>
       <c r="B94" t="n">
-        <v>80084</v>
+        <v>91615</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10598,21 +10598,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127051986</v>
+        <v>127049534</v>
       </c>
       <c r="B95" t="n">
-        <v>91541</v>
+        <v>80115</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10784,7 +10784,7 @@
         <v>127048135</v>
       </c>
       <c r="B96" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>127051933</v>
       </c>
       <c r="B97" t="n">
-        <v>91655</v>
+        <v>91729</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10975,32 +10975,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127051964</v>
+        <v>127046331</v>
       </c>
       <c r="B98" t="n">
-        <v>98361</v>
+        <v>79629</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11072,32 +11072,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127046331</v>
+        <v>127051964</v>
       </c>
       <c r="B99" t="n">
-        <v>79598</v>
+        <v>98436</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11172,7 +11172,7 @@
         <v>127048088</v>
       </c>
       <c r="B100" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>127047110</v>
       </c>
       <c r="B101" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>127047261</v>
       </c>
       <c r="B102" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>127047986</v>
       </c>
       <c r="B103" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11557,10 +11557,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127046342</v>
+        <v>127048180</v>
       </c>
       <c r="B104" t="n">
-        <v>92535</v>
+        <v>80074</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11568,21 +11568,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127048180</v>
+        <v>127046342</v>
       </c>
       <c r="B105" t="n">
-        <v>80043</v>
+        <v>92609</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11665,21 +11665,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -9998,7 +9998,7 @@
         <v>127048363</v>
       </c>
       <c r="B88" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>127046229</v>
       </c>
       <c r="B89" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>127045743</v>
       </c>
       <c r="B90" t="n">
-        <v>91893</v>
+        <v>91899</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>127046237</v>
       </c>
       <c r="B91" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>127045952</v>
       </c>
       <c r="B92" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>127049793</v>
       </c>
       <c r="B93" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>127051986</v>
       </c>
       <c r="B94" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>127049534</v>
       </c>
       <c r="B95" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>127048135</v>
       </c>
       <c r="B96" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>127051933</v>
       </c>
       <c r="B97" t="n">
-        <v>91729</v>
+        <v>91735</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>127046331</v>
       </c>
       <c r="B98" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11072,10 +11072,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127051964</v>
+        <v>127048146</v>
       </c>
       <c r="B99" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>127048088</v>
       </c>
       <c r="B100" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>127047110</v>
       </c>
       <c r="B101" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>127047261</v>
       </c>
       <c r="B102" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>127047986</v>
       </c>
       <c r="B103" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>127048180</v>
       </c>
       <c r="B104" t="n">
-        <v>80074</v>
+        <v>80077</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>127046342</v>
       </c>
       <c r="B105" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -10587,10 +10587,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127051986</v>
+        <v>127049534</v>
       </c>
       <c r="B94" t="n">
-        <v>91621</v>
+        <v>80118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10598,21 +10598,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127049534</v>
+        <v>127051986</v>
       </c>
       <c r="B95" t="n">
-        <v>80118</v>
+        <v>91621</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127048180</v>
+        <v>127046342</v>
       </c>
       <c r="B104" t="n">
-        <v>80077</v>
+        <v>92615</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11568,21 +11568,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127046342</v>
+        <v>127048180</v>
       </c>
       <c r="B105" t="n">
-        <v>92615</v>
+        <v>80077</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11665,21 +11665,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -10192,7 +10192,7 @@
         <v>127045743</v>
       </c>
       <c r="B90" t="n">
-        <v>91899</v>
+        <v>91900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>127045952</v>
       </c>
       <c r="B92" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>127049793</v>
       </c>
       <c r="B93" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>127051986</v>
       </c>
       <c r="B95" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>127051933</v>
       </c>
       <c r="B97" t="n">
-        <v>91735</v>
+        <v>91736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>127048146</v>
       </c>
       <c r="B99" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>127048088</v>
       </c>
       <c r="B100" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>127047110</v>
       </c>
       <c r="B101" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>127047261</v>
       </c>
       <c r="B102" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>127046342</v>
       </c>
       <c r="B104" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -10975,32 +10975,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127046331</v>
+        <v>127051964</v>
       </c>
       <c r="B98" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11072,32 +11072,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127048146</v>
+        <v>127046331</v>
       </c>
       <c r="B99" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -10189,32 +10189,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127045743</v>
+        <v>127046237</v>
       </c>
       <c r="B90" t="n">
-        <v>91900</v>
+        <v>79603</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>760</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10224,10 +10224,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533669</v>
+        <v>533679</v>
       </c>
       <c r="R90" t="n">
-        <v>6928742</v>
+        <v>6928782</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10257,19 +10257,9 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>10:23</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10296,32 +10286,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127046237</v>
+        <v>127045743</v>
       </c>
       <c r="B91" t="n">
-        <v>79603</v>
+        <v>91900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>760</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10331,10 +10321,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533679</v>
+        <v>533669</v>
       </c>
       <c r="R91" t="n">
-        <v>6928782</v>
+        <v>6928742</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10364,9 +10354,19 @@
           <t>2025-07-31</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -10975,32 +10975,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127051964</v>
+        <v>127046331</v>
       </c>
       <c r="B98" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11072,32 +11072,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127046331</v>
+        <v>127051964</v>
       </c>
       <c r="B99" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127046342</v>
+        <v>127048180</v>
       </c>
       <c r="B104" t="n">
-        <v>92616</v>
+        <v>80077</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11568,21 +11568,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127048180</v>
+        <v>127046342</v>
       </c>
       <c r="B105" t="n">
-        <v>80077</v>
+        <v>92616</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11665,21 +11665,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -9998,7 +9998,7 @@
         <v>127048363</v>
       </c>
       <c r="B88" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>127046229</v>
       </c>
       <c r="B89" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10189,32 +10189,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127046237</v>
+        <v>127045743</v>
       </c>
       <c r="B90" t="n">
-        <v>79603</v>
+        <v>91904</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>760</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10224,10 +10224,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533679</v>
+        <v>533669</v>
       </c>
       <c r="R90" t="n">
-        <v>6928782</v>
+        <v>6928742</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10257,9 +10257,19 @@
           <t>2025-07-31</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10286,32 +10296,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127045743</v>
+        <v>127046237</v>
       </c>
       <c r="B91" t="n">
-        <v>91900</v>
+        <v>79607</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>760</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10321,10 +10331,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533669</v>
+        <v>533679</v>
       </c>
       <c r="R91" t="n">
-        <v>6928742</v>
+        <v>6928782</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10354,19 +10364,9 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>10:23</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10396,7 +10396,7 @@
         <v>127045952</v>
       </c>
       <c r="B92" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>127049793</v>
       </c>
       <c r="B93" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10587,10 +10587,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127049534</v>
+        <v>127051986</v>
       </c>
       <c r="B94" t="n">
-        <v>80118</v>
+        <v>91626</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10598,21 +10598,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127051986</v>
+        <v>127049534</v>
       </c>
       <c r="B95" t="n">
-        <v>91622</v>
+        <v>80122</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10784,7 +10784,7 @@
         <v>127048135</v>
       </c>
       <c r="B96" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>127051933</v>
       </c>
       <c r="B97" t="n">
-        <v>91736</v>
+        <v>91740</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>127046331</v>
       </c>
       <c r="B98" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11072,10 +11072,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127051964</v>
+        <v>127048146</v>
       </c>
       <c r="B99" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>127048088</v>
       </c>
       <c r="B100" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>127047110</v>
       </c>
       <c r="B101" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>127047261</v>
       </c>
       <c r="B102" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>127047986</v>
       </c>
       <c r="B103" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>127048180</v>
       </c>
       <c r="B104" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>127046342</v>
       </c>
       <c r="B105" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -10587,10 +10587,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127051986</v>
+        <v>127049534</v>
       </c>
       <c r="B94" t="n">
-        <v>91626</v>
+        <v>80122</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10598,21 +10598,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127049534</v>
+        <v>127051986</v>
       </c>
       <c r="B95" t="n">
-        <v>80122</v>
+        <v>91626</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127048180</v>
+        <v>127046342</v>
       </c>
       <c r="B104" t="n">
-        <v>80081</v>
+        <v>92620</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11568,21 +11568,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127046342</v>
+        <v>127048180</v>
       </c>
       <c r="B105" t="n">
-        <v>92620</v>
+        <v>80081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11665,21 +11665,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -10189,32 +10189,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127045743</v>
+        <v>127046237</v>
       </c>
       <c r="B90" t="n">
-        <v>91904</v>
+        <v>79607</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>760</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10224,10 +10224,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533669</v>
+        <v>533679</v>
       </c>
       <c r="R90" t="n">
-        <v>6928742</v>
+        <v>6928782</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10257,19 +10257,9 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>10:23</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10296,32 +10286,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127046237</v>
+        <v>127045743</v>
       </c>
       <c r="B91" t="n">
-        <v>79607</v>
+        <v>91904</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>760</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10331,10 +10321,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533679</v>
+        <v>533669</v>
       </c>
       <c r="R91" t="n">
-        <v>6928782</v>
+        <v>6928742</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10364,9 +10354,19 @@
           <t>2025-07-31</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10587,10 +10587,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127049534</v>
+        <v>127051986</v>
       </c>
       <c r="B94" t="n">
-        <v>80122</v>
+        <v>91626</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10598,21 +10598,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127051986</v>
+        <v>127049534</v>
       </c>
       <c r="B95" t="n">
-        <v>91626</v>
+        <v>80122</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10975,32 +10975,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127046331</v>
+        <v>127048146</v>
       </c>
       <c r="B98" t="n">
-        <v>79636</v>
+        <v>98448</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11072,32 +11072,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127048146</v>
+        <v>127046331</v>
       </c>
       <c r="B99" t="n">
-        <v>98447</v>
+        <v>79636</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11269,7 +11269,7 @@
         <v>127047110</v>
       </c>
       <c r="B101" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11557,10 +11557,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127046342</v>
+        <v>127048180</v>
       </c>
       <c r="B104" t="n">
-        <v>92620</v>
+        <v>80081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11568,21 +11568,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127048180</v>
+        <v>127046342</v>
       </c>
       <c r="B105" t="n">
-        <v>80081</v>
+        <v>92620</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11665,21 +11665,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -11557,10 +11557,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127048180</v>
+        <v>127046342</v>
       </c>
       <c r="B104" t="n">
-        <v>80081</v>
+        <v>92620</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11568,21 +11568,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127046342</v>
+        <v>127048180</v>
       </c>
       <c r="B105" t="n">
-        <v>92620</v>
+        <v>80081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11665,21 +11665,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -9998,7 +9998,7 @@
         <v>127048363</v>
       </c>
       <c r="B88" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>127046229</v>
       </c>
       <c r="B89" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10189,32 +10189,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127046237</v>
+        <v>127045743</v>
       </c>
       <c r="B90" t="n">
-        <v>79607</v>
+        <v>91906</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>760</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10224,10 +10224,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533679</v>
+        <v>533669</v>
       </c>
       <c r="R90" t="n">
-        <v>6928782</v>
+        <v>6928742</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10257,9 +10257,19 @@
           <t>2025-07-31</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10286,32 +10296,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127045743</v>
+        <v>127046237</v>
       </c>
       <c r="B91" t="n">
-        <v>91904</v>
+        <v>79609</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>760</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10321,10 +10331,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533669</v>
+        <v>533679</v>
       </c>
       <c r="R91" t="n">
-        <v>6928742</v>
+        <v>6928782</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10354,19 +10364,9 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>10:23</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10396,7 +10396,7 @@
         <v>127045952</v>
       </c>
       <c r="B92" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>127049793</v>
       </c>
       <c r="B93" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10587,10 +10587,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127051986</v>
+        <v>127049534</v>
       </c>
       <c r="B94" t="n">
-        <v>91626</v>
+        <v>80124</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10598,21 +10598,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127049534</v>
+        <v>127051986</v>
       </c>
       <c r="B95" t="n">
-        <v>80122</v>
+        <v>91628</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10784,7 +10784,7 @@
         <v>127048135</v>
       </c>
       <c r="B96" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>127051933</v>
       </c>
       <c r="B97" t="n">
-        <v>91740</v>
+        <v>91742</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10975,10 +10975,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127048146</v>
+        <v>127051964</v>
       </c>
       <c r="B98" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>127046331</v>
       </c>
       <c r="B99" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11169,32 +11169,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127048088</v>
+        <v>127047110</v>
       </c>
       <c r="B100" t="n">
-        <v>91784</v>
+        <v>105488</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11266,32 +11266,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127047110</v>
+        <v>127048088</v>
       </c>
       <c r="B101" t="n">
-        <v>105486</v>
+        <v>91786</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
         <v>127047261</v>
       </c>
       <c r="B102" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>127047986</v>
       </c>
       <c r="B103" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>127046342</v>
       </c>
       <c r="B104" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>127048180</v>
       </c>
       <c r="B105" t="n">
-        <v>80081</v>
+        <v>80083</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -10587,10 +10587,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127049534</v>
+        <v>127051986</v>
       </c>
       <c r="B94" t="n">
-        <v>80124</v>
+        <v>91628</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10598,21 +10598,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127051986</v>
+        <v>127049534</v>
       </c>
       <c r="B95" t="n">
-        <v>91628</v>
+        <v>80124</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11169,32 +11169,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127047110</v>
+        <v>127048088</v>
       </c>
       <c r="B100" t="n">
-        <v>105488</v>
+        <v>91786</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11266,32 +11266,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127048088</v>
+        <v>127047110</v>
       </c>
       <c r="B101" t="n">
-        <v>91786</v>
+        <v>105488</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11557,10 +11557,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127046342</v>
+        <v>127048180</v>
       </c>
       <c r="B104" t="n">
-        <v>92622</v>
+        <v>80083</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11568,21 +11568,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127048180</v>
+        <v>127046342</v>
       </c>
       <c r="B105" t="n">
-        <v>80083</v>
+        <v>92622</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11665,21 +11665,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -10975,32 +10975,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127051964</v>
+        <v>127046331</v>
       </c>
       <c r="B98" t="n">
-        <v>98450</v>
+        <v>79638</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11072,32 +11072,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127046331</v>
+        <v>127048146</v>
       </c>
       <c r="B99" t="n">
-        <v>79638</v>
+        <v>98450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -10192,7 +10192,7 @@
         <v>127045743</v>
       </c>
       <c r="B90" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>127045952</v>
       </c>
       <c r="B92" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>127049793</v>
       </c>
       <c r="B93" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10587,10 +10587,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127051986</v>
+        <v>127049534</v>
       </c>
       <c r="B94" t="n">
-        <v>91628</v>
+        <v>80124</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10598,21 +10598,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127049534</v>
+        <v>127051986</v>
       </c>
       <c r="B95" t="n">
-        <v>80124</v>
+        <v>91634</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10881,7 +10881,7 @@
         <v>127051933</v>
       </c>
       <c r="B97" t="n">
-        <v>91742</v>
+        <v>91748</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10975,32 +10975,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127046331</v>
+        <v>127048146</v>
       </c>
       <c r="B98" t="n">
-        <v>79638</v>
+        <v>98456</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11072,32 +11072,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127048146</v>
+        <v>127046331</v>
       </c>
       <c r="B99" t="n">
-        <v>98450</v>
+        <v>79638</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11169,32 +11169,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127048088</v>
+        <v>127047110</v>
       </c>
       <c r="B100" t="n">
-        <v>91786</v>
+        <v>105494</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11266,32 +11266,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127047110</v>
+        <v>127048088</v>
       </c>
       <c r="B101" t="n">
-        <v>105488</v>
+        <v>91792</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
         <v>127047261</v>
       </c>
       <c r="B102" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>127046342</v>
       </c>
       <c r="B105" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -10587,10 +10587,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127049534</v>
+        <v>127051986</v>
       </c>
       <c r="B94" t="n">
-        <v>80124</v>
+        <v>91637</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10598,21 +10598,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127051986</v>
+        <v>127049534</v>
       </c>
       <c r="B95" t="n">
-        <v>91634</v>
+        <v>80127</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10695,21 +10695,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10784,7 +10784,7 @@
         <v>127048135</v>
       </c>
       <c r="B96" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>127051933</v>
       </c>
       <c r="B97" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10975,10 +10975,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127048146</v>
+        <v>127051964</v>
       </c>
       <c r="B98" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>127046331</v>
       </c>
       <c r="B99" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11169,32 +11169,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127047110</v>
+        <v>127048088</v>
       </c>
       <c r="B100" t="n">
-        <v>105494</v>
+        <v>91795</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11266,32 +11266,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127048088</v>
+        <v>127047110</v>
       </c>
       <c r="B101" t="n">
-        <v>91792</v>
+        <v>105497</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
         <v>127047261</v>
       </c>
       <c r="B102" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>127047986</v>
       </c>
       <c r="B103" t="n">
-        <v>80027</v>
+        <v>80030</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>127048180</v>
       </c>
       <c r="B104" t="n">
-        <v>80083</v>
+        <v>80086</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>127046342</v>
       </c>
       <c r="B105" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -10590,7 +10590,7 @@
         <v>127051986</v>
       </c>
       <c r="B94" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>127049534</v>
       </c>
       <c r="B95" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>127048135</v>
       </c>
       <c r="B96" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>127051933</v>
       </c>
       <c r="B97" t="n">
-        <v>91751</v>
+        <v>91759</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>127051964</v>
       </c>
       <c r="B98" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>127046331</v>
       </c>
       <c r="B99" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>127048088</v>
       </c>
       <c r="B100" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>127047110</v>
       </c>
       <c r="B101" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>127047261</v>
       </c>
       <c r="B102" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>127047986</v>
       </c>
       <c r="B103" t="n">
-        <v>80030</v>
+        <v>80036</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11557,10 +11557,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127048180</v>
+        <v>127046342</v>
       </c>
       <c r="B104" t="n">
-        <v>80086</v>
+        <v>92639</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11568,21 +11568,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127046342</v>
+        <v>127048180</v>
       </c>
       <c r="B105" t="n">
-        <v>92631</v>
+        <v>80092</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11665,21 +11665,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -10590,7 +10590,7 @@
         <v>127051986</v>
       </c>
       <c r="B94" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>127051933</v>
       </c>
       <c r="B97" t="n">
-        <v>91759</v>
+        <v>91760</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>127051964</v>
       </c>
       <c r="B98" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11169,32 +11169,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127048088</v>
+        <v>127047110</v>
       </c>
       <c r="B100" t="n">
-        <v>91803</v>
+        <v>105506</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11266,32 +11266,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127047110</v>
+        <v>127048088</v>
       </c>
       <c r="B101" t="n">
-        <v>105505</v>
+        <v>91804</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
         <v>127047261</v>
       </c>
       <c r="B102" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11557,10 +11557,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127046342</v>
+        <v>127048180</v>
       </c>
       <c r="B104" t="n">
-        <v>92639</v>
+        <v>80092</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11568,21 +11568,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11654,10 +11654,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127048180</v>
+        <v>127046342</v>
       </c>
       <c r="B105" t="n">
-        <v>80092</v>
+        <v>92640</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11665,21 +11665,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -1124,7 +1124,7 @@
         <v>126182207</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -1124,7 +1124,7 @@
         <v>126182207</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -1124,7 +1124,7 @@
         <v>126182207</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -9998,7 +9998,7 @@
         <v>127048363</v>
       </c>
       <c r="B88" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>127046229</v>
       </c>
       <c r="B89" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>127045743</v>
       </c>
       <c r="B90" t="n">
-        <v>91912</v>
+        <v>91893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>127046237</v>
       </c>
       <c r="B91" t="n">
-        <v>79609</v>
+        <v>79600</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>127045952</v>
       </c>
       <c r="B92" t="n">
-        <v>92628</v>
+        <v>92609</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>127049793</v>
       </c>
       <c r="B93" t="n">
-        <v>91634</v>
+        <v>91615</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>127051986</v>
       </c>
       <c r="B94" t="n">
-        <v>91646</v>
+        <v>91615</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>127049534</v>
       </c>
       <c r="B95" t="n">
-        <v>80133</v>
+        <v>80115</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>127048135</v>
       </c>
       <c r="B96" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>127051933</v>
       </c>
       <c r="B97" t="n">
-        <v>91760</v>
+        <v>91729</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10975,32 +10975,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127051964</v>
+        <v>127046331</v>
       </c>
       <c r="B98" t="n">
-        <v>98468</v>
+        <v>79629</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11072,32 +11072,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127046331</v>
+        <v>127051964</v>
       </c>
       <c r="B99" t="n">
-        <v>79647</v>
+        <v>98436</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11169,32 +11169,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127047110</v>
+        <v>127048088</v>
       </c>
       <c r="B100" t="n">
-        <v>105506</v>
+        <v>91773</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11266,32 +11266,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127048088</v>
+        <v>127047110</v>
       </c>
       <c r="B101" t="n">
-        <v>91804</v>
+        <v>105471</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
         <v>127047261</v>
       </c>
       <c r="B102" t="n">
-        <v>97351</v>
+        <v>97320</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>127047986</v>
       </c>
       <c r="B103" t="n">
-        <v>80036</v>
+        <v>80018</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>127048180</v>
       </c>
       <c r="B104" t="n">
-        <v>80092</v>
+        <v>80074</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>127046342</v>
       </c>
       <c r="B105" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 64523-2023 artfynd.xlsx
+++ b/artfynd/A 64523-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY135"/>
+  <dimension ref="A1:AZ135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786507</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786508</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786510</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786529</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786532</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126230878</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786502</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126175788</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126176544</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126176695</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1843,6 +1898,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126181218</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1950,6 +2010,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126181681</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2051,6 +2116,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126230916</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2152,6 +2222,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126230937</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2253,6 +2328,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126230947</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2350,6 +2430,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127047430</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2447,6 +2532,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049793</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2554,6 +2644,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126176059</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2661,6 +2756,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127045743</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2768,6 +2868,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126176512</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2875,6 +2980,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126176685</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2982,6 +3092,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126178007</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3089,6 +3204,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126178312</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3196,6 +3316,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126181209</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3303,6 +3428,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126181693</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3404,6 +3534,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126231168</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3511,6 +3646,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786500</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3608,6 +3748,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127047452</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3715,6 +3860,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182151</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3812,6 +3962,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049534</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3919,6 +4074,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182027</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4016,6 +4176,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127051933</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4123,6 +4288,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126181652</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4230,6 +4400,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182129</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4337,6 +4512,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182188</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4444,6 +4624,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182221</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4551,6 +4736,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182304</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4652,6 +4842,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126230894</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4753,6 +4948,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126230910</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4850,6 +5050,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127045952</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4947,6 +5152,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127046342</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5054,6 +5264,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786509</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5161,6 +5376,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786527</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5268,6 +5488,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786528</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5369,6 +5594,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126231107</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5476,6 +5706,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126175215</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5583,6 +5818,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126178047</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5690,6 +5930,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126180836</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5797,6 +6042,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786515</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5904,6 +6154,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786517</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6011,6 +6266,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786513</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6118,6 +6378,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786518</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6225,6 +6490,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786522</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6322,6 +6592,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127046229</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6429,6 +6704,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182142</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6526,6 +6806,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127046331</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6623,6 +6908,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127047986</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6730,6 +7020,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126175291</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6837,6 +7132,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126176144</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6949,6 +7249,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126177259</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7056,6 +7361,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126177726</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7168,6 +7478,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126181048</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7269,6 +7584,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126231127</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7370,6 +7690,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126231142</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7467,6 +7792,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048135</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7564,6 +7894,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048363</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7671,6 +8006,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786519</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7778,6 +8118,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126176239</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7895,6 +8240,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182207</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8015,6 +8365,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786503</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8135,6 +8490,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786505</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8255,6 +8615,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786524</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8375,6 +8740,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786531</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8482,6 +8852,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126177654</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8598,6 +8973,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126178109</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8714,6 +9094,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126178121</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8830,6 +9215,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126178142</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8941,6 +9331,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126180980</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9043,6 +9438,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126231185</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9159,6 +9559,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126175252</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9275,6 +9680,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126175256</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9391,6 +9801,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126175257</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9507,6 +9922,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126175525</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9623,6 +10043,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126175980</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9739,6 +10164,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126176599</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9855,6 +10285,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126176659</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9971,6 +10406,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126176747</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10087,6 +10527,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126176893</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10203,6 +10648,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126177332</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10319,6 +10769,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126177821</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10435,6 +10890,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126178017</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10551,6 +11011,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126178127</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10667,6 +11132,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126178221</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10783,6 +11253,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126180157</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10894,6 +11369,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126180477</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11010,6 +11490,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126180591</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11121,6 +11606,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126180936</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11232,6 +11722,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126181494</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11339,6 +11834,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126181665</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11446,6 +11946,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182366</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11553,6 +12058,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182411</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11655,6 +12165,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126230971</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11757,6 +12272,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126230989</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11859,6 +12379,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126231002</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11961,6 +12486,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126231026</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12063,6 +12593,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126231069</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12165,6 +12700,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126231086</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12262,6 +12802,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048038</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12374,6 +12919,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786520</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12471,6 +13021,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127047110</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12578,6 +13133,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126178155</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12675,6 +13235,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127047261</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12782,6 +13347,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126177002</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12889,6 +13459,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126179959</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12996,6 +13571,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126180415</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13103,6 +13683,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126181871</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13210,6 +13795,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126181960</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13317,6 +13907,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182040</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13424,6 +14019,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182094</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13531,6 +14131,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182178</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13638,6 +14243,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182185</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13745,6 +14355,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182214</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13852,6 +14467,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182236</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13959,6 +14579,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786504</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14066,6 +14691,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786511</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14173,6 +14803,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786512</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14280,6 +14915,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786516</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14387,6 +15027,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786523</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14494,6 +15139,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786526</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14601,6 +15251,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126175432</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14708,6 +15363,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126178181</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14805,6 +15465,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048180</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14902,6 +15567,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127046237</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15009,8 +15679,149 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126182276</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>